--- a/data/omxs30_och_makrodata.xlsx
+++ b/data/omxs30_och_makrodata.xlsx
@@ -547,49 +547,49 @@
         <v>42063</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1287688569949912</v>
+        <v>0.1287689741106801</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08842646211559413</v>
+        <v>0.08842659852752877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.106566217976285</v>
+        <v>0.1065663542323319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09620901544952876</v>
+        <v>0.09620878825504287</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.02323816809235235</v>
+        <v>-0.02323806513511095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0713576398753577</v>
+        <v>0.07135775290021384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1470475134460827</v>
+        <v>0.1470473025643535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06686212858314411</v>
+        <v>0.06686197048559217</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09907206808416458</v>
+        <v>0.0990717888863395</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07834117709004862</v>
+        <v>0.07834091361387752</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05305323574343102</v>
+        <v>0.05305291542634349</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06924672201215731</v>
+        <v>0.06924658337577916</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07416884707005567</v>
+        <v>0.07416896138191142</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08175477112425122</v>
+        <v>0.08175469195045082</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03818376125592171</v>
+        <v>0.03818368591828958</v>
       </c>
       <c r="Q2" t="n">
         <v>62.58000183105469</v>
@@ -621,49 +621,49 @@
         <v>42094</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01892031832263386</v>
+        <v>0.01892022640369628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0125447333249582</v>
+        <v>0.01254461817755992</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02697293192722205</v>
+        <v>0.02697315447891957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03867594830103172</v>
+        <v>0.03867595212496999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02946277227363781</v>
+        <v>0.02946289225598298</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002775285113181258</v>
+        <v>0.002775088172710438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0182663445414688</v>
+        <v>0.01826634789968984</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03930725132880308</v>
+        <v>-0.03930718134098632</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0361775950100871</v>
+        <v>0.0361774783679043</v>
       </c>
       <c r="K3" t="n">
         <v>0.03044868599457651</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002370342469136588</v>
+        <v>0.002370414682836053</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03067377356671686</v>
+        <v>-0.03067364788581284</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08765819700009403</v>
+        <v>0.08765829409048531</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001758485677771038</v>
+        <v>0.001758725077753764</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03677931606536022</v>
+        <v>0.03677924616755579</v>
       </c>
       <c r="Q3" t="n">
         <v>55.11000061035156</v>
@@ -695,49 +695,49 @@
         <v>42124</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.01419974473585361</v>
+        <v>-0.01419974601684237</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.05807402905748427</v>
+        <v>-0.05807392194089589</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05661478677219256</v>
+        <v>-0.0566148828566243</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05376378988899166</v>
+        <v>-0.05376398538610028</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0420876345478377</v>
+        <v>-0.04208752911715852</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1305011215651301</v>
+        <v>-0.1305008526017734</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01043693146108371</v>
+        <v>0.01043711389494328</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02156149771304383</v>
+        <v>-0.02156170497863263</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.01018335885694099</v>
+        <v>-0.01018324444061358</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08864698700403451</v>
+        <v>0.08864709694833106</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04856298843307494</v>
+        <v>0.04856298493445488</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01001789186337554</v>
+        <v>-0.01001802562431586</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.08438059565754719</v>
+        <v>-0.08438067698777918</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05676863712877789</v>
+        <v>-0.0567687121785061</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1335270213529649</v>
+        <v>0.1335272326097583</v>
       </c>
       <c r="Q4" t="n">
         <v>66.77999877929688</v>
@@ -769,49 +769,49 @@
         <v>42155</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03370122801160802</v>
+        <v>0.03370141411874883</v>
       </c>
       <c r="C5" t="n">
         <v>0.03273424402441982</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05155830004717132</v>
+        <v>0.05155840898116959</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01036483448828462</v>
+        <v>-0.01036443522338648</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005272589874683264</v>
+        <v>0.005272130279584397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04647349494171027</v>
+        <v>0.04647337675721297</v>
       </c>
       <c r="H5" t="n">
         <v>0.01119020780206337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01173641197762665</v>
+        <v>0.01173648445924513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01752155621513052</v>
+        <v>0.0175212042926709</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0146780309246648</v>
+        <v>0.01467802944230567</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.00472582869473881</v>
+        <v>-0.004725965782729769</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0005189072479472312</v>
+        <v>-0.0005186370890171155</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008823458381927551</v>
+        <v>0.008823564298096942</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02880659685923059</v>
+        <v>0.02880642814850698</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03571444290215298</v>
+        <v>-0.03571437917733078</v>
       </c>
       <c r="Q5" t="n">
         <v>65.55999755859375</v>
@@ -843,49 +843,49 @@
         <v>42185</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.06612875853509836</v>
+        <v>-0.06612910679295014</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.09322562449401883</v>
+        <v>-0.09322556604132026</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06898577647650306</v>
+        <v>-0.06898608907965287</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1000778347920199</v>
+        <v>-0.1000777229671266</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08653863518067129</v>
+        <v>-0.0865383318562456</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1024032608405909</v>
+        <v>-0.1024030449995181</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.03994906593491065</v>
+        <v>-0.0399489775813423</v>
       </c>
       <c r="I6" t="n">
         <v>-0.05056510432967665</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.08256626515804255</v>
+        <v>-0.08256595556275048</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1075948548164534</v>
+        <v>-0.107595142699742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00664756166905045</v>
+        <v>0.006647424062772078</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05763246118730381</v>
+        <v>-0.05763252098859706</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.08114658531953112</v>
+        <v>-0.08114677997753339</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0334999658087477</v>
+        <v>-0.03349980731545332</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.07046055834846432</v>
+        <v>-0.07046091538651744</v>
       </c>
       <c r="Q6" t="n">
         <v>63.59000015258789</v>
@@ -917,40 +917,40 @@
         <v>42216</v>
       </c>
       <c r="B7" t="n">
-        <v>0.008059626447405321</v>
+        <v>0.008060102723769669</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08773141940674112</v>
+        <v>0.08773122036470027</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1217167788809543</v>
+        <v>0.1217167931604768</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01637955641412336</v>
+        <v>0.01637943975757783</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1119617750521831</v>
+        <v>0.111961914185547</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07450517755343289</v>
+        <v>0.07450515963751037</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07157106029332561</v>
+        <v>-0.07157114573671131</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07518796263494498</v>
+        <v>0.07518788805399668</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07769472725490467</v>
+        <v>0.07769524268059369</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.04855443093966028</v>
+        <v>-0.04855421870840249</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01886792323440156</v>
+        <v>-0.01886765280918401</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09090914307350961</v>
+        <v>0.09090899310081269</v>
       </c>
       <c r="N7" t="n">
         <v>-0.1073506679779259</v>
@@ -959,7 +959,7 @@
         <v>0.04604237375199705</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.007774716686892669</v>
+        <v>-0.00777438646087325</v>
       </c>
       <c r="Q7" t="n">
         <v>52.20999908447266</v>
@@ -991,49 +991,49 @@
         <v>42247</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.06796116870054025</v>
+        <v>-0.06796124995744746</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1001891438001358</v>
+        <v>-0.1001889778861264</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07424356012654254</v>
+        <v>-0.07424346330393972</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09457151287592402</v>
+        <v>-0.09457178020528123</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08083420437560473</v>
+        <v>-0.08083414811278178</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1056337366249388</v>
+        <v>-0.105633824880884</v>
       </c>
       <c r="H8" t="n">
         <v>-0.02187162976590751</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05069938110021865</v>
+        <v>-0.05069938461700674</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.08410918717525007</v>
+        <v>-0.08410945080135013</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.06192647376358873</v>
+        <v>-0.06192641515228736</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05240373065825554</v>
+        <v>-0.05240393668195187</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04166678720631611</v>
+        <v>-0.04166672419695772</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04087674806407404</v>
+        <v>-0.04087687720651978</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.04352122692637683</v>
+        <v>-0.04352130802767407</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.09794308271298169</v>
+        <v>-0.09794327023710403</v>
       </c>
       <c r="Q8" t="n">
         <v>54.15000152587891</v>
@@ -1065,49 +1065,49 @@
         <v>42277</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.09313722126998902</v>
+        <v>-0.09313741366463513</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.04131651060645447</v>
+        <v>-0.04131650788528218</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0752619500111732</v>
+        <v>-0.0752621194740144</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05807961442688214</v>
+        <v>-0.05807950237629267</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.003748729647503835</v>
+        <v>-0.003748851839523559</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.004240045105372126</v>
+        <v>-0.004239982018908073</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.06414967988396858</v>
+        <v>-0.06414957854294301</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06169418742643207</v>
+        <v>-0.06169411886432097</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.05837970528256364</v>
+        <v>-0.05837976557427638</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1295843659797685</v>
+        <v>-0.1295844203637677</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.09335371296219186</v>
+        <v>-0.09335357921218546</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0521739196059402</v>
+        <v>-0.05217398821349628</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05064850395112985</v>
+        <v>-0.0506485780939514</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.04395041696658142</v>
+        <v>-0.04395033590166897</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1302931897946819</v>
+        <v>-0.1302930511825763</v>
       </c>
       <c r="Q9" t="n">
         <v>48.36999893188477</v>
@@ -1139,49 +1139,49 @@
         <v>42308</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08310809111868123</v>
+        <v>0.08310821162334503</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09788186693263667</v>
+        <v>0.09788165410795124</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1340892478568636</v>
+        <v>0.1340895778543907</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1284496311115235</v>
+        <v>0.1284495743245888</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03104408409119874</v>
+        <v>0.03104451608610281</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01399041418719893</v>
+        <v>0.01399016026106947</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1625540463627047</v>
+        <v>0.1625540287601119</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08701331934499446</v>
+        <v>0.08701324147048251</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1055382232261979</v>
+        <v>0.1055381552266492</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1221909673801522</v>
+        <v>0.1221908955977811</v>
       </c>
       <c r="L10" t="n">
         <v>0.006155534847818389</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0308589425331619</v>
+        <v>-0.03085894476685946</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02147048163349941</v>
+        <v>-0.02147034437138318</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06057339869392342</v>
+        <v>0.06057331000445565</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1079899577846433</v>
+        <v>0.1079900338215525</v>
       </c>
       <c r="Q10" t="n">
         <v>49.56000137329102</v>
@@ -1213,49 +1213,49 @@
         <v>42338</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02058646425927835</v>
+        <v>0.02058636153804905</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07318690050314758</v>
+        <v>0.07318703481272371</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09117644524113211</v>
+        <v>0.09117632769395612</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04170415409820061</v>
+        <v>0.0417041589141629</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08029200125093672</v>
+        <v>0.0802920917250014</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00719861848976211</v>
+        <v>0.007198618935756684</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06637467776027051</v>
+        <v>0.06637457843139183</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03851947107591958</v>
+        <v>-0.03851940219467331</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04095756292139585</v>
+        <v>0.04095799599729899</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1307883158442087</v>
+        <v>0.1307886440416246</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02558386734634799</v>
+        <v>0.02558378648837367</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0008607153572338655</v>
+        <v>-0.0008604913546796933</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01130335787366921</v>
+        <v>0.01130343116373345</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.01478858287216744</v>
+        <v>-0.01478841686068844</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01633818879876325</v>
+        <v>0.01633795548254691</v>
       </c>
       <c r="Q11" t="n">
         <v>44.61000061035156</v>
@@ -1287,49 +1287,49 @@
         <v>42369</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.06601461406510412</v>
+        <v>-0.06601472135865183</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.03905784722462746</v>
+        <v>-0.03905773060914908</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04043118648351407</v>
+        <v>-0.04043108775961912</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1028842078821077</v>
+        <v>-0.1028842747154658</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02364874220050017</v>
+        <v>-0.02364884208844742</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01965437573857609</v>
+        <v>-0.01965449997311897</v>
       </c>
       <c r="H12" t="n">
         <v>-0.005371414525774387</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05445996341513393</v>
+        <v>-0.05445988890420506</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.05387395065632583</v>
+        <v>-0.05387446334826251</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1804093747871635</v>
+        <v>-0.1804095036692166</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.03036865461677829</v>
+        <v>-0.03036857817014627</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02756243225950994</v>
+        <v>-0.02756257764528836</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.09796207906574839</v>
+        <v>-0.09796200740486261</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.03157332389022627</v>
+        <v>-0.03157340608961523</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1164079154599879</v>
+        <v>-0.116407848574403</v>
       </c>
       <c r="Q12" t="n">
         <v>37.27999877929688</v>
@@ -1361,49 +1361,49 @@
         <v>42400</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0366493889990408</v>
+        <v>-0.03664928913476617</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.05161273685152623</v>
+        <v>-0.05161291262105883</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01516843794503586</v>
+        <v>0.01516833350086211</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1228408029265675</v>
+        <v>-0.122840640341526</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05276786737305939</v>
+        <v>-0.05276824497231536</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.08383982953165758</v>
+        <v>-0.08383940609139573</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.09783982224465737</v>
+        <v>-0.09783973442434268</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07514079447588096</v>
+        <v>-0.07514078855459816</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.08605244491153408</v>
+        <v>-0.08605227367640989</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.03781220692532106</v>
+        <v>-0.03781234235482189</v>
       </c>
       <c r="L13" t="n">
         <v>-0.0794182743048385</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.04960139144584585</v>
+        <v>-0.04960154518997273</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05102024684469009</v>
+        <v>-0.05102032223478481</v>
       </c>
       <c r="O13" t="n">
         <v>-0.04275787430318756</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.02697628953724907</v>
+        <v>-0.02697620386723032</v>
       </c>
       <c r="Q13" t="n">
         <v>34.7400016784668</v>
@@ -1435,49 +1435,49 @@
         <v>42429</v>
       </c>
       <c r="B14" t="n">
-        <v>0.04823381397451332</v>
+        <v>0.04823393123296604</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.08163266350691489</v>
+        <v>-0.08163266872976116</v>
       </c>
       <c r="D14" t="n">
         <v>-0.08633086234076592</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06017517885603274</v>
+        <v>0.06017546060504331</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09637327171871024</v>
+        <v>-0.09637339675800305</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04973497872624866</v>
+        <v>0.04973469114921225</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03063391894475465</v>
+        <v>0.03063352658482388</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001073922213745249</v>
+        <v>-0.001073836917376614</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.002100139064001083</v>
+        <v>-0.002100070731240522</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09894718237091604</v>
+        <v>0.09894726120059283</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02187107617060402</v>
+        <v>0.02187116449540749</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0260950463307732</v>
+        <v>0.02609537408826501</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08909368978053345</v>
+        <v>0.0890935223516327</v>
       </c>
       <c r="O14" t="n">
         <v>-0.02847574670767405</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1141199856415969</v>
+        <v>0.1141197995036014</v>
       </c>
       <c r="Q14" t="n">
         <v>35.97000122070312</v>
@@ -1509,49 +1509,49 @@
         <v>42460</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02721961978523701</v>
+        <v>0.02721951306966908</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.01555565525670599</v>
+        <v>-0.01555558667346335</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.02967894078021682</v>
+        <v>-0.02967905170257501</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05417935490403436</v>
+        <v>0.05417934050549356</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0682878821382249</v>
+        <v>-0.06828749961963565</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02716359859614981</v>
+        <v>0.02716333762350609</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07960355483621617</v>
+        <v>0.07960414409875649</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0300963491914833</v>
+        <v>-0.03009677053955806</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008067224819196195</v>
+        <v>0.008067224266780304</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07279698113246957</v>
+        <v>0.07279717695259746</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.01969684174787967</v>
+        <v>-0.01969709934854402</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.00722008285666631</v>
+        <v>-0.007220002891374921</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03385047348786197</v>
+        <v>0.03385063242411923</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00517237040776819</v>
+        <v>0.005172558898362878</v>
       </c>
       <c r="P15" t="n">
-        <v>0.03124981725091325</v>
+        <v>0.03124997777375804</v>
       </c>
       <c r="Q15" t="n">
         <v>39.59999847412109</v>
@@ -1583,49 +1583,49 @@
         <v>42490</v>
       </c>
       <c r="B16" t="n">
-        <v>0.07066259939073971</v>
+        <v>0.07066271061951412</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.01578723295242801</v>
+        <v>-0.01578716218463572</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06760595581721018</v>
+        <v>0.06760596354559323</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03710209245536</v>
+        <v>0.03710176797893561</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0221836559693136</v>
+        <v>0.02218350956526538</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1633524460478311</v>
+        <v>-0.1633521699619598</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01329134666177434</v>
+        <v>0.01329108071295093</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05467282034865972</v>
+        <v>0.05467309860278369</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02540026064194545</v>
+        <v>0.02540032684511329</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01167421995571161</v>
+        <v>0.01167403529249711</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01096072357422295</v>
+        <v>-0.01096072550706095</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03484982623243171</v>
+        <v>0.03484981793117314</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04819268508985264</v>
+        <v>0.04819275943925083</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05621663362708751</v>
+        <v>0.0562164355646757</v>
       </c>
       <c r="P16" t="n">
-        <v>0.09225154942037173</v>
+        <v>0.0922513890871739</v>
       </c>
       <c r="Q16" t="n">
         <v>48.13000106811523</v>
@@ -1657,49 +1657,49 @@
         <v>42521</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02062448761410041</v>
+        <v>0.02062439058280208</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.003949340926859057</v>
+        <v>-0.003949484448761198</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02969113891521169</v>
+        <v>0.02969114209442414</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03705483137376642</v>
+        <v>0.03705452977590173</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05489356048432681</v>
+        <v>0.05489355667981011</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.01076916839851494</v>
+        <v>-0.0107693194197358</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02468465021121169</v>
+        <v>0.02468439119346577</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07114430810263583</v>
+        <v>-0.07114439148702123</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0205126492926162</v>
+        <v>0.0205123815912438</v>
       </c>
       <c r="K17" t="n">
         <v>-0.01031567572300907</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0423726796392172</v>
+        <v>0.04237277634234271</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0009352948591851984</v>
+        <v>-0.0009355248230574764</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.007437332425415999</v>
+        <v>-0.007437402828914141</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06004641427407154</v>
+        <v>0.06004623673410259</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.01223407505797114</v>
+        <v>-0.0122338654375832</v>
       </c>
       <c r="Q17" t="n">
         <v>49.68999862670898</v>
@@ -1731,49 +1731,49 @@
         <v>42551</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.04214780271118301</v>
+        <v>-0.04214752150661683</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04678824238807833</v>
+        <v>0.0467882457656299</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.007497057123010187</v>
+        <v>-0.007496745936827587</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008352523389327349</v>
+        <v>0.008352643523191317</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02057290154183589</v>
+        <v>0.02057290019018354</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05557290829778361</v>
+        <v>-0.0555726695673231</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.03710921299124081</v>
+        <v>-0.03710948563586169</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.03204710964000779</v>
+        <v>-0.03204685414322039</v>
       </c>
       <c r="K18" t="n">
         <v>0.02697748890147755</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0875547494603629</v>
+        <v>-0.08755458589977572</v>
       </c>
       <c r="M18" t="n">
         <v>-0.04681643294788551</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.08651218325394205</v>
+        <v>-0.0865122547164735</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.04302852841888483</v>
+        <v>-0.04302853562544184</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1060850291160186</v>
+        <v>-0.1060851561029488</v>
       </c>
       <c r="Q18" t="n">
         <v>49.68000030517578</v>
@@ -1805,49 +1805,49 @@
         <v>42582</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1020898294977677</v>
+        <v>0.1020896107244953</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0219697390257334</v>
+        <v>0.02196967157934293</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09122595631235031</v>
+        <v>0.09122593719612238</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1058444426364789</v>
+        <v>0.1058450483722611</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1472332357411348</v>
+        <v>0.1472331618866041</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.007776201587535003</v>
+        <v>-0.007775818454796357</v>
       </c>
       <c r="H19" t="n">
         <v>0.103301802414669</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04868130614126254</v>
+        <v>0.04868169721903581</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04948410701409522</v>
+        <v>0.0494838991863451</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09492518519526638</v>
+        <v>0.09492542188543851</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02878710337768675</v>
+        <v>0.02878710067944579</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0117877489721252</v>
+        <v>0.01178766840188117</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01118561949727259</v>
+        <v>0.0111856203723284</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02333528852904498</v>
+        <v>0.02333546762686245</v>
       </c>
       <c r="P19" t="n">
-        <v>0.09879507771491691</v>
+        <v>0.09879483934144395</v>
       </c>
       <c r="Q19" t="n">
         <v>42.45999908447266</v>
@@ -1879,22 +1879,22 @@
         <v>42613</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02032989038206834</v>
+        <v>0.0203297102627229</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.01408447757961084</v>
+        <v>-0.01408441200145782</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07667730801148376</v>
+        <v>-0.07667758133214864</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01040414311727011</v>
+        <v>0.01040361432740378</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.01941162785295036</v>
+        <v>-0.01941151562430388</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.04310344560871138</v>
+        <v>-0.04310358696765304</v>
       </c>
       <c r="H20" t="n">
         <v>0.03288884813342818</v>
@@ -1903,25 +1903,25 @@
         <v>0.009671213072069085</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02442300040110923</v>
+        <v>0.02442338537040478</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01363169141274767</v>
+        <v>0.01363136421078659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1152563806462574</v>
+        <v>0.1152562790373075</v>
       </c>
       <c r="M20" t="n">
-        <v>0.07281542342413516</v>
+        <v>0.07281558848568848</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06415921415687387</v>
+        <v>0.06415937385064563</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09510567463453889</v>
+        <v>0.0951055891230792</v>
       </c>
       <c r="P20" t="n">
-        <v>0.009320354874637893</v>
+        <v>0.009320573837441115</v>
       </c>
       <c r="Q20" t="n">
         <v>47.04000091552734</v>
@@ -1953,49 +1953,49 @@
         <v>42643</v>
       </c>
       <c r="B21" t="n">
-        <v>0.03823368171921637</v>
+        <v>0.03823360020336319</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01127816435490381</v>
+        <v>0.0112782335697581</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00519038230363833</v>
+        <v>0.005190486831975871</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06383812208705897</v>
+        <v>0.06383855144668504</v>
       </c>
       <c r="F21" t="n">
-        <v>0.009795344527489647</v>
+        <v>0.009795457856709877</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01474220778428204</v>
+        <v>0.01474196290659946</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07458405551829417</v>
+        <v>0.07458397722912546</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07279679486090129</v>
+        <v>-0.07279670680956463</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03874190107738618</v>
+        <v>0.03874163948235276</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01506170232957893</v>
+        <v>0.0150618105671636</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02986843819732266</v>
+        <v>0.0298685198898947</v>
       </c>
       <c r="M21" t="n">
-        <v>0.06696838342671807</v>
+        <v>0.066968378455875</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02633412916283784</v>
+        <v>0.02633405454771087</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02386991893280754</v>
+        <v>0.02387007696694865</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0635522175603076</v>
+        <v>0.06355243249780451</v>
       </c>
       <c r="Q21" t="n">
         <v>49.06000137329102</v>
@@ -2027,7 +2027,7 @@
         <v>42674</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.03578843381872543</v>
+        <v>-0.03578827291668585</v>
       </c>
       <c r="C22" t="n">
         <v>-0.03494421472095721</v>
@@ -2036,40 +2036,40 @@
         <v>-0.05737241336003351</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04195720503539646</v>
+        <v>0.04195670794189654</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09611983540296154</v>
+        <v>-0.09612015363474846</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2942695673238037</v>
+        <v>-0.2942694314501476</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1558996091530473</v>
+        <v>-0.1558996933664932</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04999982431577887</v>
+        <v>0.04999991453200869</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02358953812133313</v>
+        <v>0.02358935655035088</v>
       </c>
       <c r="K22" t="n">
         <v>0.08850025316881216</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05742484017344829</v>
+        <v>0.05742467697171549</v>
       </c>
       <c r="M22" t="n">
-        <v>0.04495343544226937</v>
+        <v>0.04495343231495497</v>
       </c>
       <c r="N22" t="n">
-        <v>0.03376099637415653</v>
+        <v>0.03376092553891619</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04960308804880453</v>
+        <v>0.04960316053052449</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.009192985533641562</v>
+        <v>-0.009193185769730716</v>
       </c>
       <c r="Q22" t="n">
         <v>48.29999923706055</v>
@@ -2101,49 +2101,49 @@
         <v>42704</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01075836330535629</v>
+        <v>0.01075845242422924</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06625572657604661</v>
+        <v>0.06625558631547768</v>
       </c>
       <c r="D23" t="n">
-        <v>0.06147279162305552</v>
+        <v>0.06147290137120431</v>
       </c>
       <c r="E23" t="n">
-        <v>0.052829918135473</v>
+        <v>0.0528302145296391</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.05131702302582597</v>
+        <v>-0.05131709215704627</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0862304361890911</v>
+        <v>0.08623031358417022</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0332067694569842</v>
+        <v>0.03320703412288251</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05430927012305942</v>
+        <v>0.05430916985701972</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.02989732478414453</v>
+        <v>-0.02989726962461348</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06329119910007952</v>
+        <v>0.06329100608349658</v>
       </c>
       <c r="L23" t="n">
-        <v>0.008228005871317334</v>
+        <v>0.008228081504104034</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03896114098520354</v>
+        <v>0.03896093866610428</v>
       </c>
       <c r="N23" t="n">
-        <v>0.08425846998878983</v>
+        <v>0.08425861280609492</v>
       </c>
       <c r="O23" t="n">
-        <v>0.006143881604067758</v>
+        <v>0.006143590069257909</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01649490998607361</v>
+        <v>0.01649484199638662</v>
       </c>
       <c r="Q23" t="n">
         <v>50.47000122070312</v>
@@ -2175,49 +2175,49 @@
         <v>42735</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02075567883544815</v>
+        <v>0.02075576606727347</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08959520786965114</v>
+        <v>0.08959541697291984</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03038979840252642</v>
+        <v>-0.0303897952604546</v>
       </c>
       <c r="E24" t="n">
         <v>-0.005376241536729109</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02241852077798878</v>
+        <v>0.02241892174998039</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1265529977716158</v>
+        <v>0.1265528938600196</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.003672880331114792</v>
+        <v>-0.003673130635889366</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0541246724249701</v>
+        <v>-0.05412475356546231</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09309805427055018</v>
+        <v>0.09309787847393713</v>
       </c>
       <c r="K24" t="n">
-        <v>0.03205121979666203</v>
+        <v>0.03205149790612549</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03971696068518948</v>
+        <v>0.03971718389527346</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.01093769043334636</v>
+        <v>-0.01093737144245632</v>
       </c>
       <c r="N24" t="n">
-        <v>0.009638615586476273</v>
+        <v>0.009638614977344862</v>
       </c>
       <c r="O24" t="n">
-        <v>0.03475809642547723</v>
+        <v>0.03475824587936227</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07910755079253029</v>
+        <v>0.07910762297015639</v>
       </c>
       <c r="Q24" t="n">
         <v>56.13000106811523</v>
@@ -2249,46 +2249,46 @@
         <v>42766</v>
       </c>
       <c r="B25" t="n">
-        <v>0.08237749177615483</v>
+        <v>0.08237739927825527</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08222827714819991</v>
+        <v>0.08222821182042117</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02069776294869785</v>
+        <v>-0.02069776074163587</v>
       </c>
       <c r="E25" t="n">
-        <v>0.010090111661895</v>
+        <v>0.01009020127530635</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.05330912913762342</v>
+        <v>-0.05330918343885716</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.03457939597780957</v>
+        <v>-0.03457939916736263</v>
       </c>
       <c r="H25" t="n">
-        <v>0.06297987204725652</v>
+        <v>0.0629799664535462</v>
       </c>
       <c r="I25" t="n">
         <v>-0.01341745577939601</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0246695026232322</v>
+        <v>0.02466972938240852</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04702744578784346</v>
+        <v>0.04702752959700796</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02825757355110636</v>
+        <v>0.028257424362365</v>
       </c>
       <c r="M25" t="n">
-        <v>0.03159558675185914</v>
+        <v>0.0315953862495153</v>
       </c>
       <c r="N25" t="n">
-        <v>0.05011906881892925</v>
+        <v>0.05011919086913563</v>
       </c>
       <c r="O25" t="n">
-        <v>0.003631296047672317</v>
+        <v>0.003631365838682399</v>
       </c>
       <c r="P25" t="n">
         <v>0.05075180198738805</v>
@@ -2323,25 +2323,25 @@
         <v>42794</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.01637783301929363</v>
+        <v>-0.01637775406524522</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001225323273277512</v>
+        <v>0.00122543482856452</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06038632745879258</v>
+        <v>0.06038642977011421</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05458442604625424</v>
+        <v>0.05458415504894099</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1594199375769501</v>
+        <v>0.1594200523642357</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1374635326871805</v>
+        <v>0.1374639279901217</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05375720190706779</v>
+        <v>0.05375728502477273</v>
       </c>
       <c r="I26" t="n">
         <v>-0.04559996756864981</v>
@@ -2350,19 +2350,19 @@
         <v>0.02608194879177783</v>
       </c>
       <c r="K26" t="n">
-        <v>0.04067799030362496</v>
+        <v>0.04067789947521661</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0513995751389178</v>
+        <v>0.0513996411563753</v>
       </c>
       <c r="M26" t="n">
         <v>-0.03828474120045755</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.02329526082509381</v>
+        <v>-0.02329555469073508</v>
       </c>
       <c r="O26" t="n">
-        <v>0.008141080255489985</v>
+        <v>0.008141149227862021</v>
       </c>
       <c r="P26" t="n">
         <v>0.05456176346745489</v>
@@ -2397,49 +2397,49 @@
         <v>42825</v>
       </c>
       <c r="B27" t="n">
-        <v>0.02546539777944745</v>
+        <v>0.02546539573537387</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03488387769384116</v>
+        <v>0.03488365096962176</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04954444995182494</v>
+        <v>0.04954433709105022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07002719633451826</v>
+        <v>0.07002703986424041</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0558182587824918</v>
+        <v>0.05581812785323592</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03577689869483724</v>
+        <v>0.03577663769171124</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.01261649083567995</v>
+        <v>-0.01261656568922898</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.04023459133853646</v>
+        <v>-0.04023468765621518</v>
       </c>
       <c r="J27" t="n">
         <v>0.05363135770301763</v>
       </c>
       <c r="K27" t="n">
-        <v>0.09039085548877379</v>
+        <v>0.0903909289049063</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01850009621056148</v>
+        <v>0.01849996137677667</v>
       </c>
       <c r="M27" t="n">
-        <v>0.02033592753670788</v>
+        <v>0.02033599283966181</v>
       </c>
       <c r="N27" t="n">
-        <v>0.06368184774984842</v>
+        <v>0.06368209963432681</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.009449772952027868</v>
+        <v>-0.009449840625333938</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1221373704200137</v>
+        <v>0.122137482294469</v>
       </c>
       <c r="Q27" t="n">
         <v>52.83000183105469</v>
@@ -2471,49 +2471,49 @@
         <v>42855</v>
       </c>
       <c r="B28" t="n">
-        <v>0.03984583823989385</v>
+        <v>0.03984591339630272</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1007197598424761</v>
+        <v>0.1007198783493444</v>
       </c>
       <c r="D28" t="n">
-        <v>0.05759170909348499</v>
+        <v>0.05759160562038645</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06129754604458637</v>
+        <v>0.06129787980437285</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.03136193389872577</v>
+        <v>-0.0313621535079911</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0451504921795578</v>
+        <v>-0.04515065436882748</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0713888415708106</v>
+        <v>0.07138892279281039</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.04192157784440931</v>
+        <v>-0.04192138134057022</v>
       </c>
       <c r="J28" t="n">
         <v>0.07343569990097487</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0839502422445868</v>
+        <v>0.08395000775369099</v>
       </c>
       <c r="L28" t="n">
         <v>0.02306931074644347</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0227826514152123</v>
+        <v>0.02278264995709023</v>
       </c>
       <c r="N28" t="n">
-        <v>0.09757497492172429</v>
+        <v>0.09757473422825647</v>
       </c>
       <c r="O28" t="n">
-        <v>0.01107885618690818</v>
+        <v>0.01107899468538887</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1237484082024445</v>
+        <v>0.1237483958650205</v>
       </c>
       <c r="Q28" t="n">
         <v>51.72999954223633</v>
@@ -2545,49 +2545,49 @@
         <v>42886</v>
       </c>
       <c r="B29" t="n">
-        <v>0.009681990060716794</v>
+        <v>0.009681762775320735</v>
       </c>
       <c r="C29" t="n">
         <v>-0.03687386208538435</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01719642235669983</v>
+        <v>0.01719632984611597</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.02898540954698448</v>
+        <v>-0.02898548362674347</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09990777527663397</v>
+        <v>0.09990767161683611</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1103328385073212</v>
+        <v>0.1103331120360282</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0009228340359193066</v>
+        <v>-0.0009229047945480406</v>
       </c>
       <c r="I29" t="n">
-        <v>0.009611336764342449</v>
+        <v>0.009611231011018129</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01977060916024298</v>
+        <v>0.01977033000766459</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.04219420664054185</v>
+        <v>-0.0421940729456507</v>
       </c>
       <c r="L29" t="n">
         <v>0.02745086280946452</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0262528563498432</v>
+        <v>-0.02625285470705019</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.08633094728601576</v>
+        <v>-0.08633085176440769</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.0019054805344767</v>
+        <v>-0.001905755628559769</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.0193235827787519</v>
+        <v>-0.01932375850203583</v>
       </c>
       <c r="Q29" t="n">
         <v>50.31000137329102</v>
@@ -2619,49 +2619,49 @@
         <v>42916</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.04474893497607824</v>
+        <v>-0.04474886375819187</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0148572773756882</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.05174171885487278</v>
+        <v>-0.05174163261397269</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004353169448379601</v>
+        <v>0.00435316978048772</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.03784726297715202</v>
+        <v>-0.03784695678796279</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.04968461690499892</v>
+        <v>-0.04968461310462857</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0520093827618664</v>
+        <v>0.05200952809336368</v>
       </c>
       <c r="I30" t="n">
         <v>-0.03048489673146815</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01045296580560651</v>
+        <v>0.01045305991388656</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.02716593171942006</v>
+        <v>-0.02716600107899991</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.02767187442423291</v>
+        <v>-0.02767181259689888</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.01470591448437464</v>
+        <v>-0.01470591353933048</v>
       </c>
       <c r="N30" t="n">
         <v>-0.03993263985229012</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.02004777798555479</v>
+        <v>-0.02004764136202042</v>
       </c>
       <c r="P30" t="n">
-        <v>0.01055604895240592</v>
+        <v>0.010555959440393</v>
       </c>
       <c r="Q30" t="n">
         <v>47.91999816894531</v>
@@ -2693,49 +2693,49 @@
         <v>42947</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.0913003172282093</v>
+        <v>-0.09130023918160957</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0464035678304362</v>
+        <v>0.04640367091832021</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.06537022458849229</v>
+        <v>-0.06537012867936198</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0941175416078891</v>
+        <v>-0.09411762471752216</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1375873377236393</v>
+        <v>-0.137587377162678</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1294604358991653</v>
+        <v>-0.1294605864569146</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.003745357182312947</v>
+        <v>-0.003745356930165866</v>
       </c>
       <c r="I31" t="n">
-        <v>0.002858495178643672</v>
+        <v>0.002858602190292991</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.05665036307643623</v>
+        <v>-0.05665037330782452</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03924529579575464</v>
+        <v>-0.03924522250841744</v>
       </c>
       <c r="L31" t="n">
-        <v>0.003925473860727724</v>
+        <v>0.00392541002422031</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.003316735199787479</v>
+        <v>-0.003316930649499672</v>
       </c>
       <c r="N31" t="n">
         <v>-0.05916814267507908</v>
       </c>
       <c r="O31" t="n">
-        <v>0.02679020387780251</v>
+        <v>0.02679013157626042</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.04456851793049177</v>
+        <v>-0.04456825734422787</v>
       </c>
       <c r="Q31" t="n">
         <v>52.65000152587891</v>
@@ -2767,49 +2767,49 @@
         <v>42978</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.03419227280847614</v>
+        <v>-0.03419252753640567</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.002217209490239846</v>
+        <v>-0.002217209271808462</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.006936412507358991</v>
+        <v>-0.00693641179556348</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06425148274103765</v>
+        <v>0.06425157736873643</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.04162301978600402</v>
+        <v>-0.04162301715990291</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1121069014772217</v>
+        <v>-0.1121068193837813</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.02280692602031165</v>
+        <v>-0.02280712720613454</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.04513050167374688</v>
+        <v>-0.04513081697787646</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.02976508308714243</v>
+        <v>-0.02976508878571771</v>
       </c>
       <c r="K32" t="n">
-        <v>0.03142197791619061</v>
+        <v>0.03142182295728624</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01075262142848965</v>
+        <v>0.01075268476675961</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.01164736748802941</v>
+        <v>-0.01164717269520821</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.01120787395789391</v>
+        <v>-0.01120781061760578</v>
       </c>
       <c r="O32" t="n">
-        <v>0.01897550383837343</v>
+        <v>0.01897529810468535</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.01093295901623137</v>
+        <v>-0.01093305168978631</v>
       </c>
       <c r="Q32" t="n">
         <v>52.38000106811523</v>
@@ -2841,49 +2841,49 @@
         <v>43008</v>
       </c>
       <c r="B33" t="n">
-        <v>0.09803904654698847</v>
+        <v>0.09803933077075766</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1050000439372039</v>
+        <v>0.1049999348347153</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08265429111009248</v>
+        <v>0.08265417923509477</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1075786391418443</v>
+        <v>0.1075788839880614</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1597121137061985</v>
+        <v>0.1597121690245955</v>
       </c>
       <c r="G33" t="n">
-        <v>0.004294848358343151</v>
+        <v>0.004294744225660452</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03539359929607944</v>
+        <v>0.03539367334406585</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04975130604972944</v>
+        <v>0.04975154066911647</v>
       </c>
       <c r="J33" t="n">
-        <v>0.08261555527118825</v>
+        <v>0.0826160648860117</v>
       </c>
       <c r="K33" t="n">
-        <v>0.07006853681071856</v>
+        <v>0.07006876386418925</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03771774020917906</v>
+        <v>0.03771761251669936</v>
       </c>
       <c r="M33" t="n">
-        <v>0.03451188655803117</v>
+        <v>0.03451188427299123</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1177582074145753</v>
+        <v>0.1177580076964695</v>
       </c>
       <c r="O33" t="n">
-        <v>0.04841682203063025</v>
+        <v>0.04841703370863648</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1569640432637345</v>
+        <v>0.1569641379974134</v>
       </c>
       <c r="Q33" t="n">
         <v>57.54000091552734</v>
@@ -2915,49 +2915,49 @@
         <v>43039</v>
       </c>
       <c r="B34" t="n">
-        <v>0.08829362275287367</v>
+        <v>0.0882936156020766</v>
       </c>
       <c r="C34" t="n">
-        <v>0.06636512344457302</v>
+        <v>0.06636503409137307</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.04999985206014834</v>
+        <v>-0.04999994750521397</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07785936264213733</v>
+        <v>0.07785928042757417</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03744277379681349</v>
+        <v>0.03744265601305363</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1267903567021489</v>
+        <v>0.1267904735360794</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06341342640683711</v>
+        <v>0.06341336385320906</v>
       </c>
       <c r="I34" t="n">
         <v>-0.003791669589709112</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03132002468623662</v>
+        <v>0.03131983385642423</v>
       </c>
       <c r="K34" t="n">
-        <v>0.08825602843310509</v>
+        <v>0.08825594711920925</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.03821059875453414</v>
+        <v>-0.03821066144876295</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.02359649354110416</v>
+        <v>-0.0235964280294737</v>
       </c>
       <c r="N34" t="n">
-        <v>0.09690143189112654</v>
+        <v>0.09690144299788694</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.07726452839110265</v>
+        <v>-0.07726465677673622</v>
       </c>
       <c r="P34" t="n">
-        <v>0.05668795524959624</v>
+        <v>0.05668786872665721</v>
       </c>
       <c r="Q34" t="n">
         <v>61.36999893188477</v>
@@ -2989,49 +2989,49 @@
         <v>43069</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.02734719416656695</v>
+        <v>-0.02734726654961683</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.06742105444413893</v>
+        <v>-0.06742106009350557</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03961512134933987</v>
+        <v>-0.03961522579789556</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02069702152385167</v>
+        <v>-0.02069715215502166</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.03345073909819896</v>
+        <v>-0.03345062966296686</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0009487272285910731</v>
+        <v>-0.0009486352084913108</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.04216166575566294</v>
+        <v>-0.04216141982692245</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.03957691133477159</v>
+        <v>-0.03957723191153617</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.05784508546215517</v>
+        <v>-0.05784525708232402</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.06016992295813139</v>
+        <v>-0.06017010966468672</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.03682179303458299</v>
+        <v>-0.03682148372884475</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.04666659893359748</v>
+        <v>-0.04666659281578156</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.02824858225738913</v>
+        <v>-0.02824858520918461</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.03801749425281764</v>
+        <v>-0.03801729083853256</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.04038589320134445</v>
+        <v>-0.0403858157127498</v>
       </c>
       <c r="Q35" t="n">
         <v>63.56999969482422</v>
@@ -3063,49 +3063,49 @@
         <v>43100</v>
       </c>
       <c r="B36" t="n">
-        <v>0.03233358041134515</v>
+        <v>0.03233365692187729</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.02022247244477093</v>
+        <v>-0.02022238441165292</v>
       </c>
       <c r="D36" t="n">
-        <v>0.004124670326089319</v>
+        <v>0.004125089640043322</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.01501673648175617</v>
+        <v>-0.01501667010036156</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03551951855933733</v>
+        <v>0.03551906164732777</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02279199707540314</v>
+        <v>0.02279199497608975</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0007295402355602665</v>
+        <v>-0.0007297368521307357</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1410456012043926</v>
+        <v>-0.1410451476028965</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.04297785617473082</v>
+        <v>-0.0429777664144495</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.03118695275397865</v>
+        <v>-0.03118720739972369</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.01923078906445475</v>
+        <v>-0.01923085517672796</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.03699803508290489</v>
+        <v>-0.03699803906134735</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.01000502243462609</v>
+        <v>-0.01000502171109019</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.04082917068396652</v>
+        <v>-0.04082924813676037</v>
       </c>
       <c r="Q36" t="n">
         <v>66.59999847412109</v>
@@ -3137,46 +3137,46 @@
         <v>43131</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.004085394627123873</v>
+        <v>-0.004085394324338298</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06656341340642302</v>
+        <v>0.06656350511101805</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02406116792267965</v>
+        <v>0.02406095454319557</v>
       </c>
       <c r="E37" t="n">
-        <v>0.04319587898317279</v>
+        <v>0.04319601582492805</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.02744090448674552</v>
+        <v>-0.0274404761319017</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.06035275785637151</v>
+        <v>-0.06035293253119589</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1421268637740882</v>
+        <v>0.142127069956155</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1769639234401914</v>
+        <v>-0.1769638890563813</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02940379762342271</v>
+        <v>0.02940389562660783</v>
       </c>
       <c r="K37" t="n">
-        <v>0.07967973359111058</v>
+        <v>0.07968014981177229</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03364484069672091</v>
+        <v>0.03364470839135514</v>
       </c>
       <c r="M37" t="n">
-        <v>0.02183607948443145</v>
+        <v>0.0218360779536142</v>
       </c>
       <c r="N37" t="n">
-        <v>0.06888055365822421</v>
+        <v>0.0688805613495973</v>
       </c>
       <c r="O37" t="n">
-        <v>0.01768582675060193</v>
+        <v>0.01768575241056958</v>
       </c>
       <c r="P37" t="n">
         <v>0.05337272612931421</v>
@@ -3211,49 +3211,49 @@
         <v>43159</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.07657236692093872</v>
+        <v>-0.0765724356407409</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.03096275501540147</v>
+        <v>-0.0309628383345546</v>
       </c>
       <c r="D38" t="n">
-        <v>0.06504303497877695</v>
+        <v>0.06504293324364374</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.03897158922020616</v>
+        <v>-0.03897171528358501</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00389504054064238</v>
+        <v>0.003895040102746439</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1019761640474157</v>
+        <v>0.1019762696598372</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0370766115225003</v>
+        <v>0.03707649235616506</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.01377916198319584</v>
+        <v>-0.01377915873027735</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.02596732090421938</v>
+        <v>-0.02596722322820932</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.004189284509461211</v>
+        <v>-0.004189533813752533</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.01627492052452872</v>
+        <v>-0.01627485860826428</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.003925066231333374</v>
+        <v>-0.003925203175728309</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.1042363873313189</v>
+        <v>-0.1042362937538078</v>
       </c>
       <c r="O38" t="n">
-        <v>0.037736049495116</v>
+        <v>0.03773583415914672</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.02424623722016717</v>
+        <v>-0.02424607737735018</v>
       </c>
       <c r="Q38" t="n">
         <v>65.77999877929688</v>
@@ -3285,49 +3285,49 @@
         <v>43190</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.02467927762204836</v>
+        <v>-0.02467919703296795</v>
       </c>
       <c r="C39" t="n">
         <v>-0.01572644597777439</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.02959379328046063</v>
+        <v>-0.02959360506312958</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01717843396354413</v>
+        <v>0.01717829746860589</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05707086820865603</v>
+        <v>0.05707074982966653</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.03301189430787754</v>
+        <v>-0.03301215521853051</v>
       </c>
       <c r="H39" t="n">
-        <v>0.01910822450291305</v>
+        <v>0.01910811370490473</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.08907004862236889</v>
+        <v>-0.08907010709254315</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.01572892410378468</v>
+        <v>-0.01572931199666583</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.0132687252490431</v>
+        <v>-0.01326878810063492</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.04756347939061689</v>
+        <v>-0.0475633533424672</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.01809334981059463</v>
+        <v>-0.01809328217961614</v>
       </c>
       <c r="N39" t="n">
-        <v>0.008912804400889707</v>
+        <v>0.008912921023997544</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.04264390819789332</v>
+        <v>-0.04264357120411955</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.02994573801638079</v>
+        <v>-0.02994589692550975</v>
       </c>
       <c r="Q39" t="n">
         <v>70.26999664306641</v>
@@ -3359,49 +3359,49 @@
         <v>43220</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0311123593490974</v>
+        <v>0.03111210889349669</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1257580293575999</v>
+        <v>0.1257581195039463</v>
       </c>
       <c r="D40" t="n">
-        <v>0.03989685176807267</v>
+        <v>0.03989674940567323</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.02212802696892291</v>
+        <v>-0.0221280970331712</v>
       </c>
       <c r="F40" t="n">
-        <v>0.05535617349163546</v>
+        <v>0.05535606755004996</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2698410557001181</v>
+        <v>0.2698413983259957</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02419358433502117</v>
+        <v>0.02419369568592455</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1968368367666922</v>
+        <v>0.1968364519111154</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03764887760311431</v>
+        <v>0.03764888508047437</v>
       </c>
       <c r="K40" t="n">
-        <v>0.008096368621851591</v>
+        <v>0.008096432834334921</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.05649601642410884</v>
+        <v>-0.05649587747225737</v>
       </c>
       <c r="M40" t="n">
         <v>-0.05950096184710563</v>
       </c>
       <c r="N40" t="n">
-        <v>0.044281771908949</v>
+        <v>0.04428142001177893</v>
       </c>
       <c r="O40" t="n">
-        <v>0.02112315622858696</v>
+        <v>0.02112293642780827</v>
       </c>
       <c r="P40" t="n">
-        <v>0.00849365519490286</v>
+        <v>0.008493570759055435</v>
       </c>
       <c r="Q40" t="n">
         <v>75.16999816894531</v>
@@ -3433,49 +3433,49 @@
         <v>43251</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.01133558999103046</v>
+        <v>-0.01133559180778798</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01148371780018698</v>
+        <v>0.01148363680449171</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02931566676129371</v>
+        <v>0.02931604539560317</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04825426170046465</v>
+        <v>0.04825447747261458</v>
       </c>
       <c r="F41" t="n">
-        <v>0.04970045213257213</v>
+        <v>0.04970075827578868</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0482141984450597</v>
+        <v>-0.04821434009945558</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.02119788039241977</v>
+        <v>-0.02119798654476557</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.08303468077793896</v>
+        <v>-0.08303461974488402</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.02588583329927974</v>
+        <v>-0.02588555115129565</v>
       </c>
       <c r="K41" t="n">
-        <v>0.02000001010963137</v>
+        <v>0.02000007329482734</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.03709078318661718</v>
+        <v>-0.03709099863235743</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.01367344826063666</v>
+        <v>-0.0136735974290525</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.03819169023098823</v>
+        <v>-0.03819147730341899</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.04006279359763987</v>
+        <v>-0.04006272567733182</v>
       </c>
       <c r="P41" t="n">
-        <v>0.01709114540773271</v>
+        <v>0.01709106311395869</v>
       </c>
       <c r="Q41" t="n">
         <v>77.58999633789062</v>
@@ -3507,49 +3507,49 @@
         <v>43281</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.02442672408307989</v>
+        <v>-0.024426565935039</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.03451411967168494</v>
+        <v>-0.03451404050468643</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00685682576998925</v>
+        <v>0.006856271472116982</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.02066928206153995</v>
+        <v>-0.02066921660684984</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.02868607735842199</v>
+        <v>-0.02868635876697057</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0828643696225817</v>
+        <v>0.08286453078544076</v>
       </c>
       <c r="H42" t="n">
-        <v>0.005637080795121374</v>
+        <v>0.005637081406470124</v>
       </c>
       <c r="I42" t="n">
-        <v>0.004665720597907042</v>
+        <v>0.004665800784880547</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.001914774929947183</v>
+        <v>-0.001914872985790073</v>
       </c>
       <c r="K42" t="n">
-        <v>0.03921576765490387</v>
+        <v>0.03921570327936719</v>
       </c>
       <c r="L42" t="n">
-        <v>0.07200405426580025</v>
+        <v>0.07200428918963309</v>
       </c>
       <c r="M42" t="n">
-        <v>0.03000203790965661</v>
+        <v>0.03000204244705573</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.02656912233463748</v>
+        <v>-0.02656923742123618</v>
       </c>
       <c r="O42" t="n">
         <v>0.0463720645925807</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.05634275622592255</v>
+        <v>-0.05634260086629639</v>
       </c>
       <c r="Q42" t="n">
         <v>79.44000244140625</v>
@@ -3581,49 +3581,49 @@
         <v>43312</v>
       </c>
       <c r="B43" t="n">
-        <v>0.03168117398756931</v>
+        <v>0.0316809247375418</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1368767813860126</v>
+        <v>0.1368767701625206</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.08669464055628229</v>
+        <v>-0.08669438238391769</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.03450903905396374</v>
+        <v>-0.03450903674751282</v>
       </c>
       <c r="F43" t="n">
-        <v>0.08812328588014195</v>
+        <v>0.08812339301247496</v>
       </c>
       <c r="G43" t="n">
         <v>-0.005486719302502663</v>
       </c>
       <c r="H43" t="n">
-        <v>0.07347346643504782</v>
+        <v>0.07347358220204736</v>
       </c>
       <c r="I43" t="n">
-        <v>0.02471929089635538</v>
+        <v>0.02471913200853204</v>
       </c>
       <c r="J43" t="n">
-        <v>0.05069890972288116</v>
+        <v>0.05069871285799388</v>
       </c>
       <c r="K43" t="n">
         <v>0.01163519517637113</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1047439518653119</v>
+        <v>0.1047437229132739</v>
       </c>
       <c r="M43" t="n">
-        <v>0.09130178402730116</v>
+        <v>0.0913018708488087</v>
       </c>
       <c r="N43" t="n">
-        <v>0.08458301111329569</v>
+        <v>0.08458302111336091</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0855056866618269</v>
+        <v>0.08550554577907521</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0764663933664731</v>
+        <v>0.07646648059921923</v>
       </c>
       <c r="Q43" t="n">
         <v>74.25</v>
@@ -3655,49 +3655,49 @@
         <v>43343</v>
       </c>
       <c r="B44" t="n">
-        <v>0.06934110735518839</v>
+        <v>0.06934136570376692</v>
       </c>
       <c r="C44" t="n">
-        <v>0.01406701219753637</v>
+        <v>0.01406693905812184</v>
       </c>
       <c r="D44" t="n">
-        <v>0.06911370254285187</v>
+        <v>0.06911369563104208</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03534547203547422</v>
+        <v>0.03534553881371272</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02128364182416953</v>
+        <v>0.02128355134172799</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1199187359839888</v>
+        <v>0.1199190123828051</v>
       </c>
       <c r="H44" t="n">
         <v>0.01305484445157057</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.09926929568061027</v>
+        <v>-0.09926900096281399</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07642148465732923</v>
+        <v>0.0764214989760934</v>
       </c>
       <c r="K44" t="n">
         <v>-0.004973462219340474</v>
       </c>
       <c r="L44" t="n">
-        <v>0.03741488625919787</v>
+        <v>0.03741508239250213</v>
       </c>
       <c r="M44" t="n">
-        <v>0.02024847824264731</v>
+        <v>0.02024854687820921</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.02793156632715521</v>
+        <v>-0.02793146036428173</v>
       </c>
       <c r="O44" t="n">
-        <v>0.02209407647914108</v>
+        <v>0.02209420913201088</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02173220712463797</v>
+        <v>0.02173204329115541</v>
       </c>
       <c r="Q44" t="n">
         <v>77.41999816894531</v>
@@ -3729,40 +3729,40 @@
         <v>43373</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.02130608037993553</v>
+        <v>-0.02130630630969865</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.01672787389599029</v>
+        <v>-0.01672780277165831</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.04157736582985794</v>
+        <v>-0.0415773619406542</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01726110238082068</v>
+        <v>-0.01726130065789966</v>
       </c>
       <c r="F45" t="n">
-        <v>0.004147392437308106</v>
+        <v>0.004147481401540976</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02255633530769208</v>
+        <v>0.02255620633948019</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.04086879015909828</v>
+        <v>-0.04086888932654786</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3329009087543684</v>
+        <v>0.3329005071606106</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.004846274980935705</v>
+        <v>-0.004846014729252945</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01437063233150959</v>
+        <v>-0.01437069154911474</v>
       </c>
       <c r="L45" t="n">
-        <v>0.01680340756339449</v>
+        <v>0.01680334322799015</v>
       </c>
       <c r="M45" t="n">
-        <v>0.01262974170019082</v>
+        <v>0.01262967576196572</v>
       </c>
       <c r="N45" t="n">
         <v>-0.002275878402715703</v>
@@ -3771,7 +3771,7 @@
         <v>0.03524446702710748</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.002539667583599248</v>
+        <v>-0.002539509159887987</v>
       </c>
       <c r="Q45" t="n">
         <v>82.72000122070312</v>
@@ -3803,49 +3803,49 @@
         <v>43404</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.1261238557718715</v>
+        <v>-0.1261237309884893</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.03029043536153497</v>
+        <v>-0.03029050550482304</v>
       </c>
       <c r="D46" t="n">
-        <v>0.02155080409624266</v>
+        <v>0.02155070439360784</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1155347764073482</v>
+        <v>-0.1155346481955757</v>
       </c>
       <c r="F46" t="n">
-        <v>0.01253407475482415</v>
+        <v>0.01253398652397264</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01140967547914462</v>
+        <v>0.01140955342304695</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1389635989447711</v>
+        <v>-0.1389634582231251</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.01522182337973499</v>
+        <v>-0.01522156704650846</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.03408799324283318</v>
+        <v>-0.03408816517276536</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.08145806991566729</v>
+        <v>-0.08145795464772876</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.04514305023240273</v>
+        <v>-0.04514316989892975</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1132293941447455</v>
+        <v>-0.1132293364019387</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.1616768240494334</v>
+        <v>-0.1616767116537773</v>
       </c>
       <c r="O46" t="n">
         <v>-0.0644575425643924</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.1292169523013167</v>
+        <v>-0.1292171010556902</v>
       </c>
       <c r="Q46" t="n">
         <v>75.47000122070312</v>
@@ -3877,49 +3877,49 @@
         <v>43434</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0002705058300522811</v>
+        <v>0.0002705939091627307</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1621737322669999</v>
+        <v>-0.1621738068608105</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.07287682634895298</v>
+        <v>-0.07287673080862278</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.01522508198121064</v>
+        <v>-0.01522508081004426</v>
       </c>
       <c r="F47" t="n">
-        <v>0.01702053091139</v>
+        <v>0.017020619533193</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.04838296010220766</v>
+        <v>-0.04838290044329552</v>
       </c>
       <c r="H47" t="n">
-        <v>0.01047695418310868</v>
+        <v>0.01047701359392228</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0690803399299682</v>
+        <v>0.06908039644327335</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01535238523285987</v>
+        <v>0.01535247716486299</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.06832301711802113</v>
+        <v>-0.06832301264907392</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0004220940596608713</v>
+        <v>0.0004220940867207812</v>
       </c>
       <c r="M47" t="n">
-        <v>0.007132725335369017</v>
+        <v>0.007132651905072063</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.02244881282269873</v>
+        <v>-0.02244887684892793</v>
       </c>
       <c r="O47" t="n">
-        <v>0.02620070790329443</v>
+        <v>0.02620064234940922</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.07456154768844614</v>
+        <v>-0.07456155449694446</v>
       </c>
       <c r="Q47" t="n">
         <v>58.70999908447266</v>
@@ -3954,46 +3954,46 @@
         <v>-0.07606931386687565</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.03140961588953273</v>
+        <v>-0.03140961868601122</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.06530730942030283</v>
+        <v>-0.06530740574066418</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.05668838592079917</v>
+        <v>-0.05668838149271294</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.06818817215679052</v>
+        <v>-0.06818808647646601</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02634342681024515</v>
+        <v>0.02634336246657965</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.09993378531707231</v>
+        <v>-0.09993377344147447</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2482700080944871</v>
+        <v>-0.2482702690899705</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.05793851418616669</v>
+        <v>-0.05793833584028196</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.06407386434081475</v>
+        <v>-0.06407407045977687</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.0917721707583139</v>
+        <v>-0.09177217663925963</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.01945150640957638</v>
+        <v>-0.01945128909702987</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.06437031775523538</v>
+        <v>-0.0643703819164404</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.065011816555545</v>
+        <v>-0.06501162906796198</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.08412340723056</v>
+        <v>-0.08412321818937996</v>
       </c>
       <c r="Q48" t="n">
         <v>53.79999923706055</v>
@@ -4028,46 +4028,46 @@
         <v>0.00937586436191129</v>
       </c>
       <c r="C49" t="n">
-        <v>0.07988402305750886</v>
+        <v>0.07988412232014941</v>
       </c>
       <c r="D49" t="n">
-        <v>0.06386346758018746</v>
+        <v>0.06386335732971604</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1187648017435834</v>
+        <v>0.118764709102082</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.01588228971186201</v>
+        <v>-0.01588247215195182</v>
       </c>
       <c r="G49" t="n">
-        <v>0.03131438721679247</v>
+        <v>0.0313141428847612</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08235297534863539</v>
+        <v>0.08235289846127025</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1156958419944172</v>
+        <v>0.115696187245889</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0572418848452998</v>
+        <v>0.05724177935135955</v>
       </c>
       <c r="K49" t="n">
-        <v>0.142065475954724</v>
+        <v>0.1420657223042938</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1010453190307303</v>
+        <v>0.1010453261602056</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.001017123877940396</v>
+        <v>-0.001017272439850725</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1294162631928943</v>
+        <v>0.1294161898995463</v>
       </c>
       <c r="O49" t="n">
-        <v>0.03716821257515335</v>
+        <v>0.03716820749634731</v>
       </c>
       <c r="P49" t="n">
-        <v>0.121604500686264</v>
+        <v>0.1216042721178228</v>
       </c>
       <c r="Q49" t="n">
         <v>61.88999938964844</v>
@@ -4099,49 +4099,49 @@
         <v>43524</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06182881541888929</v>
+        <v>0.06182890981316258</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.01367180218251052</v>
+        <v>-0.01367188730249824</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1355126278898606</v>
+        <v>0.1355127455655016</v>
       </c>
       <c r="E50" t="n">
         <v>0.06263283633039363</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1563157776714705</v>
+        <v>0.1563156054083079</v>
       </c>
       <c r="G50" t="n">
-        <v>0.05201584144060312</v>
+        <v>0.0520159722204947</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1000904626991406</v>
+        <v>0.1000905175860343</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.005832190100042101</v>
+        <v>-0.005832262378821507</v>
       </c>
       <c r="J50" t="n">
-        <v>0.03878098263432528</v>
+        <v>0.03878088962993731</v>
       </c>
       <c r="K50" t="n">
-        <v>0.05162854591616406</v>
+        <v>0.05162860820621962</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.008227874099094978</v>
+        <v>-0.008227874626353771</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07281064637979506</v>
+        <v>0.07281049751518931</v>
       </c>
       <c r="N50" t="n">
-        <v>0.02370766200377394</v>
+        <v>0.0237075986473827</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.1725988726802726</v>
+        <v>-0.1725990475613927</v>
       </c>
       <c r="P50" t="n">
-        <v>0.04575151596069116</v>
+        <v>0.04575161640855074</v>
       </c>
       <c r="Q50" t="n">
         <v>66.02999877929688</v>
@@ -4173,49 +4173,49 @@
         <v>43555</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.04620020021568394</v>
+        <v>-0.04620001831295051</v>
       </c>
       <c r="C51" t="n">
-        <v>0.05643544977417059</v>
+        <v>0.05643545464454247</v>
       </c>
       <c r="D51" t="n">
-        <v>0.05051042036953968</v>
+        <v>0.05051032910489006</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.002397762329958586</v>
+        <v>-0.002397553368565619</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.01685840763740365</v>
+        <v>-0.01685816931393336</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02240080026825741</v>
+        <v>0.02240091539024625</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.001646637018329566</v>
+        <v>-0.001646858605013679</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1088852824457041</v>
+        <v>0.1088854951185392</v>
       </c>
       <c r="J51" t="n">
         <v>0.01503045384665169</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.004942435682569357</v>
+        <v>-0.004942497521724931</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.08121366653556561</v>
+        <v>-0.0812137363967268</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.01533645453763344</v>
+        <v>-0.01533624852375293</v>
       </c>
       <c r="N51" t="n">
-        <v>0.03247820249654243</v>
+        <v>0.03247833339831008</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.1400861895665706</v>
+        <v>-0.140086121104559</v>
       </c>
       <c r="P51" t="n">
-        <v>0.05882364287469954</v>
+        <v>0.05882336732185789</v>
       </c>
       <c r="Q51" t="n">
         <v>68.38999938964844</v>
@@ -4247,49 +4247,49 @@
         <v>43585</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1246775961866198</v>
+        <v>0.1246775613253288</v>
       </c>
       <c r="C52" t="n">
-        <v>0.05629643547128804</v>
+        <v>0.05629644007012558</v>
       </c>
       <c r="D52" t="n">
-        <v>0.02684570172089273</v>
+        <v>0.02684587780613223</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1950030354772052</v>
+        <v>0.1950029248099712</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.02565478069569471</v>
+        <v>-0.02565453412891117</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1004446713665386</v>
+        <v>0.1004450017643241</v>
       </c>
       <c r="H52" t="n">
-        <v>0.06927060061213752</v>
+        <v>0.06927071937340123</v>
       </c>
       <c r="I52" t="n">
-        <v>0.06825812909904516</v>
+        <v>0.06825784563616755</v>
       </c>
       <c r="J52" t="n">
-        <v>0.08120365477626623</v>
+        <v>0.08120373968970429</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1841680893798645</v>
+        <v>0.1841680150534764</v>
       </c>
       <c r="L52" t="n">
-        <v>0.1259940526150525</v>
+        <v>0.1259942813111365</v>
       </c>
       <c r="M52" t="n">
-        <v>0.05657491104968138</v>
+        <v>0.05657490706334101</v>
       </c>
       <c r="N52" t="n">
         <v>0.1382772086736108</v>
       </c>
       <c r="O52" t="n">
-        <v>0.1728204862795319</v>
+        <v>0.1728206714491662</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1291902263683191</v>
+        <v>0.1291906937300014</v>
       </c>
       <c r="Q52" t="n">
         <v>72.80000305175781</v>
@@ -4321,22 +4321,22 @@
         <v>43616</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.1098567845675792</v>
+        <v>-0.1098569229987688</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1154718265200377</v>
+        <v>-0.1154717581142219</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.08588349610668033</v>
+        <v>-0.08588365805086906</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1331300168166446</v>
+        <v>-0.1331301765426123</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.03233275228185373</v>
+        <v>-0.03233308151161862</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.02680805180305279</v>
+        <v>-0.0268085441544692</v>
       </c>
       <c r="H53" t="n">
         <v>-0.148069622656032</v>
@@ -4345,25 +4345,25 @@
         <v>-0.1163950098566477</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.07489548818386227</v>
+        <v>-0.07489540376584924</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.1656703858112983</v>
+        <v>-0.1656703328063582</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.07018328064968149</v>
+        <v>-0.07018315135448461</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.09773276815367993</v>
+        <v>-0.09773269494765457</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.1607397219664298</v>
+        <v>-0.1607396140877476</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.1178187530713379</v>
+        <v>-0.1178188923536535</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.1266447290081514</v>
+        <v>-0.1266448631961802</v>
       </c>
       <c r="Q53" t="n">
         <v>64.48999786376953</v>
@@ -4395,49 +4395,49 @@
         <v>43646</v>
       </c>
       <c r="B54" t="n">
-        <v>0.06958029946291067</v>
+        <v>0.06958010678664306</v>
       </c>
       <c r="C54" t="n">
         <v>0.03924089921905871</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1333693862258822</v>
+        <v>0.1333694911238332</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1598278882666231</v>
+        <v>0.1598279664398408</v>
       </c>
       <c r="F54" t="n">
-        <v>0.08825589222536756</v>
+        <v>0.08825598709025151</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.03694818211023876</v>
+        <v>-0.03694808687255313</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1683660981330304</v>
+        <v>0.1683663419845134</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1645070390068279</v>
+        <v>0.1645068984487732</v>
       </c>
       <c r="J54" t="n">
-        <v>0.08725343004482844</v>
+        <v>0.08725324544179669</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1641079015979123</v>
+        <v>0.1641077005822267</v>
       </c>
       <c r="L54" t="n">
-        <v>0.01970107002709032</v>
+        <v>0.0197008645467327</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.01753629079943231</v>
+        <v>-0.01753643603115596</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1576272379250141</v>
+        <v>0.1576270891233991</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02612211324635338</v>
+        <v>0.02612193427628484</v>
       </c>
       <c r="P54" t="n">
-        <v>0.1099813288910649</v>
+        <v>0.1099812409276759</v>
       </c>
       <c r="Q54" t="n">
         <v>66.55000305175781</v>
@@ -4469,49 +4469,49 @@
         <v>43677</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.0196236132349541</v>
+        <v>-0.01962361494304754</v>
       </c>
       <c r="C55" t="n">
         <v>-0.1061204343118803</v>
       </c>
       <c r="D55" t="n">
-        <v>0.06193409244305137</v>
+        <v>0.06193417410580304</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0006737583500648903</v>
+        <v>0.0006739908007635798</v>
       </c>
       <c r="F55" t="n">
-        <v>0.08407834873240971</v>
+        <v>0.08407842883441496</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.03405235944692298</v>
+        <v>-0.03405225630074693</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.08844057419048101</v>
+        <v>-0.0884407644434092</v>
       </c>
       <c r="I55" t="n">
-        <v>0.01995634699971016</v>
+        <v>0.01995671151381506</v>
       </c>
       <c r="J55" t="n">
         <v>0.03250394018031333</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.1257327236039681</v>
+        <v>-0.1257326827534704</v>
       </c>
       <c r="L55" t="n">
-        <v>0.05982306150083128</v>
+        <v>0.05982299562844506</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.05093602398554176</v>
+        <v>-0.05093609921683473</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.06939969164847037</v>
+        <v>-0.06939974716729103</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.05199011177234369</v>
+        <v>-0.05198985921909427</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.0210385021437276</v>
+        <v>-0.02103826606807224</v>
       </c>
       <c r="Q55" t="n">
         <v>65.16999816894531</v>
@@ -4543,49 +4543,49 @@
         <v>43708</v>
       </c>
       <c r="B56" t="n">
-        <v>0.02522613547175045</v>
+        <v>0.02522613771145377</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.002208769987683712</v>
+        <v>-0.002208675869310284</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.08075370938775439</v>
+        <v>-0.08075370317779307</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01313112588811871</v>
+        <v>-0.01313135513196984</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05599656502501205</v>
+        <v>0.05599641310846892</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1015276121419225</v>
+        <v>-0.1015275015951893</v>
       </c>
       <c r="H56" t="n">
         <v>-0.07234039216207044</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1145500489395601</v>
+        <v>0.1145496668075308</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.0008684579607814991</v>
+        <v>-0.0008686848306771466</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.05631908689350762</v>
+        <v>-0.05631909040908656</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.07357800350226118</v>
+        <v>-0.07357800807543868</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.009403674051836508</v>
+        <v>-0.009403516259368305</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.003461364050316718</v>
+        <v>-0.003461304597668247</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.04614205026309015</v>
+        <v>-0.0461422299975871</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.06065855346260185</v>
+        <v>-0.06065862459259541</v>
       </c>
       <c r="Q56" t="n">
         <v>60.43000030517578</v>
@@ -4617,49 +4617,49 @@
         <v>43738</v>
       </c>
       <c r="B57" t="n">
-        <v>0.03209403491002139</v>
+        <v>0.03209421089026554</v>
       </c>
       <c r="C57" t="n">
-        <v>0.07526291214880976</v>
+        <v>0.07526262206937528</v>
       </c>
       <c r="D57" t="n">
-        <v>0.06930231721584423</v>
+        <v>0.06930239507382852</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03445943114963468</v>
+        <v>0.03445931345710518</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.001812327761165466</v>
+        <v>-0.001812257916628313</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02877342446223996</v>
+        <v>0.02877305180641776</v>
       </c>
       <c r="H57" t="n">
         <v>0.08853224428363982</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0152143850964177</v>
+        <v>0.01521449288934584</v>
       </c>
       <c r="J57" t="n">
-        <v>0.04541485687885372</v>
+        <v>0.04541509425822121</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0895203999460763</v>
+        <v>0.08952040586766308</v>
       </c>
       <c r="L57" t="n">
-        <v>0.07254632348970014</v>
+        <v>0.07254639544739794</v>
       </c>
       <c r="M57" t="n">
-        <v>0.06714518416612703</v>
+        <v>0.0671450187502205</v>
       </c>
       <c r="N57" t="n">
         <v>0.02747075977004121</v>
       </c>
       <c r="O57" t="n">
-        <v>0.1237112914893426</v>
+        <v>0.1237114962989423</v>
       </c>
       <c r="P57" t="n">
-        <v>0.02029521360504849</v>
+        <v>0.0202950394997532</v>
       </c>
       <c r="Q57" t="n">
         <v>60.77999877929688</v>
@@ -4691,22 +4691,22 @@
         <v>43769</v>
       </c>
       <c r="B58" t="n">
-        <v>0.04690354035132915</v>
+        <v>0.0469034525082721</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1482243805916585</v>
+        <v>0.1482245820461248</v>
       </c>
       <c r="D58" t="n">
-        <v>0.04518467463764098</v>
+        <v>0.04518451110026955</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1356306860406749</v>
+        <v>0.1356307014716525</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06830800164647077</v>
+        <v>0.06830814184323986</v>
       </c>
       <c r="G58" t="n">
-        <v>0.07246359651978973</v>
+        <v>0.07246409224208494</v>
       </c>
       <c r="H58" t="n">
         <v>0.03855857085572456</v>
@@ -4715,25 +4715,25 @@
         <v>0.05716832240685643</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02785293599980254</v>
+        <v>0.02785286359884998</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1108573718313579</v>
+        <v>0.1108575607004176</v>
       </c>
       <c r="L58" t="n">
-        <v>0.02254632095532783</v>
+        <v>0.0225463835078914</v>
       </c>
       <c r="M58" t="n">
-        <v>0.04860067028891235</v>
+        <v>0.04860067393330447</v>
       </c>
       <c r="N58" t="n">
-        <v>0.07283348379495158</v>
+        <v>0.07283336726342848</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.04693011131321301</v>
+        <v>-0.0469302789301087</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0444845385380237</v>
+        <v>0.0444847112232567</v>
       </c>
       <c r="Q58" t="n">
         <v>60.22999954223633</v>
@@ -4765,49 +4765,49 @@
         <v>43799</v>
       </c>
       <c r="B59" t="n">
-        <v>0.03712876524540287</v>
+        <v>0.03712868509713485</v>
       </c>
       <c r="C59" t="n">
-        <v>0.05602869644733177</v>
+        <v>0.0560286200473421</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.006986871779978254</v>
+        <v>-0.006986722076802176</v>
       </c>
       <c r="E59" t="n">
-        <v>0.02873056368019866</v>
+        <v>0.02873056655854134</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0143386638021229</v>
+        <v>-0.01433885876920304</v>
       </c>
       <c r="G59" t="n">
-        <v>0.02299680795353076</v>
+        <v>0.02299657979166514</v>
       </c>
       <c r="H59" t="n">
         <v>0.0983974289348748</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.06027731428800942</v>
+        <v>-0.06027751214916988</v>
       </c>
       <c r="J59" t="n">
-        <v>0.03180709119465064</v>
+        <v>0.03180744563023064</v>
       </c>
       <c r="K59" t="n">
-        <v>0.02230705260299781</v>
+        <v>0.02230694085655793</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.1124080740720939</v>
+        <v>-0.1124080671957181</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.02751906697059781</v>
+        <v>-0.02751906893851319</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0478372606822659</v>
+        <v>0.04783737449870351</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.07663835819700704</v>
+        <v>-0.07663827504989573</v>
       </c>
       <c r="P59" t="n">
-        <v>0.02527712790213132</v>
+        <v>0.02527704499143701</v>
       </c>
       <c r="Q59" t="n">
         <v>62.43000030517578</v>
@@ -4839,46 +4839,46 @@
         <v>43830</v>
       </c>
       <c r="B60" t="n">
-        <v>0.07446287041850508</v>
+        <v>0.07446295345192167</v>
       </c>
       <c r="C60" t="n">
-        <v>0.001273298560224845</v>
+        <v>0.001273298652343602</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.0369392602846268</v>
+        <v>-0.03693940547226382</v>
       </c>
       <c r="E60" t="n">
-        <v>0.06469081444230973</v>
+        <v>0.06469091812833372</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01314646908451822</v>
+        <v>0.01314660310130766</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.05492479593682109</v>
+        <v>-0.05492468692725694</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.03029186329544464</v>
+        <v>-0.03029176391269106</v>
       </c>
       <c r="I60" t="n">
-        <v>0.03051277270655728</v>
+        <v>0.03051288440748401</v>
       </c>
       <c r="J60" t="n">
-        <v>0.009877506036223282</v>
+        <v>0.009877366803757059</v>
       </c>
       <c r="K60" t="n">
         <v>0.04880841295619898</v>
       </c>
       <c r="L60" t="n">
-        <v>0.07257672391506809</v>
+        <v>0.07257664999248759</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07340412506907645</v>
+        <v>0.07340420400139891</v>
       </c>
       <c r="N60" t="n">
         <v>0.03553856475336659</v>
       </c>
       <c r="O60" t="n">
-        <v>0.1182839877527726</v>
+        <v>0.1182837927083824</v>
       </c>
       <c r="P60" t="n">
         <v>0.05977709401946685</v>
@@ -4913,49 +4913,49 @@
         <v>43861</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.001332812032722841</v>
+        <v>-0.001332740109349473</v>
       </c>
       <c r="C61" t="n">
-        <v>0.02161927120201956</v>
+        <v>0.02161941727313499</v>
       </c>
       <c r="D61" t="n">
         <v>0.04703196329162229</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.08458251564002806</v>
+        <v>-0.08458260710886667</v>
       </c>
       <c r="F61" t="n">
-        <v>0.000425452758941125</v>
+        <v>0.0004253870240005231</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.07111333393466457</v>
+        <v>-0.07111321038726459</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0003808427488400934</v>
+        <v>0.0003807402225346479</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1111402151309211</v>
+        <v>0.1111404308033299</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0332553005086218</v>
+        <v>0.03325516081271851</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.03558697927588816</v>
+        <v>-0.03558708122298593</v>
       </c>
       <c r="L61" t="n">
         <v>0.08128985379477394</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.06164515271381887</v>
+        <v>-0.06164522121977456</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.06705379513396958</v>
+        <v>-0.06705389523786742</v>
       </c>
       <c r="O61" t="n">
-        <v>0.06310499313288465</v>
+        <v>0.06310517855331765</v>
       </c>
       <c r="P61" t="n">
-        <v>0.05353726525712399</v>
+        <v>0.05353733968121177</v>
       </c>
       <c r="Q61" t="n">
         <v>58.15999984741211</v>
@@ -4987,49 +4987,49 @@
         <v>43890</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.07384339605859636</v>
+        <v>-0.07384346275979903</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1033195213554509</v>
+        <v>-0.1033195140481292</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.06279979484607967</v>
+        <v>-0.0627997200924284</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.008479540957902487</v>
+        <v>-0.00847954180518129</v>
       </c>
       <c r="F62" t="n">
         <v>-0.1045892839644083</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01214373151494219</v>
+        <v>0.01214354223601055</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.02399072064570273</v>
+        <v>-0.02399082309397049</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.180911862174019</v>
+        <v>-0.180911845540827</v>
       </c>
       <c r="J62" t="n">
         <v>-0.09636514242881988</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.1007663265375157</v>
+        <v>-0.100766442898392</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.03989925587645327</v>
+        <v>-0.03989907759772027</v>
       </c>
       <c r="M62" t="n">
-        <v>0.01901131745978435</v>
+        <v>0.01901153786709742</v>
       </c>
       <c r="N62" t="n">
-        <v>-0.04923614605024429</v>
+        <v>-0.04923593673583215</v>
       </c>
       <c r="O62" t="n">
         <v>-0.02360877962284358</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.09981849218104955</v>
+        <v>-0.09981848512966185</v>
       </c>
       <c r="Q62" t="n">
         <v>50.52000045776367</v>
@@ -5064,46 +5064,46 @@
         <v>-0.1541187020541799</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2029153064711077</v>
+        <v>-0.202915290466209</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.126570458451472</v>
+        <v>-0.1265706078813232</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.01533481243981216</v>
+        <v>-0.01533461243539946</v>
       </c>
       <c r="F63" t="n">
         <v>0.05720060094801438</v>
       </c>
       <c r="G63" t="n">
-        <v>0.05712041620818065</v>
+        <v>0.05712035136149951</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1728444868975579</v>
+        <v>-0.1728442951074379</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.261651998494083</v>
+        <v>-0.2616520813720365</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.04232129676254626</v>
+        <v>-0.04232136916369789</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.1082702761225778</v>
+        <v>-0.1082700664688537</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.265310648424559</v>
+        <v>-0.2653107848471826</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1382668045869034</v>
+        <v>-0.1382670713523623</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.1683603792793719</v>
+        <v>-0.1683605295618622</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.2341969153946887</v>
+        <v>-0.2341968313807514</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.196908587225445</v>
+        <v>-0.1969087287237515</v>
       </c>
       <c r="Q63" t="n">
         <v>22.73999977111816</v>
@@ -5138,46 +5138,46 @@
         <v>0.06959494343019523</v>
       </c>
       <c r="C64" t="n">
-        <v>0.06531216349429791</v>
+        <v>0.06531205807732854</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.05196283295523263</v>
+        <v>-0.05196265505789999</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02589003984161597</v>
+        <v>0.02588993484761959</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1718787043512053</v>
+        <v>0.1718788431153124</v>
       </c>
       <c r="G64" t="n">
-        <v>0.05964390434404665</v>
+        <v>0.05964402040038275</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1488209067133119</v>
+        <v>0.1488207609273255</v>
       </c>
       <c r="I64" t="n">
-        <v>0.06406246733823995</v>
+        <v>0.06406239132541658</v>
       </c>
       <c r="J64" t="n">
-        <v>0.07460069994124319</v>
+        <v>0.07460100798380931</v>
       </c>
       <c r="K64" t="n">
-        <v>0.07115033066949517</v>
+        <v>0.07115019884200091</v>
       </c>
       <c r="L64" t="n">
-        <v>0.1958915965424433</v>
+        <v>0.195891680790081</v>
       </c>
       <c r="M64" t="n">
-        <v>0.08611953087158364</v>
+        <v>0.08611979461120467</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1378932765447207</v>
+        <v>0.1378932180498726</v>
       </c>
       <c r="O64" t="n">
-        <v>0.04068570806689631</v>
+        <v>0.04068559389643145</v>
       </c>
       <c r="P64" t="n">
-        <v>0.05564855465844065</v>
+        <v>0.05564856009623131</v>
       </c>
       <c r="Q64" t="n">
         <v>25.27000045776367</v>
@@ -5209,49 +5209,49 @@
         <v>43982</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.00906674674733865</v>
+        <v>-0.009066660799279092</v>
       </c>
       <c r="C65" t="n">
-        <v>0.03487736030362298</v>
+        <v>0.03487726741622454</v>
       </c>
       <c r="D65" t="n">
-        <v>0.083214827380101</v>
+        <v>0.08321491569100536</v>
       </c>
       <c r="E65" t="n">
-        <v>0.08812280718031262</v>
+        <v>0.08812260765735203</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.02015751356346407</v>
+        <v>-0.02015768879405433</v>
       </c>
       <c r="G65" t="n">
-        <v>0.006345595885055566</v>
+        <v>0.006345485666170214</v>
       </c>
       <c r="H65" t="n">
         <v>0.06179429561037919</v>
       </c>
       <c r="I65" t="n">
-        <v>0.04368566256573936</v>
+        <v>0.04368595143222542</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01995107839227184</v>
+        <v>0.01995093347681465</v>
       </c>
       <c r="K65" t="n">
-        <v>0.03040326413709904</v>
+        <v>0.03040326787885839</v>
       </c>
       <c r="L65" t="n">
-        <v>0.01717722709550995</v>
+        <v>0.0171769440952203</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.01284607089795964</v>
+        <v>-0.01284599336699488</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1108967792177435</v>
+        <v>0.1108969117003245</v>
       </c>
       <c r="O65" t="n">
         <v>0.02288497560997205</v>
       </c>
       <c r="P65" t="n">
-        <v>0.05628205080735627</v>
+        <v>0.05628205601713354</v>
       </c>
       <c r="Q65" t="n">
         <v>35.33000183105469</v>
@@ -5283,49 +5283,49 @@
         <v>44012</v>
       </c>
       <c r="B66" t="n">
-        <v>0.124865615797745</v>
+        <v>0.1248655182331428</v>
       </c>
       <c r="C66" t="n">
-        <v>0.07635593750513303</v>
+        <v>0.07635603411552894</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.006554698460216279</v>
+        <v>-0.006554875147818384</v>
       </c>
       <c r="E66" t="n">
-        <v>0.06879739739937962</v>
+        <v>0.06879731833216862</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.04192797201990139</v>
+        <v>-0.04192791412952046</v>
       </c>
       <c r="G66" t="n">
-        <v>0.006071918126892006</v>
+        <v>0.006071809293601182</v>
       </c>
       <c r="H66" t="n">
-        <v>0.05181744469766048</v>
+        <v>0.05181754873057987</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.05029886395557237</v>
+        <v>-0.05029912741243237</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.001092582804360753</v>
+        <v>-0.001092720681363235</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1167414010205516</v>
+        <v>0.1167415344037153</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.01248172717001783</v>
+        <v>-0.0124815912475732</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.007852934833846636</v>
+        <v>-0.007852856072199432</v>
       </c>
       <c r="N66" t="n">
         <v>0.002025415654647755</v>
       </c>
       <c r="O66" t="n">
-        <v>0.01186420432897117</v>
+        <v>0.01186430738842503</v>
       </c>
       <c r="P66" t="n">
-        <v>0.09493440820864874</v>
+        <v>0.09493441652806722</v>
       </c>
       <c r="Q66" t="n">
         <v>41.15000152587891</v>
@@ -5360,46 +5360,46 @@
         <v>0.04545459452232281</v>
       </c>
       <c r="C67" t="n">
-        <v>0.01320949974566155</v>
+        <v>0.01320941635604034</v>
       </c>
       <c r="D67" t="n">
         <v>0.01161257832090157</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.01951347932179037</v>
+        <v>-0.01951322700126634</v>
       </c>
       <c r="F67" t="n">
-        <v>0.007157477690431957</v>
+        <v>0.007157414622286362</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1699165397035705</v>
+        <v>0.169916558084541</v>
       </c>
       <c r="H67" t="n">
-        <v>0.04558827325724746</v>
+        <v>0.04558816984045189</v>
       </c>
       <c r="I67" t="n">
-        <v>0.006296303183120688</v>
+        <v>0.006296375708326973</v>
       </c>
       <c r="J67" t="n">
-        <v>0.05064046424240654</v>
+        <v>0.05064060584248664</v>
       </c>
       <c r="K67" t="n">
         <v>-0.06605405738407133</v>
       </c>
       <c r="L67" t="n">
-        <v>0.04882286199046937</v>
+        <v>0.04882272514800756</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.06399804543641285</v>
+        <v>-0.0639983430606873</v>
       </c>
       <c r="N67" t="n">
         <v>-0.06757151709579357</v>
       </c>
       <c r="O67" t="n">
-        <v>0.1891122833716821</v>
+        <v>0.1891122641103951</v>
       </c>
       <c r="P67" t="n">
-        <v>0.03426988423224375</v>
+        <v>0.03426996701027663</v>
       </c>
       <c r="Q67" t="n">
         <v>43.29999923706055</v>
@@ -5434,46 +5434,46 @@
         <v>0.007780240671256156</v>
       </c>
       <c r="C68" t="n">
-        <v>0.02076268525560709</v>
+        <v>0.02076285156933499</v>
       </c>
       <c r="D68" t="n">
-        <v>0.04356885887801476</v>
+        <v>0.04356903584979244</v>
       </c>
       <c r="E68" t="n">
-        <v>0.03360025014538293</v>
+        <v>0.03360033763327586</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.01860150502027225</v>
+        <v>-0.01860138094520059</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.005456365672108943</v>
+        <v>-0.005456181246411229</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1012658179951731</v>
+        <v>0.10126600718584</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01509007563694942</v>
+        <v>0.01509014725742297</v>
       </c>
       <c r="J68" t="n">
-        <v>0.06736382512115435</v>
+        <v>0.06736368924704617</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0442805843673455</v>
+        <v>0.04428046984928402</v>
       </c>
       <c r="L68" t="n">
-        <v>0.01299610624345116</v>
+        <v>0.01299617571912304</v>
       </c>
       <c r="M68" t="n">
-        <v>0.05122013173524897</v>
+        <v>0.05122030301514635</v>
       </c>
       <c r="N68" t="n">
-        <v>0.06906177900745458</v>
+        <v>0.06906166410824421</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0326807428858733</v>
+        <v>0.03268065443364465</v>
       </c>
       <c r="P68" t="n">
-        <v>0.09542762907671731</v>
+        <v>0.09542770646002841</v>
       </c>
       <c r="Q68" t="n">
         <v>45.27999877929688</v>
@@ -5505,49 +5505,49 @@
         <v>44104</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0408719453732187</v>
+        <v>0.04087187218856592</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.05960243755734695</v>
+        <v>-0.05960251338007794</v>
       </c>
       <c r="D69" t="n">
-        <v>0.05050018997561301</v>
+        <v>0.05050009662002863</v>
       </c>
       <c r="E69" t="n">
-        <v>0.07226806297400024</v>
+        <v>0.07226797221312298</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02049699281515749</v>
+        <v>0.02049692770046518</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0196510169645796</v>
+        <v>-0.01965101513757772</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0820561178271999</v>
+        <v>0.08205593193667271</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1221899837178424</v>
+        <v>0.1221901162081858</v>
       </c>
       <c r="J69" t="n">
-        <v>0.06456293031978322</v>
+        <v>0.0645627495690182</v>
       </c>
       <c r="K69" t="n">
-        <v>0.03592444540557227</v>
+        <v>0.03592466866946342</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.07114519228020899</v>
+        <v>-0.07114506965151168</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.1344518597704294</v>
+        <v>-0.1344519285234227</v>
       </c>
       <c r="N69" t="n">
-        <v>0.07589788167763367</v>
+        <v>0.07589788983488677</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.04010356853091901</v>
+        <v>-0.04010365147333095</v>
       </c>
       <c r="P69" t="n">
-        <v>0.04688459849571891</v>
+        <v>0.04688452454159453</v>
       </c>
       <c r="Q69" t="n">
         <v>40.95000076293945</v>
@@ -5579,49 +5579,49 @@
         <v>44135</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.0558464786609203</v>
+        <v>-0.05584641227662313</v>
       </c>
       <c r="C70" t="n">
         <v>-0.09205249329609766</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.09090902486916219</v>
+        <v>-0.09090917896232198</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.08372206218203837</v>
+        <v>-0.0837219043039078</v>
       </c>
       <c r="F70" t="n">
         <v>-0.07699336494360787</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0179431642056247</v>
+        <v>0.01794306766795795</v>
       </c>
       <c r="H70" t="n">
         <v>-0.04042486442169291</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.06558948366187145</v>
+        <v>-0.06558984853008865</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.08960841971023259</v>
+        <v>-0.08960803555511954</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.09891972779782754</v>
+        <v>-0.09891992904468727</v>
       </c>
       <c r="L70" t="n">
         <v>-0.04193875752596776</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.04248547367319788</v>
+        <v>-0.04248538190141049</v>
       </c>
       <c r="N70" t="n">
-        <v>-0.01884766471765109</v>
+        <v>-0.01884746681067517</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.008810730657189958</v>
+        <v>-0.00881064501082951</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0005776151458247725</v>
+        <v>0.000577750102634722</v>
       </c>
       <c r="Q70" t="n">
         <v>37.45999908447266</v>
@@ -5656,46 +5656,46 @@
         <v>0.04436232082104419</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1983381989033699</v>
+        <v>0.1983381044721222</v>
       </c>
       <c r="D71" t="n">
-        <v>0.07795765729795034</v>
+        <v>0.07795775300659469</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1088926140961013</v>
+        <v>0.1088925091816348</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.001318779163289263</v>
+        <v>-0.001318711422424013</v>
       </c>
       <c r="G71" t="n">
-        <v>0.05610403998837676</v>
+        <v>0.0561038536596683</v>
       </c>
       <c r="H71" t="n">
         <v>0.09440349903333156</v>
       </c>
       <c r="I71" t="n">
-        <v>0.255878173058814</v>
+        <v>0.2558782919969318</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1107784741199984</v>
+        <v>0.1107782624026734</v>
       </c>
       <c r="K71" t="n">
-        <v>0.2135645863481728</v>
+        <v>0.2135648463985396</v>
       </c>
       <c r="L71" t="n">
-        <v>0.1882044466836208</v>
+        <v>0.1882043725059617</v>
       </c>
       <c r="M71" t="n">
-        <v>0.2077095182816211</v>
+        <v>0.2077094025302173</v>
       </c>
       <c r="N71" t="n">
-        <v>0.1591657538208946</v>
+        <v>0.1591657376156224</v>
       </c>
       <c r="O71" t="n">
         <v>0.1126880816801905</v>
       </c>
       <c r="P71" t="n">
-        <v>0.1250363835837269</v>
+        <v>0.1250358946428669</v>
       </c>
       <c r="Q71" t="n">
         <v>47.59000015258789</v>
@@ -5730,46 +5730,46 @@
         <v>0.01327434006936978</v>
       </c>
       <c r="C72" t="n">
-        <v>0.04623209031320585</v>
+        <v>0.04623217275821956</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.007839344222057343</v>
+        <v>-0.007839426588009402</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.02568258279286373</v>
+        <v>-0.02568258079753749</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.08836798219047159</v>
+        <v>-0.08836797619644365</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.06876501642036414</v>
+        <v>-0.06876485212230643</v>
       </c>
       <c r="H72" t="n">
         <v>0.05430351731201277</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.05286356310395701</v>
+        <v>-0.05286335445923007</v>
       </c>
       <c r="J72" t="n">
         <v>0.009434112273817963</v>
       </c>
       <c r="K72" t="n">
-        <v>0.04652971262070627</v>
+        <v>0.04652970811635071</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.06794621921345256</v>
+        <v>-0.06794622345522405</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.05166474933051957</v>
+        <v>-0.05166482869045941</v>
       </c>
       <c r="N72" t="n">
-        <v>0.01041663830369921</v>
+        <v>0.0104166373887673</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.07151144014753053</v>
+        <v>-0.07151136180055151</v>
       </c>
       <c r="P72" t="n">
-        <v>-0.005133444869582338</v>
+        <v>-0.005133446408185027</v>
       </c>
       <c r="Q72" t="n">
         <v>51.79999923706055</v>
@@ -5801,49 +5801,49 @@
         <v>44227</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0777292513729464</v>
+        <v>0.07772932174526437</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.02960679829126833</v>
+        <v>-0.02960687361091741</v>
       </c>
       <c r="D73" t="n">
-        <v>0.02271612206849172</v>
+        <v>0.02271628998782238</v>
       </c>
       <c r="E73" t="n">
-        <v>0.08145334280535077</v>
+        <v>0.08145325657055369</v>
       </c>
       <c r="F73" t="n">
-        <v>0.03802508800295246</v>
+        <v>0.03802493636295123</v>
       </c>
       <c r="G73" t="n">
-        <v>0.08203623031278906</v>
+        <v>0.08203613558360612</v>
       </c>
       <c r="H73" t="n">
         <v>-0.02373963384665356</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0406977375639328</v>
+        <v>0.04069761982421261</v>
       </c>
       <c r="J73" t="n">
-        <v>0.02536728058019655</v>
+        <v>0.02536716725347254</v>
       </c>
       <c r="K73" t="n">
-        <v>0.03725783227662216</v>
+        <v>0.03725782883020146</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08118340200615237</v>
+        <v>0.08118347442312679</v>
       </c>
       <c r="M73" t="n">
-        <v>0.01452777695489083</v>
+        <v>0.01452794553748493</v>
       </c>
       <c r="N73" t="n">
-        <v>0.07497662065904453</v>
+        <v>0.07497652721326364</v>
       </c>
       <c r="O73" t="n">
-        <v>0.09478228004922129</v>
+        <v>0.09478218767018642</v>
       </c>
       <c r="P73" t="n">
-        <v>0.06707937133616992</v>
+        <v>0.0670796928128583</v>
       </c>
       <c r="Q73" t="n">
         <v>55.88000106811523</v>
@@ -5875,46 +5875,46 @@
         <v>44255</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.01985415819440128</v>
+        <v>-0.01985422219482658</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1898906724219644</v>
+        <v>0.189890842396166</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0222115615255456</v>
+        <v>0.02221131620413863</v>
       </c>
       <c r="E74" t="n">
-        <v>0.05862992596603722</v>
+        <v>0.0586298522321711</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.05426185168988218</v>
+        <v>-0.05426171221986298</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.002366399335622216</v>
+        <v>-0.002366136901335025</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.03879783154459848</v>
+        <v>-0.03879790498583757</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1117318393241475</v>
+        <v>0.1117317306130632</v>
       </c>
       <c r="J74" t="n">
-        <v>0.01692693740836249</v>
+        <v>0.01692693927917954</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0857280575456163</v>
+        <v>0.08572796072116073</v>
       </c>
       <c r="L74" t="n">
         <v>0.06370403392037405</v>
       </c>
       <c r="M74" t="n">
-        <v>0.0622912611493045</v>
+        <v>0.06229109104102215</v>
       </c>
       <c r="N74" t="n">
         <v>0.003051529411726595</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.03437179075713392</v>
+        <v>-0.03437171368135206</v>
       </c>
       <c r="P74" t="n">
         <v>0.04593802149745407</v>
@@ -5949,49 +5949,49 @@
         <v>44286</v>
       </c>
       <c r="B75" t="n">
-        <v>0.09969437630007993</v>
+        <v>0.09969430968056203</v>
       </c>
       <c r="C75" t="n">
-        <v>0.01033296860553401</v>
+        <v>0.01033283746967983</v>
       </c>
       <c r="D75" t="n">
-        <v>0.185639942990677</v>
+        <v>0.1856401312917166</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1026755108586521</v>
+        <v>0.1026757269608713</v>
       </c>
       <c r="F75" t="n">
-        <v>0.07759570511884273</v>
+        <v>0.07759569923768028</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1058329129146733</v>
+        <v>0.1058326310756044</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1449687974765366</v>
+        <v>0.144968808552967</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0113065286094014</v>
+        <v>-0.01130652971501434</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1145966232726543</v>
+        <v>0.1145967444107936</v>
       </c>
       <c r="K75" t="n">
-        <v>0.05249236837317506</v>
+        <v>0.05249228623539137</v>
       </c>
       <c r="L75" t="n">
         <v>0.1372260743402349</v>
       </c>
       <c r="M75" t="n">
-        <v>0.1126814873436397</v>
+        <v>0.1126814960931648</v>
       </c>
       <c r="N75" t="n">
         <v>0.1079361212203103</v>
       </c>
       <c r="O75" t="n">
-        <v>0.05923511066469045</v>
+        <v>0.05923502611727671</v>
       </c>
       <c r="P75" t="n">
-        <v>0.02126675423891511</v>
+        <v>0.02126664626721309</v>
       </c>
       <c r="Q75" t="n">
         <v>63.54000091552734</v>
@@ -6023,40 +6023,40 @@
         <v>44316</v>
       </c>
       <c r="B76" t="n">
-        <v>0.03355951897033327</v>
+        <v>0.03355970274346975</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1050470799093008</v>
+        <v>0.1050471512553233</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.03095146226956269</v>
+        <v>-0.03095139529390156</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.02845548868298431</v>
+        <v>-0.02845573774737309</v>
       </c>
       <c r="F76" t="n">
-        <v>0.02434579579921747</v>
+        <v>0.02434565341746109</v>
       </c>
       <c r="G76" t="n">
-        <v>0.003375023429947444</v>
+        <v>0.003375182410389144</v>
       </c>
       <c r="H76" t="n">
-        <v>0.003007393461983865</v>
+        <v>0.003007393662671998</v>
       </c>
       <c r="I76" t="n">
-        <v>0.06124516670449731</v>
+        <v>0.06124546947270715</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03230887936917815</v>
+        <v>0.03230907438749386</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.09549013863397593</v>
+        <v>-0.09549006804492144</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02066691480716631</v>
+        <v>0.0206670172316985</v>
       </c>
       <c r="M76" t="n">
-        <v>0.03499883668688986</v>
+        <v>0.03499897869894686</v>
       </c>
       <c r="N76" t="n">
         <v>-0.1192585982817371</v>
@@ -6065,7 +6065,7 @@
         <v>-0.03352820044533666</v>
       </c>
       <c r="P76" t="n">
-        <v>0.004613870982884238</v>
+        <v>0.004613977193999474</v>
       </c>
       <c r="Q76" t="n">
         <v>67.25</v>
@@ -6097,40 +6097,40 @@
         <v>44347</v>
       </c>
       <c r="B77" t="n">
-        <v>0.03210515642052725</v>
+        <v>0.03210480097897772</v>
       </c>
       <c r="C77" t="n">
         <v>0.0925279341849079</v>
       </c>
       <c r="D77" t="n">
-        <v>0.05636130819791485</v>
+        <v>0.05636130430251085</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.01988302922539975</v>
+        <v>-0.0198829667959487</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0623744066997558</v>
+        <v>0.06237434231951888</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.051578291675907</v>
+        <v>-0.05157836668597771</v>
       </c>
       <c r="H77" t="n">
-        <v>0.02477075066652934</v>
+        <v>0.02477088537762095</v>
       </c>
       <c r="I77" t="n">
-        <v>0.01460732504163986</v>
+        <v>0.01460694953578234</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0808450985468776</v>
+        <v>0.08084489435939557</v>
       </c>
       <c r="K77" t="n">
         <v>0.04443374187543281</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.02393000425586878</v>
+        <v>-0.02393010220506364</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.05296404823128298</v>
+        <v>-0.05296397723515311</v>
       </c>
       <c r="N77" t="n">
         <v>0.02424511408819097</v>
@@ -6139,7 +6139,7 @@
         <v>0.002285840730458455</v>
       </c>
       <c r="P77" t="n">
-        <v>0.04955277636671496</v>
+        <v>0.04955288160447169</v>
       </c>
       <c r="Q77" t="n">
         <v>69.62999725341797</v>
@@ -6171,31 +6171,31 @@
         <v>44377</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02615759113280136</v>
+        <v>0.02615771065428407</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.03387663831366994</v>
+        <v>-0.03387674526978557</v>
       </c>
       <c r="D78" t="n">
-        <v>0.01137708762154754</v>
+        <v>0.01137702144988073</v>
       </c>
       <c r="E78" t="n">
-        <v>0.04216391545260434</v>
+        <v>0.04216398458324133</v>
       </c>
       <c r="F78" t="n">
-        <v>0.08076873186232914</v>
+        <v>0.08076887156615853</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.02182621550843367</v>
+        <v>-0.02182613211792217</v>
       </c>
       <c r="H78" t="n">
-        <v>0.07275814081674192</v>
+        <v>0.07275800624640238</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.04177477125121964</v>
+        <v>-0.04177468707150067</v>
       </c>
       <c r="J78" t="n">
-        <v>0.02948837418230466</v>
+        <v>0.02948846157442686</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6204,16 +6204,16 @@
         <v>0.04243292028385248</v>
       </c>
       <c r="M78" t="n">
-        <v>0.03850314422243528</v>
+        <v>0.03850285395653796</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.02679767969618008</v>
+        <v>-0.02679776035863168</v>
       </c>
       <c r="O78" t="n">
         <v>0.06815137853229092</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.007756018705409096</v>
+        <v>-0.007756017927719738</v>
       </c>
       <c r="Q78" t="n">
         <v>75.12999725341797</v>
@@ -6245,49 +6245,49 @@
         <v>44408</v>
       </c>
       <c r="B79" t="n">
-        <v>0.08129528509284079</v>
+        <v>0.0812952940909526</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1888851802218448</v>
+        <v>0.1888852011326603</v>
       </c>
       <c r="D79" t="n">
-        <v>0.07098531125798768</v>
+        <v>0.07098537594928822</v>
       </c>
       <c r="E79" t="n">
-        <v>0.110686919165826</v>
+        <v>0.1106871737658597</v>
       </c>
       <c r="F79" t="n">
         <v>-0.04013595532199443</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.08079207252287435</v>
+        <v>-0.08079198038403623</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1238169625822383</v>
+        <v>0.1238170305956463</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1127094137589018</v>
+        <v>-0.1127092328459693</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08136879934431818</v>
+        <v>0.08136879243701212</v>
       </c>
       <c r="K79" t="n">
         <v>0.02607510026724169</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0542739177856677</v>
+        <v>0.05427401641154295</v>
       </c>
       <c r="M79" t="n">
-        <v>0.005592199618169369</v>
+        <v>0.005592406053624988</v>
       </c>
       <c r="N79" t="n">
-        <v>0.05002295045172356</v>
+        <v>0.05002303748134818</v>
       </c>
       <c r="O79" t="n">
         <v>0.05350397757111769</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.01529870330926053</v>
+        <v>-0.01529870176328219</v>
       </c>
       <c r="Q79" t="n">
         <v>76.33000183105469</v>
@@ -6319,40 +6319,40 @@
         <v>44439</v>
       </c>
       <c r="B80" t="n">
-        <v>0.01847718105450968</v>
+        <v>0.01847718294588363</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.02615467347048051</v>
+        <v>-0.0261545827880505</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.001086659625225028</v>
+        <v>-0.001086599156053913</v>
       </c>
       <c r="E80" t="n">
-        <v>0.01786954775124916</v>
+        <v>0.01786908520007602</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02325084861750293</v>
+        <v>0.02325072401321493</v>
       </c>
       <c r="G80" t="n">
-        <v>0.03469218146742326</v>
+        <v>0.03469198954401853</v>
       </c>
       <c r="H80" t="n">
-        <v>0.04912288789030184</v>
+        <v>0.04912278018592797</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.03975130317353137</v>
+        <v>-0.03975119084389567</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.03234874874378246</v>
+        <v>-0.03234882470568479</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.01917083715991408</v>
+        <v>-0.01917075664975654</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.00557690127289745</v>
+        <v>-0.005577087848418261</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.000411981369961123</v>
+        <v>-0.0004119813418742568</v>
       </c>
       <c r="N80" t="n">
         <v>-0.03846154149749914</v>
@@ -6361,7 +6361,7 @@
         <v>-0.006795398963452604</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.0375339181539206</v>
+        <v>-0.03753391430208119</v>
       </c>
       <c r="Q80" t="n">
         <v>72.98999786376953</v>
@@ -6393,49 +6393,49 @@
         <v>44469</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.07944949451701622</v>
+        <v>-0.07944940199650419</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.06114294259871533</v>
+        <v>-0.06114275136118097</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.07287892629838966</v>
+        <v>-0.07287897795376208</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.1016206077200129</v>
+        <v>-0.1016202928003401</v>
       </c>
       <c r="F81" t="n">
-        <v>0.04534648578754252</v>
+        <v>0.04534673485547525</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.02139586888465694</v>
+        <v>-0.02139568961545502</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.09063549840649054</v>
+        <v>-0.09063550771125428</v>
       </c>
       <c r="I81" t="n">
-        <v>0.03122126138378278</v>
+        <v>0.03122102934373072</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.08362398622356815</v>
+        <v>-0.08362406734920913</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.08545446008742252</v>
+        <v>-0.0854544530729987</v>
       </c>
       <c r="L81" t="n">
-        <v>0.06902484503076334</v>
+        <v>0.06902513374396935</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01298170466214388</v>
+        <v>0.01298170377675167</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.05636364099066127</v>
+        <v>-0.05636355889828415</v>
       </c>
       <c r="O81" t="n">
-        <v>0.06409804705487998</v>
+        <v>0.06409797745201162</v>
       </c>
       <c r="P81" t="n">
-        <v>0.009839138120588009</v>
+        <v>0.009839137071490311</v>
       </c>
       <c r="Q81" t="n">
         <v>78.51999664306641</v>
@@ -6467,49 +6467,49 @@
         <v>44500</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.03533804393705386</v>
+        <v>-0.03533815311696642</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1189897535868354</v>
+        <v>0.1189896275036906</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.01642533326628448</v>
+        <v>-0.01642539741757654</v>
       </c>
       <c r="E82" t="n">
-        <v>0.04386582150001006</v>
+        <v>0.04386562799402594</v>
       </c>
       <c r="F82" t="n">
-        <v>0.01117633415727082</v>
+        <v>0.01117609987430668</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.05146319670663391</v>
+        <v>-0.05146318727916033</v>
       </c>
       <c r="H82" t="n">
-        <v>0.01507907343779369</v>
+        <v>0.01507907514012352</v>
       </c>
       <c r="I82" t="n">
         <v>-0.06073530249276493</v>
       </c>
       <c r="J82" t="n">
-        <v>0.04631488815762164</v>
+        <v>0.04631489225782204</v>
       </c>
       <c r="K82" t="n">
-        <v>0.08101395022551494</v>
+        <v>0.08101385320060928</v>
       </c>
       <c r="L82" t="n">
-        <v>0.08353529134929771</v>
+        <v>0.08353501264987351</v>
       </c>
       <c r="M82" t="n">
-        <v>0.04404638027367236</v>
+        <v>0.04404637730807259</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.04142582248633753</v>
+        <v>-0.04142590587823447</v>
       </c>
       <c r="O82" t="n">
-        <v>0.09138511662802551</v>
+        <v>0.09138518801575124</v>
       </c>
       <c r="P82" t="n">
-        <v>0.01451344084460415</v>
+        <v>0.01451333372611363</v>
       </c>
       <c r="Q82" t="n">
         <v>84.37999725341797</v>
@@ -6541,49 +6541,49 @@
         <v>44530</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1000352440816765</v>
+        <v>0.1000352554036121</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.0478652024504409</v>
+        <v>-0.04786528910989585</v>
       </c>
       <c r="D83" t="n">
-        <v>0.01645918369918209</v>
+        <v>0.01645911738738959</v>
       </c>
       <c r="E83" t="n">
-        <v>0.005799157109519282</v>
+        <v>0.005799277529263014</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.06219549692287085</v>
+        <v>-0.06219544648648145</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.0302126963082201</v>
+        <v>-0.03021269047331421</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.04347829955355487</v>
+        <v>-0.04347830438905842</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.006334446803958338</v>
+        <v>-0.006334562959875778</v>
       </c>
       <c r="J83" t="n">
-        <v>0.06599458072540432</v>
+        <v>0.06599484013942392</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0317240492922839</v>
+        <v>0.03172413231953741</v>
       </c>
       <c r="L83" t="n">
-        <v>0.01032118678907579</v>
+        <v>0.01032143127182183</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.02542196302988053</v>
+        <v>-0.02542215485606414</v>
       </c>
       <c r="N83" t="n">
-        <v>0.04170854649884292</v>
+        <v>0.04170863725423546</v>
       </c>
       <c r="O83" t="n">
         <v>-0.02094083975882166</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.02250894815901205</v>
+        <v>-0.02250905223460176</v>
       </c>
       <c r="Q83" t="n">
         <v>70.56999969482422</v>
@@ -6615,49 +6615,49 @@
         <v>44561</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1059877214516549</v>
+        <v>0.1059879381306787</v>
       </c>
       <c r="C84" t="n">
         <v>0.0408454682715198</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0882583749481276</v>
+        <v>0.08825857642002655</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1275675051031657</v>
+        <v>0.1275674377990712</v>
       </c>
       <c r="F84" t="n">
-        <v>0.06152624052210354</v>
+        <v>0.06152618287950307</v>
       </c>
       <c r="G84" t="n">
-        <v>0.09466873683842625</v>
+        <v>0.0946686184135388</v>
       </c>
       <c r="H84" t="n">
-        <v>0.08825759777874409</v>
+        <v>0.08825772431239476</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1129996502459967</v>
+        <v>0.1130000141444649</v>
       </c>
       <c r="J84" t="n">
-        <v>0.08478233434479643</v>
+        <v>0.08478192402645557</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1256685602265513</v>
+        <v>0.1256683891649113</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.04441907131506184</v>
+        <v>-0.04441914455894236</v>
       </c>
       <c r="M84" t="n">
-        <v>0.02107676717868245</v>
+        <v>0.02107696848023011</v>
       </c>
       <c r="N84" t="n">
-        <v>0.03473236221707232</v>
+        <v>0.0347322720694645</v>
       </c>
       <c r="O84" t="n">
         <v>-0.001316124545784003</v>
       </c>
       <c r="P84" t="n">
-        <v>0.07281737915355913</v>
+        <v>0.07281738690658401</v>
       </c>
       <c r="Q84" t="n">
         <v>77.77999877929688</v>
@@ -6689,40 +6689,40 @@
         <v>44592</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.07701195382940607</v>
+        <v>-0.07701222574723521</v>
       </c>
       <c r="C85" t="n">
         <v>-0.1451699810726514</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.08399709855617199</v>
+        <v>-0.08399714843257311</v>
       </c>
       <c r="E85" t="n">
         <v>-0.1319909588446175</v>
       </c>
       <c r="F85" t="n">
-        <v>0.01750094459112361</v>
+        <v>0.01750106233966542</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1504159373868104</v>
+        <v>0.1504157417828338</v>
       </c>
       <c r="H85" t="n">
         <v>-0.1353985847476651</v>
       </c>
       <c r="I85" t="n">
-        <v>0.02953740627936519</v>
+        <v>0.02953719001841248</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.1203074542285018</v>
+        <v>-0.1203073342995485</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.04077601480533677</v>
+        <v>-0.04077601772042294</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.05125144174201379</v>
+        <v>-0.05125152155241675</v>
       </c>
       <c r="M85" t="n">
-        <v>0.008992451077034058</v>
+        <v>0.008992320884581018</v>
       </c>
       <c r="N85" t="n">
         <v>-0.05454553874275747</v>
@@ -6731,7 +6731,7 @@
         <v>-0.003075453864514244</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.006677725248302013</v>
+        <v>-0.006677725911035437</v>
       </c>
       <c r="Q85" t="n">
         <v>91.20999908447266</v>
@@ -6763,40 +6763,40 @@
         <v>44620</v>
       </c>
       <c r="B86" t="n">
-        <v>0.005018603696711255</v>
+        <v>0.00501880628707907</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.004815425175259014</v>
+        <v>-0.004815532612067019</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.005533513545174396</v>
+        <v>-0.005533709515982976</v>
       </c>
       <c r="E86" t="n">
         <v>-0.0898380997162308</v>
       </c>
       <c r="F86" t="n">
-        <v>0.06201464514902177</v>
+        <v>0.06201453141619218</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.2343205728503032</v>
+        <v>-0.2343204332416778</v>
       </c>
       <c r="H86" t="n">
         <v>0.03663458441985656</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1247953324474352</v>
+        <v>-0.1247952304324558</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.03119533314302858</v>
+        <v>-0.03119541891284605</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.1460998451506486</v>
+        <v>-0.1460997069809137</v>
       </c>
       <c r="L86" t="n">
         <v>-0.08123963272400858</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.08041314848290315</v>
+        <v>-0.08041308942032555</v>
       </c>
       <c r="N86" t="n">
         <v>-0.1331360174761232</v>
@@ -6805,7 +6805,7 @@
         <v>-0.1543460636100247</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.117502973148198</v>
+        <v>-0.1175030848007993</v>
       </c>
       <c r="Q86" t="n">
         <v>100.9899978637695</v>
@@ -6837,34 +6837,34 @@
         <v>44651</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.04332347153786742</v>
+        <v>-0.04332337125182162</v>
       </c>
       <c r="C87" t="n">
-        <v>0.04935476460265042</v>
+        <v>0.0493548778875037</v>
       </c>
       <c r="D87" t="n">
-        <v>0.01311582580550219</v>
+        <v>0.0131160907656882</v>
       </c>
       <c r="E87" t="n">
         <v>-0.005461187695586234</v>
       </c>
       <c r="F87" t="n">
-        <v>0.08892756560912307</v>
+        <v>0.08892768222411251</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.003699470601368215</v>
+        <v>-0.003699470219342138</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0310679079270717</v>
+        <v>0.03106778872029747</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2136357935457219</v>
+        <v>-0.2136360600472377</v>
       </c>
       <c r="J87" t="n">
-        <v>0.06208116439132372</v>
+        <v>0.06208134675782473</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.02851625703680827</v>
+        <v>-0.02851634182882379</v>
       </c>
       <c r="L87" t="n">
         <v>-0.01347467239295608</v>
@@ -6879,7 +6879,7 @@
         <v>-0.01197824086568888</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03906849247449218</v>
+        <v>-0.03906827488927211</v>
       </c>
       <c r="Q87" t="n">
         <v>107.9100036621094</v>
@@ -6911,37 +6911,37 @@
         <v>44681</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.02028119358312896</v>
+        <v>-0.02028129628462938</v>
       </c>
       <c r="C88" t="n">
         <v>-0.1297853695231801</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.007018616211911577</v>
+        <v>-0.007018615300101949</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.07284804352893781</v>
+        <v>-0.07284811090285082</v>
       </c>
       <c r="F88" t="n">
-        <v>0.05484388076934055</v>
+        <v>0.0548439791152604</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.08053312227734821</v>
+        <v>-0.08053311393021179</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.03201508496478433</v>
+        <v>-0.03201497305132861</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.007925238482360486</v>
+        <v>-0.007925017902254528</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.07281093697899299</v>
+        <v>-0.07281085614396721</v>
       </c>
       <c r="K88" t="n">
         <v>-0.03882607270665128</v>
       </c>
       <c r="L88" t="n">
-        <v>0.08882398354673371</v>
+        <v>0.08882388572242461</v>
       </c>
       <c r="M88" t="n">
         <v>0.1505178622029013</v>
@@ -6953,7 +6953,7 @@
         <v>0.1131205879649653</v>
       </c>
       <c r="P88" t="n">
-        <v>-0.02868503783101328</v>
+        <v>-0.02868497892163557</v>
       </c>
       <c r="Q88" t="n">
         <v>109.3399963378906</v>
@@ -6991,34 +6991,34 @@
         <v>-0.04803185864352499</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.04302785711968127</v>
+        <v>-0.04302798232155625</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.03217539925399437</v>
+        <v>-0.03217525625688122</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.02239085320300405</v>
+        <v>-0.02239085111544503</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.002016343122147268</v>
+        <v>-0.002016455621574598</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.07391541745229957</v>
+        <v>-0.07391535773294833</v>
       </c>
       <c r="I89" t="n">
         <v>0.1045200639723456</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.02651441046055236</v>
+        <v>-0.02651440814894956</v>
       </c>
       <c r="K89" t="n">
-        <v>0.06241701431272628</v>
+        <v>0.06241710778481346</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.03361729130562474</v>
+        <v>-0.03361720448192262</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.03900790763093176</v>
+        <v>-0.0390077274178261</v>
       </c>
       <c r="N89" t="n">
         <v>0.06128739111796455</v>
@@ -7027,7 +7027,7 @@
         <v>-0.05989171058625842</v>
       </c>
       <c r="P89" t="n">
-        <v>0.07965149329302834</v>
+        <v>0.07965154911133299</v>
       </c>
       <c r="Q89" t="n">
         <v>122.8399963378906</v>
@@ -7065,34 +7065,34 @@
         <v>-0.0644916280153377</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.09533728759719584</v>
+        <v>-0.09533715088341366</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.1259372384984362</v>
+        <v>-0.1259374542929558</v>
       </c>
       <c r="F90" t="n">
-        <v>0.04736034588847349</v>
+        <v>0.0473602460037692</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.03687342873243715</v>
+        <v>-0.03687320282345563</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.1063918503298903</v>
+        <v>-0.1063919724408131</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.09255673385496133</v>
+        <v>-0.09255680149168743</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.08108397838584502</v>
+        <v>-0.08108423979651835</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.1707500223030822</v>
+        <v>-0.1707501832415799</v>
       </c>
       <c r="L90" t="n">
         <v>-0.06864561920353318</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.09013317314258795</v>
+        <v>-0.09013340627761746</v>
       </c>
       <c r="N90" t="n">
         <v>-0.1265235191291805</v>
@@ -7101,7 +7101,7 @@
         <v>-0.1236868139070303</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.0741259441281934</v>
+        <v>-0.0741261043242718</v>
       </c>
       <c r="Q90" t="n">
         <v>114.8099975585938</v>
@@ -7133,40 +7133,40 @@
         <v>44773</v>
       </c>
       <c r="B91" t="n">
-        <v>0.1265125382768986</v>
+        <v>0.1265126557898266</v>
       </c>
       <c r="C91" t="n">
         <v>0.2246553309799624</v>
       </c>
       <c r="D91" t="n">
-        <v>0.09940175621055536</v>
+        <v>0.09940159006758598</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2349061756252653</v>
+        <v>0.2349063877862931</v>
       </c>
       <c r="F91" t="n">
-        <v>0.005559583249334477</v>
+        <v>0.00555967430495885</v>
       </c>
       <c r="G91" t="n">
-        <v>0.007867073202482811</v>
+        <v>0.007866719520376098</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1195293066607588</v>
+        <v>0.1195294596133236</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0586117258632477</v>
+        <v>0.05861180476739447</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1226065921286907</v>
+        <v>0.1226068109469702</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1223998243889128</v>
+        <v>0.1223999434717271</v>
       </c>
       <c r="L91" t="n">
         <v>0.09213154384953026</v>
       </c>
       <c r="M91" t="n">
-        <v>0.04232443676115194</v>
+        <v>0.04232457707231818</v>
       </c>
       <c r="N91" t="n">
         <v>0.1308970176693889</v>
@@ -7175,7 +7175,7 @@
         <v>0.08429994359428394</v>
       </c>
       <c r="P91" t="n">
-        <v>0.146356760176694</v>
+        <v>0.1463568297285422</v>
       </c>
       <c r="Q91" t="n">
         <v>110.0100021362305</v>
@@ -7207,28 +7207,28 @@
         <v>44804</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.04329413914836255</v>
+        <v>-0.04329423894778028</v>
       </c>
       <c r="C92" t="n">
         <v>-0.05463571169812598</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.0929259645082755</v>
+        <v>-0.09292589577940835</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.07863075838776967</v>
+        <v>-0.07863068882648161</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.02082148042872844</v>
+        <v>-0.02082147854329786</v>
       </c>
       <c r="G92" t="n">
-        <v>0.04045773688297949</v>
+        <v>0.04045797431786813</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.07986547975773051</v>
+        <v>-0.07986553906844229</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1412000939533844</v>
+        <v>-0.1412001643620957</v>
       </c>
       <c r="J92" t="n">
         <v>-0.1064618498761835</v>
@@ -7237,10 +7237,10 @@
         <v>-0.05766668554047027</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.02735991866059062</v>
+        <v>-0.02735982725977992</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.03884979061731997</v>
+        <v>-0.0388499857926673</v>
       </c>
       <c r="N92" t="n">
         <v>-0.05669797310127755</v>
@@ -7249,7 +7249,7 @@
         <v>-0.01355187278988235</v>
       </c>
       <c r="P92" t="n">
-        <v>-0.06763593222212028</v>
+        <v>-0.06763603807411611</v>
       </c>
       <c r="Q92" t="n">
         <v>96.48999786376953</v>
@@ -7281,28 +7281,28 @@
         <v>44834</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.002041487011157472</v>
+        <v>-0.002041596047477001</v>
       </c>
       <c r="C93" t="n">
         <v>-0.02486881578989608</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.03230258297158906</v>
+        <v>-0.03230273206372369</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.03623309803961838</v>
+        <v>-0.03623317080182809</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.06779652239403344</v>
+        <v>-0.06779670107977898</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.1656645538829196</v>
+        <v>-0.1656647031133566</v>
       </c>
       <c r="H93" t="n">
         <v>-0.04339877134375858</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.06843156871822931</v>
+        <v>-0.06843165631359982</v>
       </c>
       <c r="J93" t="n">
         <v>-0.0303498081828697</v>
@@ -7311,10 +7311,10 @@
         <v>-0.08625336656843197</v>
       </c>
       <c r="L93" t="n">
-        <v>0.001406571002046553</v>
+        <v>0.001406476898003772</v>
       </c>
       <c r="M93" t="n">
-        <v>0.04612913868387092</v>
+        <v>0.04612928216296974</v>
       </c>
       <c r="N93" t="n">
         <v>-0.06415442612346856</v>
@@ -7323,7 +7323,7 @@
         <v>0.06182208366275543</v>
       </c>
       <c r="P93" t="n">
-        <v>-0.06616260147094988</v>
+        <v>-0.06616255221705725</v>
       </c>
       <c r="Q93" t="n">
         <v>87.95999908447266</v>
@@ -7355,40 +7355,40 @@
         <v>44865</v>
       </c>
       <c r="B94" t="n">
-        <v>0.09062223539647429</v>
+        <v>0.09062224529780383</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.0226292516786829</v>
+        <v>-0.02262919288582954</v>
       </c>
       <c r="D94" t="n">
-        <v>0.06342392958842225</v>
+        <v>0.06342393455446027</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1362663358167964</v>
+        <v>0.1362664141528875</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05252520162090346</v>
+        <v>0.05252520683158046</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.06245219607831576</v>
+        <v>-0.06245213324135146</v>
       </c>
       <c r="H94" t="n">
         <v>0.04297995045723724</v>
       </c>
       <c r="I94" t="n">
-        <v>0.07481147255103537</v>
+        <v>0.07481157372648517</v>
       </c>
       <c r="J94" t="n">
         <v>0.10257992397583</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1314324400784663</v>
+        <v>0.13143233029839</v>
       </c>
       <c r="L94" t="n">
         <v>0.09082396107521729</v>
       </c>
       <c r="M94" t="n">
-        <v>0.1203885835935814</v>
+        <v>0.1203887146981975</v>
       </c>
       <c r="N94" t="n">
         <v>0.06356070456685425</v>
@@ -7397,7 +7397,7 @@
         <v>0.1212119285116833</v>
       </c>
       <c r="P94" t="n">
-        <v>0.1437247501295831</v>
+        <v>0.1437246980789901</v>
       </c>
       <c r="Q94" t="n">
         <v>94.83000183105469</v>
@@ -7429,19 +7429,19 @@
         <v>44895</v>
       </c>
       <c r="B95" t="n">
-        <v>0.06681866760382427</v>
+        <v>0.06681877447854645</v>
       </c>
       <c r="C95" t="n">
-        <v>0.09408329128562065</v>
+        <v>0.09408298485566591</v>
       </c>
       <c r="D95" t="n">
-        <v>0.07805062409265751</v>
+        <v>0.07805070346873366</v>
       </c>
       <c r="E95" t="n">
-        <v>0.09420533598823089</v>
+        <v>0.09420519161024132</v>
       </c>
       <c r="F95" t="n">
-        <v>0.08944337551393655</v>
+        <v>0.08944347819694154</v>
       </c>
       <c r="G95" t="n">
         <v>0.06058640812317706</v>
@@ -7450,19 +7450,19 @@
         <v>0.08195973129669709</v>
       </c>
       <c r="I95" t="n">
-        <v>0.07874662227363305</v>
+        <v>0.07874671060334926</v>
       </c>
       <c r="J95" t="n">
-        <v>0.07612218765818501</v>
+        <v>0.07612209677991011</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1066048083924918</v>
+        <v>0.1066049157636153</v>
       </c>
       <c r="L95" t="n">
-        <v>0.027897051274695</v>
+        <v>0.02789696524809093</v>
       </c>
       <c r="M95" t="n">
-        <v>0.02922560427627263</v>
+        <v>0.02922548383929757</v>
       </c>
       <c r="N95" t="n">
         <v>0.08479350485268133</v>
@@ -7471,7 +7471,7 @@
         <v>0.02763439022521208</v>
       </c>
       <c r="P95" t="n">
-        <v>0.06183622214741291</v>
+        <v>0.06183633501736052</v>
       </c>
       <c r="Q95" t="n">
         <v>85.43000030517578</v>
@@ -7506,16 +7506,16 @@
         <v>-0.03391371364108919</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0114208206395312</v>
+        <v>0.0114209331138333</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.06126718612698634</v>
+        <v>-0.06126732272402358</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.04691853626385012</v>
+        <v>-0.04691847621385448</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.01092324185975846</v>
+        <v>-0.01092332837431875</v>
       </c>
       <c r="G96" t="n">
         <v>-0.06480351786808747</v>
@@ -7524,19 +7524,19 @@
         <v>-0.07744397565599626</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0378878400733299</v>
+        <v>-0.03788791597789598</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.02300513167493123</v>
+        <v>-0.02300521806749012</v>
       </c>
       <c r="K96" t="n">
         <v>-0.01361255204048872</v>
       </c>
       <c r="L96" t="n">
-        <v>0.001669987140747509</v>
+        <v>0.001670154664222379</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.005205948713634112</v>
+        <v>-0.005206062407943191</v>
       </c>
       <c r="N96" t="n">
         <v>-0.08191530174711692</v>
@@ -7545,7 +7545,7 @@
         <v>0.04787253026780647</v>
       </c>
       <c r="P96" t="n">
-        <v>-0.01823113438925894</v>
+        <v>-0.01823103428254524</v>
       </c>
       <c r="Q96" t="n">
         <v>85.91000366210938</v>
@@ -7580,37 +7580,37 @@
         <v>0.1432636857354814</v>
       </c>
       <c r="C97" t="n">
-        <v>0.08601777847165848</v>
+        <v>0.0860180052653523</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0970048068486169</v>
+        <v>0.09700496647617673</v>
       </c>
       <c r="E97" t="n">
-        <v>0.001949586036069428</v>
+        <v>0.001949718251730737</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.02885644587106095</v>
+        <v>-0.02885636092511101</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.00853847792700968</v>
+        <v>-0.008538550001138789</v>
       </c>
       <c r="H97" t="n">
         <v>0.09403667336986854</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1414824768859277</v>
+        <v>0.1414824091543181</v>
       </c>
       <c r="J97" t="n">
-        <v>0.07313328284184228</v>
+        <v>0.0731333819231903</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1433119314903986</v>
+        <v>0.1433120203807887</v>
       </c>
       <c r="L97" t="n">
-        <v>0.05168838762326167</v>
+        <v>0.05168821619995745</v>
       </c>
       <c r="M97" t="n">
-        <v>0.0356803173036504</v>
+        <v>0.03568043567083534</v>
       </c>
       <c r="N97" t="n">
         <v>0.1583410920124715</v>
@@ -7619,7 +7619,7 @@
         <v>0.1302875819074247</v>
       </c>
       <c r="P97" t="n">
-        <v>0.09746398139412138</v>
+        <v>0.09746397145614294</v>
       </c>
       <c r="Q97" t="n">
         <v>84.48999786376953</v>
@@ -7654,34 +7654,34 @@
         <v>-0.03623791507643603</v>
       </c>
       <c r="C98" t="n">
-        <v>0.05504589727587605</v>
+        <v>0.05504589176525054</v>
       </c>
       <c r="D98" t="n">
-        <v>0.03952726928332728</v>
+        <v>0.0395274019282863</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0108643327800757</v>
+        <v>0.01086426536724616</v>
       </c>
       <c r="F98" t="n">
-        <v>0.009577496706173472</v>
+        <v>0.009577586775263658</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.03776096717857402</v>
+        <v>-0.03776082453392615</v>
       </c>
       <c r="H98" t="n">
         <v>-0.02599575153897082</v>
       </c>
       <c r="I98" t="n">
-        <v>0.03059621865751105</v>
+        <v>0.03059643023216596</v>
       </c>
       <c r="J98" t="n">
-        <v>0.001235438909044095</v>
+        <v>0.001235358460961011</v>
       </c>
       <c r="K98" t="n">
-        <v>0.001857092365271429</v>
+        <v>0.001857014472739671</v>
       </c>
       <c r="L98" t="n">
-        <v>0.03884252426912971</v>
+        <v>0.03884268624679565</v>
       </c>
       <c r="M98" t="n">
         <v>0.02067067692836355</v>
@@ -7693,7 +7693,7 @@
         <v>0.06686630198255306</v>
       </c>
       <c r="P98" t="n">
-        <v>0.01426153903615268</v>
+        <v>0.0142615377111095</v>
       </c>
       <c r="Q98" t="n">
         <v>83.88999938964844</v>
@@ -7728,37 +7728,37 @@
         <v>0.02520422452024573</v>
       </c>
       <c r="C99" t="n">
-        <v>0.07159427044676958</v>
+        <v>0.07159407388036487</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.02665615232524532</v>
+        <v>-0.02665621272449514</v>
       </c>
       <c r="E99" t="n">
-        <v>0.05502085215967289</v>
+        <v>0.05502078329837912</v>
       </c>
       <c r="F99" t="n">
-        <v>0.04983627775835386</v>
+        <v>0.04983627331222862</v>
       </c>
       <c r="G99" t="n">
-        <v>0.06801767904078138</v>
+        <v>0.06801759835463428</v>
       </c>
       <c r="H99" t="n">
         <v>0.02324575393554107</v>
       </c>
       <c r="I99" t="n">
-        <v>0.119509408399789</v>
+        <v>0.1195094003851038</v>
       </c>
       <c r="J99" t="n">
-        <v>0.01702855082463839</v>
+        <v>0.01702871446089604</v>
       </c>
       <c r="K99" t="n">
         <v>0.01853572362037093</v>
       </c>
       <c r="L99" t="n">
-        <v>-0.1274322424220918</v>
+        <v>-0.1274323091520463</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.1193359775159784</v>
+        <v>-0.1193359234574535</v>
       </c>
       <c r="N99" t="n">
         <v>0.05978006426555127</v>
@@ -7767,7 +7767,7 @@
         <v>-0.158289805764838</v>
       </c>
       <c r="P99" t="n">
-        <v>0.01930413686640819</v>
+        <v>0.01930395189039635</v>
       </c>
       <c r="Q99" t="n">
         <v>79.76999664306641</v>
@@ -7799,40 +7799,40 @@
         <v>45046</v>
       </c>
       <c r="B100" t="n">
-        <v>0.03929269601903163</v>
+        <v>0.03929278206909448</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03188332469851707</v>
+        <v>0.03188341606878198</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.007764997254199768</v>
+        <v>-0.007765127840950958</v>
       </c>
       <c r="E100" t="n">
-        <v>0.134755557854227</v>
+        <v>0.1347554341219186</v>
       </c>
       <c r="F100" t="n">
-        <v>0.04712406184677276</v>
+        <v>0.04712397286262582</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.06980198089837886</v>
+        <v>-0.06980205163464437</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.01682788782509137</v>
+        <v>-0.01682795233806966</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01393597352333953</v>
+        <v>0.01393567316796007</v>
       </c>
       <c r="J100" t="n">
-        <v>0.06673137146486763</v>
+        <v>0.06673145056608787</v>
       </c>
       <c r="K100" t="n">
         <v>-0.02844215726925059</v>
       </c>
       <c r="L100" t="n">
-        <v>0.08274345222105417</v>
+        <v>0.08274336457698372</v>
       </c>
       <c r="M100" t="n">
-        <v>0.008682189367008153</v>
+        <v>0.008682188834062243</v>
       </c>
       <c r="N100" t="n">
         <v>-0.09166663396140518</v>
@@ -7841,7 +7841,7 @@
         <v>0.04613578241989402</v>
       </c>
       <c r="P100" t="n">
-        <v>0.05419163864176668</v>
+        <v>0.05419182324994032</v>
       </c>
       <c r="Q100" t="n">
         <v>79.54000091552734</v>
@@ -7873,40 +7873,40 @@
         <v>45077</v>
       </c>
       <c r="B101" t="n">
-        <v>0.07237380284171713</v>
+        <v>0.07237371405265325</v>
       </c>
       <c r="C101" t="n">
         <v>0.03808246776354474</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.01271010399758532</v>
+        <v>-0.01271010483722546</v>
       </c>
       <c r="E101" t="n">
-        <v>0.06718432441727251</v>
+        <v>0.06718444078171193</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0426869905278886</v>
+        <v>0.04268690937268005</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.004435056183056285</v>
+        <v>-0.00443505652031706</v>
       </c>
       <c r="H101" t="n">
-        <v>0.07769736465669874</v>
+        <v>0.077697435372162</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.07583063718252803</v>
+        <v>-0.07583047786071795</v>
       </c>
       <c r="J101" t="n">
-        <v>0.01916503839266182</v>
+        <v>0.01916488866573807</v>
       </c>
       <c r="K101" t="n">
         <v>-0.0856115458275003</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.02618029815758138</v>
+        <v>-0.02618021933047854</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.05385124417172005</v>
+        <v>-0.05385130175003872</v>
       </c>
       <c r="N101" t="n">
         <v>-0.07231520117695733</v>
@@ -7915,7 +7915,7 @@
         <v>-0.06713479870131445</v>
       </c>
       <c r="P101" t="n">
-        <v>-0.05004742413544938</v>
+        <v>-0.05004750511814904</v>
       </c>
       <c r="Q101" t="n">
         <v>72.66000366210938</v>
@@ -7950,28 +7950,28 @@
         <v>0.06799297584706232</v>
       </c>
       <c r="C102" t="n">
-        <v>0.008209357250419602</v>
+        <v>0.008209274587298143</v>
       </c>
       <c r="D102" t="n">
-        <v>0.07558144397622168</v>
+        <v>0.07558144903347319</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.01676679059719199</v>
+        <v>-0.01676699494564537</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.01745485310622774</v>
+        <v>-0.01745477663201889</v>
       </c>
       <c r="G102" t="n">
-        <v>0.04080536478034591</v>
+        <v>0.04080559704641917</v>
       </c>
       <c r="H102" t="n">
         <v>0.05524636396719851</v>
       </c>
       <c r="I102" t="n">
-        <v>0.367247406004958</v>
+        <v>0.3672476212680693</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.02266019106521544</v>
+        <v>-0.02266019271393649</v>
       </c>
       <c r="K102" t="n">
         <v>0.1025439786439004</v>
@@ -7980,7 +7980,7 @@
         <v>0.05024245991959408</v>
       </c>
       <c r="M102" t="n">
-        <v>0.05365045151386005</v>
+        <v>0.05365051583299008</v>
       </c>
       <c r="N102" t="n">
         <v>0.09133227976729175</v>
@@ -8021,40 +8021,40 @@
         <v>45138</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.006837944701178378</v>
+        <v>-0.006838016994590745</v>
       </c>
       <c r="C103" t="n">
-        <v>0.002289981703103683</v>
+        <v>0.00229014587094456</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.02316609786534651</v>
+        <v>-0.02316597488767935</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.03667964099733312</v>
+        <v>-0.03667933687079283</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.0271317691290871</v>
+        <v>-0.02713168991363057</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.0945044101309499</v>
+        <v>-0.09450454303673061</v>
       </c>
       <c r="H103" t="n">
         <v>-0.2320150501575754</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.04525328594783073</v>
+        <v>-0.0452532817160074</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.003246118285292532</v>
+        <v>-0.003246044081521293</v>
       </c>
       <c r="K103" t="n">
         <v>0.01712658833413072</v>
       </c>
       <c r="L103" t="n">
-        <v>0.07049935808655428</v>
+        <v>0.07049943723253116</v>
       </c>
       <c r="M103" t="n">
-        <v>0.02280283559551521</v>
+        <v>0.02280277315945378</v>
       </c>
       <c r="N103" t="n">
         <v>0.06929643128606844</v>
@@ -8095,28 +8095,28 @@
         <v>45169</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.01092129361818839</v>
+        <v>-0.01092114883084294</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.02208673148604279</v>
+        <v>-0.02208681148199088</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.02411072074493814</v>
+        <v>-0.02411078289418045</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.03173007676697592</v>
+        <v>-0.03173028909078224</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.006835925174979551</v>
+        <v>-0.006836087467656071</v>
       </c>
       <c r="G104" t="n">
-        <v>0.06504086389828445</v>
+        <v>0.0650407018026733</v>
       </c>
       <c r="H104" t="n">
         <v>-0.03972535729824234</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.05271484900506351</v>
+        <v>-0.05271503973496439</v>
       </c>
       <c r="J104" t="n">
         <v>-0.01791112218151314</v>
@@ -8125,10 +8125,10 @@
         <v>-0.02993464172253402</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.003135971760875989</v>
+        <v>-0.003136119396408232</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.01125540505456535</v>
+        <v>-0.01125546473770755</v>
       </c>
       <c r="N104" t="n">
         <v>-0.1139084175763925</v>
@@ -8169,40 +8169,40 @@
         <v>45199</v>
       </c>
       <c r="B105" t="n">
-        <v>-0.06144983289172712</v>
+        <v>-0.06144990196423317</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.02440295874351939</v>
+        <v>-0.02440304239378965</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.03523698758972671</v>
+        <v>-0.0352369223315746</v>
       </c>
       <c r="E105" t="n">
-        <v>0.01586744192005551</v>
+        <v>0.01586766650449323</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.002675665569350838</v>
+        <v>-0.002675665788715587</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.02879179404571852</v>
+        <v>-0.02879157013278011</v>
       </c>
       <c r="H105" t="n">
         <v>-0.04616959609935778</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.07176981893195511</v>
+        <v>-0.07176961955844041</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.006158149648474054</v>
+        <v>-0.006158073598462988</v>
       </c>
       <c r="K105" t="n">
         <v>-0.02796517180499902</v>
       </c>
       <c r="L105" t="n">
-        <v>0.02752637056322471</v>
+        <v>0.02752652093732832</v>
       </c>
       <c r="M105" t="n">
-        <v>0.06786343867080702</v>
+        <v>0.06786350312976808</v>
       </c>
       <c r="N105" t="n">
         <v>0.02475396411095132</v>
@@ -8243,40 +8243,40 @@
         <v>45230</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.04347818927472547</v>
+        <v>-0.04347826768812135</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.04044703471068034</v>
+        <v>-0.04044686669341269</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.002938555754940508</v>
+        <v>-0.002938690839442204</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.01290048622480044</v>
+        <v>-0.01290048481002792</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.05868536206761477</v>
+        <v>-0.05868528468679302</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.06225387455967846</v>
+        <v>-0.06225386968182212</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.02869997618807207</v>
+        <v>-0.02869989416282948</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.03962425795022106</v>
+        <v>-0.03962436492810228</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.02573891396617467</v>
+        <v>-0.02573891199660128</v>
       </c>
       <c r="K106" t="n">
         <v>-0.05952379214387615</v>
       </c>
       <c r="L106" t="n">
-        <v>-0.04860303904330476</v>
+        <v>-0.04860310771460341</v>
       </c>
       <c r="M106" t="n">
-        <v>-0.02624037721693973</v>
+        <v>-0.02624026416400638</v>
       </c>
       <c r="N106" t="n">
         <v>-0.01125445859849283</v>
@@ -8285,7 +8285,7 @@
         <v>-0.09215105021721925</v>
       </c>
       <c r="P106" t="n">
-        <v>-0.0208334710728989</v>
+        <v>-0.02083339141628271</v>
       </c>
       <c r="Q106" t="n">
         <v>87.41000366210938</v>
@@ -8317,31 +8317,31 @@
         <v>45260</v>
       </c>
       <c r="B107" t="n">
-        <v>0.1152406342806369</v>
+        <v>0.1152406437277922</v>
       </c>
       <c r="C107" t="n">
-        <v>0.08541318882302895</v>
+        <v>0.08541300247706141</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1423658189934431</v>
+        <v>0.1423660321746791</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1227463074327748</v>
+        <v>0.1227459604912238</v>
       </c>
       <c r="F107" t="n">
         <v>-0.04488781713577894</v>
       </c>
       <c r="G107" t="n">
-        <v>0.03899213479512786</v>
+        <v>0.03899213153710335</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1565601993737775</v>
+        <v>0.1565601017035205</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1475174761462739</v>
+        <v>0.1475175921339045</v>
       </c>
       <c r="J107" t="n">
-        <v>0.07121346500884718</v>
+        <v>0.07121322378701378</v>
       </c>
       <c r="K107" t="n">
         <v>0.09177220102259542</v>
@@ -8350,7 +8350,7 @@
         <v>0.02172165138355253</v>
       </c>
       <c r="M107" t="n">
-        <v>0.04631589237443867</v>
+        <v>0.04631577089777816</v>
       </c>
       <c r="N107" t="n">
         <v>0.09439199641993445</v>
@@ -8359,7 +8359,7 @@
         <v>0.05253075199457169</v>
       </c>
       <c r="P107" t="n">
-        <v>0.1011771229311513</v>
+        <v>0.1011771147002463</v>
       </c>
       <c r="Q107" t="n">
         <v>82.83000183105469</v>
@@ -8391,40 +8391,40 @@
         <v>45291</v>
       </c>
       <c r="B108" t="n">
-        <v>0.06760960544114081</v>
+        <v>0.06760968391758282</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03065922402894938</v>
+        <v>0.03065930887818968</v>
       </c>
       <c r="D108" t="n">
-        <v>0.0803870948125267</v>
+        <v>0.0803869664919401</v>
       </c>
       <c r="E108" t="n">
-        <v>0.07195794568099245</v>
+        <v>0.07195805887728524</v>
       </c>
       <c r="F108" t="n">
-        <v>0.009697890911710916</v>
+        <v>0.009697799477379698</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2145883354692937</v>
+        <v>0.2145881573716881</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1530028262813572</v>
+        <v>0.1530027532640383</v>
       </c>
       <c r="I108" t="n">
-        <v>0.05193569036150891</v>
+        <v>0.05193558403500975</v>
       </c>
       <c r="J108" t="n">
-        <v>0.07208437354984065</v>
+        <v>0.07208460408466122</v>
       </c>
       <c r="K108" t="n">
         <v>0.05362319699172446</v>
       </c>
       <c r="L108" t="n">
-        <v>0.09291336524616756</v>
+        <v>0.09291329099228363</v>
       </c>
       <c r="M108" t="n">
-        <v>0.1011064951665734</v>
+        <v>0.1011066061267787</v>
       </c>
       <c r="N108" t="n">
         <v>0.02130894968609032</v>
@@ -8433,7 +8433,7 @@
         <v>0.05692744578026399</v>
       </c>
       <c r="P108" t="n">
-        <v>0.07584798753668731</v>
+        <v>0.07584790805647934</v>
       </c>
       <c r="Q108" t="n">
         <v>77.04000091552734</v>
@@ -8471,34 +8471,34 @@
         <v>-0.04784332494845589</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.01240093445100998</v>
+        <v>-0.0124008245155971</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.03802940613093131</v>
+        <v>-0.03802922501660244</v>
       </c>
       <c r="F109" t="n">
-        <v>0.02918361386867097</v>
+        <v>0.02918370706756224</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.08524801021675987</v>
+        <v>-0.08524801586119235</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.05746170257351535</v>
+        <v>-0.05746164288448241</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1649870715374926</v>
+        <v>-0.1649868793641368</v>
       </c>
       <c r="J109" t="n">
-        <v>0.05310498439444444</v>
+        <v>0.05310491237109849</v>
       </c>
       <c r="K109" t="n">
         <v>0.005960445177121576</v>
       </c>
       <c r="L109" t="n">
-        <v>0.06736305526842834</v>
+        <v>0.06736312778639753</v>
       </c>
       <c r="M109" t="n">
-        <v>0.02832355647781681</v>
+        <v>0.02832345285207127</v>
       </c>
       <c r="N109" t="n">
         <v>0.02285141369217158</v>
@@ -8507,7 +8507,7 @@
         <v>0.04672900713997552</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.04508989729260926</v>
+        <v>-0.04508996596105264</v>
       </c>
       <c r="Q109" t="n">
         <v>81.70999908447266</v>
@@ -8539,37 +8539,37 @@
         <v>45351</v>
       </c>
       <c r="B110" t="n">
-        <v>0.08329574323739131</v>
+        <v>0.08329567384029124</v>
       </c>
       <c r="C110" t="n">
-        <v>0.01457946531306509</v>
+        <v>0.0145795492028955</v>
       </c>
       <c r="D110" t="n">
-        <v>0.03034536405175392</v>
+        <v>0.03034524935801386</v>
       </c>
       <c r="E110" t="n">
-        <v>0.07666965651713675</v>
+        <v>0.07666955319796576</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.04590763726220504</v>
+        <v>-0.04590754927389407</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.02598308974744645</v>
+        <v>-0.02598301924581503</v>
       </c>
       <c r="H110" t="n">
         <v>0.06447364407409406</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.04759945248702413</v>
+        <v>-0.04759972921243416</v>
       </c>
       <c r="J110" t="n">
-        <v>0.05896701446051944</v>
+        <v>0.05896694951787218</v>
       </c>
       <c r="K110" t="n">
         <v>0.06153141594882428</v>
       </c>
       <c r="L110" t="n">
-        <v>0.03813707774594821</v>
+        <v>0.0381370140925974</v>
       </c>
       <c r="M110" t="n">
         <v>0.09995557843434422</v>
@@ -8581,7 +8581,7 @@
         <v>0.06860901657701857</v>
       </c>
       <c r="P110" t="n">
-        <v>0.1408563351128405</v>
+        <v>0.1408565609746575</v>
       </c>
       <c r="Q110" t="n">
         <v>83.62000274658203</v>
@@ -8613,19 +8613,19 @@
         <v>45382</v>
       </c>
       <c r="B111" t="n">
-        <v>0.03521918275865099</v>
+        <v>0.03521924907591889</v>
       </c>
       <c r="C111" t="n">
-        <v>0.07980502041104209</v>
+        <v>0.07980484844375679</v>
       </c>
       <c r="D111" t="n">
         <v>0.03960726676832271</v>
       </c>
       <c r="E111" t="n">
-        <v>0.005841473948086762</v>
+        <v>0.005841563076465661</v>
       </c>
       <c r="F111" t="n">
-        <v>0.09416198739896964</v>
+        <v>0.09416188649316637</v>
       </c>
       <c r="G111" t="n">
         <v>0.02507558770246821</v>
@@ -8634,16 +8634,16 @@
         <v>0.04408732013232819</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2429161356486926</v>
+        <v>0.2429160899120413</v>
       </c>
       <c r="J111" t="n">
-        <v>0.03168208290006214</v>
+        <v>0.03168202351659533</v>
       </c>
       <c r="K111" t="n">
         <v>0.02060975558385647</v>
       </c>
       <c r="L111" t="n">
-        <v>0.01738524856079948</v>
+        <v>0.01738524962677568</v>
       </c>
       <c r="M111" t="n">
         <v>-0.02160648581228564</v>
@@ -8655,7 +8655,7 @@
         <v>-0.001298053609855687</v>
       </c>
       <c r="P111" t="n">
-        <v>0.07860025238167867</v>
+        <v>0.0786001164081982</v>
       </c>
       <c r="Q111" t="n">
         <v>87.48000335693359</v>
@@ -8690,34 +8690,34 @@
         <v>0.1002830714790137</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1438015444241321</v>
+        <v>0.1438016320089071</v>
       </c>
       <c r="D112" t="n">
         <v>-0.03070335741849373</v>
       </c>
       <c r="E112" t="n">
-        <v>0.08892976011028852</v>
+        <v>0.08892975223015553</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1507745628005042</v>
+        <v>0.1507744785149905</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.001547051124095034</v>
+        <v>-0.001546978628728435</v>
       </c>
       <c r="H112" t="n">
         <v>-0.07753674044206238</v>
       </c>
       <c r="I112" t="n">
-        <v>0.01242978439428555</v>
+        <v>0.01242988281204438</v>
       </c>
       <c r="J112" t="n">
-        <v>0.01377249758987831</v>
+        <v>0.01377273699978598</v>
       </c>
       <c r="K112" t="n">
         <v>-0.03979893102570631</v>
       </c>
       <c r="L112" t="n">
-        <v>0.002414606025070265</v>
+        <v>0.002414726705032066</v>
       </c>
       <c r="M112" t="n">
         <v>-0.1115011339487294</v>
@@ -8729,7 +8729,7 @@
         <v>0.0004710307452100437</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.02309552647809632</v>
+        <v>-0.02309558491715857</v>
       </c>
       <c r="Q112" t="n">
         <v>87.86000061035156</v>
@@ -8770,13 +8770,13 @@
         <v>0.04135608353749398</v>
       </c>
       <c r="E113" t="n">
-        <v>0.02737280789160246</v>
+        <v>0.0273726429158252</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.01705054239674098</v>
+        <v>-0.01705047040313878</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1487015021442868</v>
+        <v>0.1487014913474143</v>
       </c>
       <c r="H113" t="n">
         <v>-0.0132762843652684</v>
@@ -8785,13 +8785,13 @@
         <v>0.07034842573608979</v>
       </c>
       <c r="J113" t="n">
-        <v>0.05784539840349412</v>
+        <v>0.05784539161989888</v>
       </c>
       <c r="K113" t="n">
         <v>0.03502474544426715</v>
       </c>
       <c r="L113" t="n">
-        <v>0.02649686758131531</v>
+        <v>0.02649680586622782</v>
       </c>
       <c r="M113" t="n">
         <v>0.02557700634641646</v>
@@ -8803,7 +8803,7 @@
         <v>0.02683611184321189</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.00494004923837843</v>
+        <v>-0.004939989713240167</v>
       </c>
       <c r="Q113" t="n">
         <v>81.62000274658203</v>
@@ -8844,13 +8844,13 @@
         <v>-0.02473965170210901</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.007968211113991597</v>
+        <v>-0.007968053332944702</v>
       </c>
       <c r="F114" t="n">
         <v>0.01095555796977377</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01889137607298008</v>
+        <v>0.01889124846190038</v>
       </c>
       <c r="H114" t="n">
         <v>0.03862853667912747</v>
@@ -8859,7 +8859,7 @@
         <v>-0.09671341960896529</v>
       </c>
       <c r="J114" t="n">
-        <v>0.0203938602577749</v>
+        <v>0.02039374713846565</v>
       </c>
       <c r="K114" t="n">
         <v>-0.07852497904154809</v>
@@ -8877,7 +8877,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.03865245357505753</v>
+        <v>-0.03865251369269329</v>
       </c>
       <c r="Q114" t="n">
         <v>86.41000366210938</v>
@@ -8912,25 +8912,25 @@
         <v>0.01156453166072402</v>
       </c>
       <c r="C115" t="n">
-        <v>0.01917686072525226</v>
+        <v>0.01917692904202872</v>
       </c>
       <c r="D115" t="n">
-        <v>0.08778362560443709</v>
+        <v>0.08778373117146154</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.04317263849681896</v>
+        <v>-0.04317271489209351</v>
       </c>
       <c r="F115" t="n">
         <v>0.02137258215814342</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1133737629603639</v>
+        <v>0.1133738320302247</v>
       </c>
       <c r="H115" t="n">
         <v>-0.08900962216237784</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.008350677820368468</v>
+        <v>-0.008350777130342935</v>
       </c>
       <c r="J115" t="n">
         <v>0.04686417645683538</v>
@@ -8951,7 +8951,7 @@
         <v>0.04539202975872514</v>
       </c>
       <c r="P115" t="n">
-        <v>0.00811501042423135</v>
+        <v>0.008115136001224599</v>
       </c>
       <c r="Q115" t="n">
         <v>80.72000122070312</v>
@@ -8986,10 +8986,10 @@
         <v>-0.01277730734572446</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.02769553406471659</v>
+        <v>-0.02769559923956988</v>
       </c>
       <c r="D116" t="n">
-        <v>0.01595592243511601</v>
+        <v>0.0159558238388231</v>
       </c>
       <c r="E116" t="n">
         <v>-0.02334735873794058</v>
@@ -9004,7 +9004,7 @@
         <v>-0.03669723611458964</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0225564436860034</v>
+        <v>-0.02255624565239989</v>
       </c>
       <c r="J116" t="n">
         <v>0.005102102236734796</v>
@@ -9025,7 +9025,7 @@
         <v>-0.03771931497007264</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.002561213333643453</v>
+        <v>-0.002561337237504957</v>
       </c>
       <c r="Q116" t="n">
         <v>78.80000305175781</v>
@@ -9069,25 +9069,25 @@
         <v>0.05533171328450859</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1188674652205588</v>
+        <v>-0.1188673966091992</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00261372080728961</v>
+        <v>0.002613827498481047</v>
       </c>
       <c r="H117" t="n">
         <v>0.03999995044902649</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0633847191029655</v>
+        <v>0.06338461015141039</v>
       </c>
       <c r="J117" t="n">
-        <v>0.02357946493519103</v>
+        <v>0.02357936168268537</v>
       </c>
       <c r="K117" t="n">
         <v>0.03939532887006325</v>
       </c>
       <c r="L117" t="n">
-        <v>-0.01740500747679197</v>
+        <v>-0.0174051180556869</v>
       </c>
       <c r="M117" t="n">
         <v>-0.01558076132980002</v>
@@ -9099,7 +9099,7 @@
         <v>-0.01868729783405509</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.01614083845193526</v>
+        <v>-0.01614071507442516</v>
       </c>
       <c r="Q117" t="n">
         <v>71.76999664306641</v>
@@ -9137,16 +9137,16 @@
         <v>-0.03630023300783503</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.02546849720728428</v>
+        <v>-0.02546858979475031</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.1003064658017877</v>
+        <v>-0.1003063848418358</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.0324530415762011</v>
+        <v>-0.03245303904917252</v>
       </c>
       <c r="G118" t="n">
-        <v>0.1805760415470627</v>
+        <v>0.1805759159183702</v>
       </c>
       <c r="H118" t="n">
         <v>-0.08809521690848576</v>
@@ -9155,13 +9155,13 @@
         <v>-0.08420140854366187</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.03551438956834219</v>
+        <v>-0.03551419140289558</v>
       </c>
       <c r="K118" t="n">
         <v>-0.07888940405369549</v>
       </c>
       <c r="L118" t="n">
-        <v>-0.03091790853798115</v>
+        <v>-0.03091791201740912</v>
       </c>
       <c r="M118" t="n">
         <v>0.06282979189928461</v>
@@ -9173,7 +9173,7 @@
         <v>0.004180206532939934</v>
       </c>
       <c r="P118" t="n">
-        <v>0.03169269777183992</v>
+        <v>0.03169269576851508</v>
       </c>
       <c r="Q118" t="n">
         <v>73.16000366210938</v>
@@ -9208,16 +9208,16 @@
         <v>0.04485657755910721</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.01191751360013493</v>
+        <v>-0.01191744612659718</v>
       </c>
       <c r="D119" t="n">
-        <v>0.01411587813736181</v>
+        <v>0.01411606949280042</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.007126542654962043</v>
+        <v>-0.007126631999807786</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.03255505550357052</v>
+        <v>-0.03255521384161952</v>
       </c>
       <c r="G119" t="n">
         <v>-0.003371647979255599</v>
@@ -9229,13 +9229,13 @@
         <v>-0.02450537328397628</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.003388453133179148</v>
+        <v>-0.003388452778786522</v>
       </c>
       <c r="K119" t="n">
         <v>-0.03492818561678757</v>
       </c>
       <c r="L119" t="n">
-        <v>0.006979063506249439</v>
+        <v>0.006979064316714689</v>
       </c>
       <c r="M119" t="n">
         <v>0.02436819636114418</v>
@@ -9247,7 +9247,7 @@
         <v>-0.01110081372711047</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.01843147548118951</v>
+        <v>-0.01843153562105382</v>
       </c>
       <c r="Q119" t="n">
         <v>72.94000244140625</v>
@@ -9282,16 +9282,16 @@
         <v>-0.03905729474165909</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.003661363015569519</v>
+        <v>-0.003661431052893294</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.02418630142119715</v>
+        <v>-0.02418639284001534</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.03043351297207286</v>
+        <v>-0.03043342234003577</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.01665540727992765</v>
+        <v>-0.01665524229104209</v>
       </c>
       <c r="G120" t="n">
         <v>0.01353185602582729</v>
@@ -9300,16 +9300,16 @@
         <v>0.1362168365435832</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.01421477238827462</v>
+        <v>-0.01421488024017326</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.02188805273055217</v>
+        <v>-0.02188805043353381</v>
       </c>
       <c r="K120" t="n">
         <v>-0.01685668503492432</v>
       </c>
       <c r="L120" t="n">
-        <v>-0.0003300550022476978</v>
+        <v>-0.000330055040310695</v>
       </c>
       <c r="M120" t="n">
         <v>0.006167392311198894</v>
@@ -9321,7 +9321,7 @@
         <v>0.02104775781467949</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.01104565372083444</v>
+        <v>-0.01104571614046912</v>
       </c>
       <c r="Q120" t="n">
         <v>74.63999938964844</v>
@@ -9362,10 +9362,10 @@
         <v>0.04222780618884547</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1027538845714002</v>
+        <v>0.1027537814894321</v>
       </c>
       <c r="F121" t="n">
-        <v>0.08261324361626676</v>
+        <v>0.08261315203133179</v>
       </c>
       <c r="G121" t="n">
         <v>-0.06697814088476572</v>
@@ -9374,16 +9374,16 @@
         <v>0.2272728063146028</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.006036427092479091</v>
+        <v>-0.006036208938691945</v>
       </c>
       <c r="J121" t="n">
-        <v>0.08062860019518636</v>
+        <v>0.08062848425200442</v>
       </c>
       <c r="K121" t="n">
         <v>0.159858695771107</v>
       </c>
       <c r="L121" t="n">
-        <v>0.03664577858479401</v>
+        <v>0.03664589817358843</v>
       </c>
       <c r="M121" t="n">
         <v>0.07530646217383885</v>
@@ -9395,7 +9395,7 @@
         <v>0.1062756637959652</v>
       </c>
       <c r="P121" t="n">
-        <v>0.1418466789390975</v>
+        <v>0.1418467510088117</v>
       </c>
       <c r="Q121" t="n">
         <v>76.76000213623047</v>
@@ -9433,7 +9433,7 @@
         <v>-0.06294131974479789</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.03317690353751801</v>
+        <v>-0.03317681142064943</v>
       </c>
       <c r="E122" t="n">
         <v>-0.01852840169404657</v>
@@ -9448,7 +9448,7 @@
         <v>-0.05516978520169735</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0273280102005492</v>
+        <v>-0.0273280071925136</v>
       </c>
       <c r="J122" t="n">
         <v>0.010907470184365</v>
@@ -9457,7 +9457,7 @@
         <v>0.01173914901279738</v>
       </c>
       <c r="L122" t="n">
-        <v>0.09968149630523038</v>
+        <v>0.09968138502201351</v>
       </c>
       <c r="M122" t="n">
         <v>0.09812710260179003</v>
@@ -9469,7 +9469,7 @@
         <v>0.06956525305466066</v>
       </c>
       <c r="P122" t="n">
-        <v>0.08575154178788247</v>
+        <v>0.08575143123573525</v>
       </c>
       <c r="Q122" t="n">
         <v>73.18000030517578</v>
@@ -9504,13 +9504,13 @@
         <v>-0.103297079919212</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.07664159165516582</v>
+        <v>-0.07664152339721986</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.08928024601514495</v>
+        <v>-0.08928042806448222</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.1277702969565048</v>
+        <v>-0.1277702105895091</v>
       </c>
       <c r="F123" t="n">
         <v>-0.1004932057969844</v>
@@ -9522,7 +9522,7 @@
         <v>-0.1290322479863364</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.08532764283966709</v>
+        <v>-0.08532774634771445</v>
       </c>
       <c r="J123" t="n">
         <v>-0.06692722638553139</v>
@@ -9531,7 +9531,7 @@
         <v>-0.0975504690368747</v>
       </c>
       <c r="L123" t="n">
-        <v>-0.04720533966036844</v>
+        <v>-0.0472052432414819</v>
       </c>
       <c r="M123" t="n">
         <v>-0.05334514279833158</v>
@@ -9543,7 +9543,7 @@
         <v>-0.03583678796580736</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.1195195562728721</v>
+        <v>-0.119519466621594</v>
       </c>
       <c r="Q123" t="n">
         <v>74.73999786376953</v>
@@ -9578,13 +9578,13 @@
         <v>-0.01283550107674092</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.04674386652479257</v>
+        <v>-0.04674393699287971</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.01744446314786019</v>
+        <v>-0.01744436035462238</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.05019700252764869</v>
+        <v>-0.05019719559446323</v>
       </c>
       <c r="F124" t="n">
         <v>-0.04180944968984102</v>
@@ -9599,7 +9599,7 @@
         <v>0.06219189630605282</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.04374068444586665</v>
+        <v>-0.0437407897063653</v>
       </c>
       <c r="K124" t="n">
         <v>-0.01928152745538114</v>
@@ -9658,7 +9658,7 @@
         <v>0.04218096622177248</v>
       </c>
       <c r="E125" t="n">
-        <v>0.02702695658664722</v>
+        <v>0.02702706365602836</v>
       </c>
       <c r="F125" t="n">
         <v>-0.01609442923211279</v>
@@ -9673,7 +9673,7 @@
         <v>0.005332199313531349</v>
       </c>
       <c r="J125" t="n">
-        <v>0.002372232061116364</v>
+        <v>0.002372342397518823</v>
       </c>
       <c r="K125" t="n">
         <v>0.04647667637185338</v>
@@ -9732,7 +9732,7 @@
         <v>-0.02862778051639892</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.006822575974142153</v>
+        <v>-0.0068224744658405</v>
       </c>
       <c r="F126" t="n">
         <v>-0.03416937405010523</v>
@@ -9806,7 +9806,7 @@
         <v>0.09688342173298947</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.02257129071066521</v>
+        <v>-0.022571288403753</v>
       </c>
       <c r="F127" t="n">
         <v>0.1031238392027138</v>
@@ -9818,7 +9818,7 @@
         <v>0.1344051891994655</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.00413839520348569</v>
+        <v>-0.004138335355979517</v>
       </c>
       <c r="J127" t="n">
         <v>0.01697937950756523</v>
@@ -9880,7 +9880,7 @@
         <v>0.03180974199417919</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0107096284285948</v>
+        <v>0.01070952274295278</v>
       </c>
       <c r="F128" t="n">
         <v>0.03296811547686151</v>
@@ -9892,10 +9892,10 @@
         <v>-0.02408521546260645</v>
       </c>
       <c r="I128" t="n">
-        <v>0.04911224379108514</v>
+        <v>0.04911218074342139</v>
       </c>
       <c r="J128" t="n">
-        <v>0.02407733119284527</v>
+        <v>0.02407744011983715</v>
       </c>
       <c r="K128" t="n">
         <v>-0.000418045516998089</v>
@@ -9969,7 +9969,7 @@
         <v>0.2621533152029087</v>
       </c>
       <c r="J129" t="n">
-        <v>0.009267136251207564</v>
+        <v>0.009267028899528018</v>
       </c>
       <c r="K129" t="n">
         <v>0.09493926145177234</v>
@@ -10043,7 +10043,7 @@
         <v>0.02881597888468734</v>
       </c>
       <c r="J130" t="n">
-        <v>0.06631538999267228</v>
+        <v>0.06631528460334679</v>
       </c>
       <c r="K130" t="n">
         <v>0.1019862859998426</v>
@@ -10117,7 +10117,7 @@
         <v>-0.03078575650900361</v>
       </c>
       <c r="J131" t="n">
-        <v>0.02978136997029712</v>
+        <v>0.02978147174879142</v>
       </c>
       <c r="K131" t="n">
         <v>-0.01178500421345874</v>

--- a/data/omxs30_och_makrodata.xlsx
+++ b/data/omxs30_och_makrodata.xlsx
@@ -625,91 +625,91 @@
         <v>0.0469034525082721</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04882823030985017</v>
+        <v>0.04882823339631215</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1482241921401288</v>
+        <v>0.1482242928673276</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04518459286894894</v>
+        <v>0.04518475640634567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1356309598777179</v>
+        <v>0.135630458496653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06830828682830936</v>
+        <v>0.06830814184323986</v>
       </c>
       <c r="H2" t="n">
         <v>0.1476241736201755</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02800947496240203</v>
+        <v>0.02800914577013036</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05910619116378424</v>
+        <v>0.05910599736641164</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0724638443809078</v>
+        <v>0.07246383571442627</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04872955250752109</v>
+        <v>0.04872974746758252</v>
       </c>
       <c r="M2" t="n">
-        <v>0.190599102387321</v>
+        <v>0.1905990872079053</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03855868422660702</v>
+        <v>0.03855891971128966</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05716853755845186</v>
+        <v>0.05716832240685643</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.03062655943626624</v>
+        <v>-0.03062648036077809</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02785278716476092</v>
+        <v>0.02785278514819312</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03662215997331986</v>
+        <v>0.0366221663246098</v>
       </c>
       <c r="S2" t="n">
         <v>0.01174610229876083</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05726872190202248</v>
+        <v>0.05726859366114301</v>
       </c>
       <c r="U2" t="n">
         <v>0.05343230275694832</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1108575607004176</v>
+        <v>0.1108574932570781</v>
       </c>
       <c r="W2" t="n">
         <v>0.1205285903661986</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02254625558211187</v>
+        <v>0.02254632095532783</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04860051667162457</v>
+        <v>0.04860043804080227</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03059169849201493</v>
+        <v>0.03059180278118157</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.07283349228234948</v>
+        <v>0.07283335877604635</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.04693011131321301</v>
+        <v>-0.04693011534086255</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.04331265710614041</v>
+        <v>-0.04331248904829643</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.00991441666788262</v>
+        <v>-0.009914546753673203</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.04448462300196332</v>
+        <v>0.0444847956872032</v>
       </c>
       <c r="AF2" t="n">
         <v>60.22999954223633</v>
@@ -744,58 +744,58 @@
         <v>0.03712868509713485</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.007448923013873676</v>
+        <v>-0.007448802927136344</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05602885352791498</v>
+        <v>0.05602877712791932</v>
       </c>
       <c r="E3" t="n">
         <v>-0.006986796928390215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02873056655854134</v>
+        <v>0.02873056943688468</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.01433885782834077</v>
+        <v>-0.01433885876920304</v>
       </c>
       <c r="H3" t="n">
         <v>-0.04871942069040325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02946577497326253</v>
+        <v>0.02946602049804592</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2165369003893345</v>
+        <v>0.2165371862262067</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02299658235616131</v>
+        <v>0.02299635675884248</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0009955008196382842</v>
+        <v>-0.0009957485027676238</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09761392566787475</v>
+        <v>0.09761385224721808</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09839730903189037</v>
+        <v>0.09839719987014117</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06027750618588124</v>
+        <v>-0.0602774132185897</v>
       </c>
       <c r="P3" t="n">
         <v>0.06318827681425288</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0318073025117076</v>
+        <v>0.0318070889541906</v>
       </c>
       <c r="R3" t="n">
-        <v>0.09621765201682497</v>
+        <v>0.09621791906499033</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03964294744915919</v>
+        <v>-0.03964317251159433</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1090908164660194</v>
+        <v>0.1090909509926501</v>
       </c>
       <c r="U3" t="n">
         <v>0.06281497610865139</v>
@@ -807,28 +807,28 @@
         <v>-0.03111022604556757</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1124081283690445</v>
+        <v>-0.1124080740720939</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.02751906893851319</v>
+        <v>-0.02751899742753561</v>
       </c>
       <c r="Z3" t="n">
         <v>0.02968382233597389</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.04783726587836545</v>
+        <v>0.0478372606822659</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.07663835819700704</v>
+        <v>-0.07663818500163344</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02354239905957467</v>
+        <v>0.02354221544013635</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.02355728100281806</v>
+        <v>-0.02355701268806942</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.02527704499143701</v>
+        <v>0.02527696208075625</v>
       </c>
       <c r="AF3" t="n">
         <v>62.43000030517578</v>
@@ -860,58 +860,58 @@
         <v>43830</v>
       </c>
       <c r="B4" t="n">
-        <v>0.07446295345192167</v>
+        <v>0.07446287617292136</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1369605069596502</v>
+        <v>0.136960559363517</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001273298468106088</v>
+        <v>0.001273226213715839</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03693925750021032</v>
+        <v>-0.03693933287845075</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06469072335625015</v>
+        <v>0.06469092442832691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01314666879693238</v>
+        <v>0.01314653653049858</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00607300372497166</v>
+        <v>0.006072843120855875</v>
       </c>
       <c r="I4" t="n">
         <v>0.02280853654600068</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.03371777416290855</v>
+        <v>-0.03371784228424834</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0549246929145738</v>
+        <v>-0.05492458989230398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002657686383702451</v>
+        <v>0.002657686548555471</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1146244230665512</v>
+        <v>0.1146245449512171</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03029186329544464</v>
+        <v>-0.03029176692317026</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03051267064246388</v>
+        <v>0.03051288119519846</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01710924293125649</v>
+        <v>0.0171093220809857</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009877504013282135</v>
+        <v>0.009877641897148903</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08436035766826566</v>
+        <v>0.0843601986147029</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1151406134819224</v>
+        <v>0.1151408748183911</v>
       </c>
       <c r="T4" t="n">
         <v>0.1092896431838675</v>
@@ -923,31 +923,31 @@
         <v>0.04880862680214659</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.003147966231295429</v>
+        <v>-0.003148055091630519</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07257699959729713</v>
+        <v>0.07257672391506809</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07340420400139891</v>
+        <v>0.07340412506907645</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004723134490611791</v>
+        <v>0.0004725041671911345</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03553867209880357</v>
+        <v>0.03553856475336659</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1182838902305776</v>
+        <v>0.1182837811730886</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.03857050429747666</v>
+        <v>-0.03857024212278637</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.02895043737353509</v>
+        <v>-0.02895070066680971</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.05977709401946685</v>
+        <v>0.05977701514652356</v>
       </c>
       <c r="AF4" t="n">
         <v>66</v>
@@ -979,94 +979,94 @@
         <v>43861</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.001332740109349473</v>
+        <v>-0.001332668281825988</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.02475245674061177</v>
+        <v>-0.0247523472854545</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02161926963992977</v>
+        <v>0.02161927276410935</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04703195961045603</v>
+        <v>0.04703204156108431</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08458243964450451</v>
+        <v>-0.08458270631438725</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004253212611218249</v>
+        <v>0.000425387051951498</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.07726373113437657</v>
+        <v>-0.07726350401632875</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0231743671064556</v>
+        <v>-0.02317444260799528</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1230486617002433</v>
+        <v>0.123048727994493</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.07111333393466457</v>
+        <v>-0.07111298790009379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01391664280247684</v>
+        <v>0.01391658179902411</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05673767628793769</v>
+        <v>0.05673756073322522</v>
       </c>
       <c r="N5" t="n">
         <v>0.0003809452361245302</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1111403399981326</v>
+        <v>0.1111401129717251</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00619760638639355</v>
+        <v>0.006197528085795545</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0332549557649966</v>
+        <v>0.03325502336488873</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00611901571058493</v>
+        <v>-0.006119016141189482</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006345958947184149</v>
+        <v>0.006345748791737549</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02894093781530027</v>
+        <v>0.0289411349935611</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.001911865852168071</v>
+        <v>-0.001911968646181261</v>
       </c>
       <c r="V5" t="n">
         <v>-0.03558717591406513</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01599999786061734</v>
+        <v>0.01600008842782819</v>
       </c>
       <c r="X5" t="n">
-        <v>0.08128944735914101</v>
+        <v>0.08128972528078382</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.06164522121977456</v>
+        <v>-0.06164515271381887</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05337758192647413</v>
+        <v>0.05337728580912326</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.06705379513396958</v>
+        <v>-0.06705399534176526</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06310508584309305</v>
+        <v>0.06310499863608232</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07029807767214025</v>
+        <v>0.07029779122408364</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02484488518479444</v>
+        <v>0.02484481310652931</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.05353733968121177</v>
+        <v>0.05353726924158653</v>
       </c>
       <c r="AF5" t="n">
         <v>58.15999984741211</v>
@@ -1098,94 +1098,94 @@
         <v>43890</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.07384339074044255</v>
+        <v>-0.07384346275979903</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0592215397889484</v>
+        <v>-0.05922174586129114</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.10331944332266</v>
+        <v>-0.1033193872118149</v>
       </c>
       <c r="E6" t="n">
         <v>-0.06279993965885722</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.008479441884817751</v>
+        <v>-0.008479343658972516</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1045892770950843</v>
+        <v>-0.1045892251546824</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1347579593829075</v>
+        <v>-0.1347580342269373</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01029547163417899</v>
+        <v>-0.01029547242994433</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1459525805046933</v>
+        <v>0.1459524262286807</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0121437936026334</v>
+        <v>0.01214329237741008</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06013091069372467</v>
+        <v>-0.06013079600098581</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1778521885657069</v>
+        <v>0.1778523955242322</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02399102553266685</v>
+        <v>-0.02399092308440964</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1809117868663377</v>
+        <v>-0.1809116949254612</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.04839433794993031</v>
+        <v>-0.04839426061093011</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.09636508961383428</v>
+        <v>-0.09636508330922455</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1178539295842151</v>
+        <v>-0.1178538671240468</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.005780524869695158</v>
+        <v>-0.005780317246581346</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07001791857296835</v>
+        <v>-0.07001828841969449</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1663473776555435</v>
+        <v>-0.1663473432923501</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1007664322464761</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.05035226467140685</v>
+        <v>-0.05035217693425331</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03989932004483121</v>
+        <v>-0.0398991417660769</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01901146486064276</v>
+        <v>0.01901131745978435</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.06322865244296982</v>
+        <v>-0.06322856767993923</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.04923614605024429</v>
+        <v>-0.04923572742137494</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.02360877962284358</v>
+        <v>-0.02360861749852816</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.04092170105210891</v>
+        <v>-0.04092153384883757</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.08048514671223239</v>
+        <v>-0.08048507808632821</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.09981862641385741</v>
+        <v>-0.09981842859033041</v>
       </c>
       <c r="AF6" t="n">
         <v>50.52000045776367</v>
@@ -1217,94 +1217,94 @@
         <v>43921</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1541187678312053</v>
+        <v>-0.1541187798157176</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1205036253889334</v>
+        <v>-0.120503508972289</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2029154322108455</v>
+        <v>-0.202915290466209</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1265703887843377</v>
+        <v>-0.1265704685470787</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01533491321469038</v>
+        <v>-0.01533441088562282</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05720059675230771</v>
+        <v>0.05720067429876319</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08618957367387547</v>
+        <v>-0.08618947370104801</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1093621420950855</v>
+        <v>-0.1093621506359188</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1544772401238101</v>
+        <v>-0.1544772988639769</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05712071941804364</v>
+        <v>0.05712048105486978</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06397796392911248</v>
+        <v>0.06397783409131552</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03703695894441417</v>
+        <v>-0.03703704029089572</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1728442607670448</v>
+        <v>-0.1728444000739384</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.261651998494083</v>
+        <v>-0.2616520252481266</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1035598484567727</v>
+        <v>-0.1035599213123494</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.04232122742550026</v>
+        <v>-0.04232129676254626</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.272183431405536</v>
+        <v>-0.2721835116697788</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2589851474464326</v>
+        <v>-0.258985199957529</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06949811166481767</v>
+        <v>-0.06949781689532819</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2686710988922812</v>
+        <v>-0.2686709301756715</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1082701712957281</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09589781980991674</v>
+        <v>0.0958977185608505</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2653103882101768</v>
+        <v>-0.2653105865287165</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.1382668663252525</v>
+        <v>-0.1382669478756935</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.2750120980945381</v>
+        <v>-0.2750119532071783</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.1683604357069912</v>
+        <v>-0.1683606234167119</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.2341968313807514</v>
+        <v>-0.2341969797328155</v>
       </c>
       <c r="AC7" t="n">
         <v>-0.043384662031136</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.05879223195673511</v>
+        <v>-0.05879245146708534</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.1969085242025211</v>
+        <v>-0.1969086657008438</v>
       </c>
       <c r="AF7" t="n">
         <v>22.73999977111816</v>
@@ -1336,64 +1336,64 @@
         <v>43951</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06959485150058531</v>
+        <v>0.06959504175765008</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09284249120468302</v>
+        <v>0.0928424789153659</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06531206454022276</v>
+        <v>0.06531205807732854</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05196292427654803</v>
+        <v>-0.05196265505789999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0258901448356339</v>
+        <v>0.02588962251541349</v>
       </c>
       <c r="G8" t="n">
         <v>0.1718786230438598</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1443771451027003</v>
+        <v>0.1443770199053913</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.003453439681691539</v>
+        <v>-0.003453089239032203</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1510549394391636</v>
+        <v>0.1510546720451902</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05964353540900791</v>
+        <v>0.05964402040038275</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03758155986869749</v>
+        <v>0.03758156445479588</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3162722989909061</v>
+        <v>0.3162720876699892</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1488207069197722</v>
+        <v>0.1488209067133119</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06406239132541658</v>
+        <v>0.06406223443021863</v>
       </c>
       <c r="P8" t="n">
         <v>0.04280556455113582</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07460085114258308</v>
+        <v>0.07460077554191313</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2772602174121139</v>
+        <v>0.2772604685503743</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1276747347888465</v>
+        <v>0.1276748147001205</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2645228925603913</v>
+        <v>0.2645226418205093</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1861743762067249</v>
+        <v>0.1861741758289559</v>
       </c>
       <c r="V8" t="n">
         <v>0.07115039658324229</v>
@@ -1402,28 +1402,28 @@
         <v>0.04778499106119005</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1958914792880166</v>
+        <v>0.1958914957914095</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08611953087158364</v>
+        <v>0.08611979461120467</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.235721412197694</v>
+        <v>0.2357211652413291</v>
       </c>
       <c r="AA8" t="n">
         <v>0.1378934216030285</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04068559389643145</v>
+        <v>0.04068570806689631</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.05097446986805965</v>
+        <v>-0.05097465988802119</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.03122797343597861</v>
+        <v>-0.03122774050444566</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.05564845694179543</v>
+        <v>0.0556486578128863</v>
       </c>
       <c r="AF8" t="n">
         <v>25.27000045776367</v>
@@ -1455,94 +1455,94 @@
         <v>43982</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.00906666157854108</v>
+        <v>-0.009066660799279092</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2971558528538278</v>
+        <v>0.2971556957395847</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03487736354329041</v>
+        <v>0.03487736030362298</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08321522070285003</v>
+        <v>0.08321481936428987</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08812280718031262</v>
+        <v>0.08812271621008483</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.02015763197512788</v>
+        <v>-0.02015757276929597</v>
       </c>
       <c r="H9" t="n">
         <v>0.01947070250509553</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07815441898378683</v>
+        <v>0.07815413438269281</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09200854096788058</v>
+        <v>0.09200911192967376</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006345595885055566</v>
+        <v>0.006345266618388523</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.02110244831045982</v>
+        <v>-0.02110233318177257</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2492694882945541</v>
+        <v>0.2492695748836757</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06179430243627415</v>
+        <v>0.06179418514881885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04368573712292179</v>
+        <v>0.04368588311655475</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03560839967248164</v>
+        <v>0.03560831273303022</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01995093488040922</v>
+        <v>0.01995100663633553</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2344487304483449</v>
+        <v>0.2344485375221737</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006325032069129266</v>
+        <v>0.006325094909729101</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1430133925678727</v>
+        <v>0.1430134050905387</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003531937182915446</v>
+        <v>0.003532150803841283</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03040307765979855</v>
+        <v>0.03040295458885112</v>
       </c>
       <c r="W9" t="n">
         <v>0.1163895578671468</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01717701454276943</v>
+        <v>0.01717708620040193</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.01284607089795964</v>
+        <v>-0.01284606991462334</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.005076247759963737</v>
+        <v>0.005076355577128489</v>
       </c>
       <c r="AA9" t="n">
         <v>0.1108967129764651</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02288487019200502</v>
+        <v>0.02288476477403822</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0115842983661627</v>
+        <v>0.01158450091208141</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.04355568804450649</v>
+        <v>-0.04355568447944447</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.05628214858265079</v>
+        <v>0.05628205080735627</v>
       </c>
       <c r="AF9" t="n">
         <v>35.33000183105469</v>
@@ -1574,34 +1574,34 @@
         <v>44012</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1248657025322037</v>
+        <v>0.1248654314986914</v>
       </c>
       <c r="C10" t="n">
         <v>0.0802076625885384</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07635603411552894</v>
+        <v>0.07635584774821891</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0065549634915959</v>
+        <v>-0.006554875730721776</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06879721403500283</v>
+        <v>0.06879741001437401</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04192773539146577</v>
+        <v>-0.04192785370569074</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03819795087167055</v>
+        <v>0.0381977633238868</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1104734591979264</v>
+        <v>0.1104736224217271</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1291667062766801</v>
+        <v>0.1291662355624297</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006071918126892006</v>
+        <v>0.006072028281860486</v>
       </c>
       <c r="L10" t="n">
         <v>-0.03120976425869215</v>
@@ -1613,52 +1613,52 @@
         <v>0.05181745008838123</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.05029886395557237</v>
+        <v>-0.05029886051280108</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008118480486003943</v>
+        <v>0.008118481167551428</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.001092720756734944</v>
+        <v>-0.001092651780547849</v>
       </c>
       <c r="R10" t="n">
-        <v>0.03445538657036096</v>
+        <v>0.03445545892385815</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01052795843818743</v>
+        <v>0.01052789533513687</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.01483265688032043</v>
+        <v>-0.01483250480249632</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02331732486852323</v>
+        <v>0.02331717799229294</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1167415344037153</v>
+        <v>0.1167415483472809</v>
       </c>
       <c r="W10" t="n">
         <v>-0.05702123973198658</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0124817288989344</v>
+        <v>-0.01248165964102932</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.007852934833846636</v>
+        <v>-0.007852856681139442</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.007442896369390217</v>
+        <v>0.007442788298360314</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.002025308302357809</v>
+        <v>0.002025200950067862</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01186420555168977</v>
+        <v>0.01186430983388354</v>
       </c>
       <c r="AC10" t="n">
         <v>-0.01396648293491798</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.07806715055366875</v>
+        <v>0.07806714387283242</v>
       </c>
       <c r="AE10" t="n">
         <v>0.09493440820864874</v>
@@ -1693,94 +1693,94 @@
         <v>44043</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04545443680447536</v>
+        <v>0.04545459802716811</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0913462116125805</v>
+        <v>0.09134612517073348</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01320941635604034</v>
+        <v>0.01320941745756854</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01161248880746357</v>
+        <v>0.01161266887382961</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01951348266955077</v>
+        <v>-0.01951331110812216</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007157287583201777</v>
+        <v>0.007157477239023047</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1221696839302375</v>
+        <v>0.1221697963236075</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0534023568727866</v>
+        <v>0.05340212854477278</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2264436426858618</v>
+        <v>0.2264435891263503</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1699165397035705</v>
+        <v>0.169916666261005</v>
       </c>
       <c r="L11" t="n">
         <v>-0.04184649567362442</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07703387738070178</v>
+        <v>0.0770339883006117</v>
       </c>
       <c r="N11" t="n">
         <v>0.0455882777662826</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006296303183120688</v>
+        <v>0.006296302729337233</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01800093783249768</v>
+        <v>0.01800093933150904</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.05064081649422736</v>
+        <v>0.05064074394575968</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1355932466969427</v>
+        <v>0.1355929762413557</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05286881991530978</v>
+        <v>0.0528690670955243</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01991273878579713</v>
+        <v>0.01991258171649934</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2085123449359663</v>
+        <v>0.2085125384964484</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.06605405738407133</v>
+        <v>-0.06605395749510612</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04512627722314155</v>
+        <v>-0.04512635365265427</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04882300910526483</v>
+        <v>0.04882265501472283</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.06399796727887985</v>
+        <v>-0.06399826990511837</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.06860182894482691</v>
+        <v>-0.06860172246472473</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.06757141719978088</v>
+        <v>-0.06757131730374688</v>
       </c>
       <c r="AB11" t="n">
         <v>0.1891124044840551</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.004046758889289626</v>
+        <v>0.004046859257822888</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.02068963382165367</v>
+        <v>-0.02068971156031418</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0342700443027002</v>
+        <v>0.03426996426747198</v>
       </c>
       <c r="AF11" t="n">
         <v>43.29999923706055</v>
@@ -1812,31 +1812,31 @@
         <v>44074</v>
       </c>
       <c r="B12" t="n">
-        <v>0.007780241245080477</v>
+        <v>0.00778031499913312</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1062205950365804</v>
+        <v>0.1062207618632123</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02076276926688103</v>
+        <v>0.02076293558062936</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04356903970503767</v>
+        <v>0.0435689473639036</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03360043100043031</v>
+        <v>0.03360025014538293</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01860150618509759</v>
+        <v>-0.01860162909532848</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08406908123445622</v>
+        <v>0.08406900751094759</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05273915623043024</v>
+        <v>0.05273915990989142</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2219513661085727</v>
+        <v>-0.2219512596169242</v>
       </c>
       <c r="K12" t="n">
         <v>-0.005456458137210962</v>
@@ -1845,61 +1845,61 @@
         <v>0.03154243711509941</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08255343401152659</v>
+        <v>0.0825533225231887</v>
       </c>
       <c r="N12" t="n">
         <v>0.1012660167651325</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01509007563694942</v>
+        <v>0.01509000293572305</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06049315214615381</v>
+        <v>0.06049323889615321</v>
       </c>
       <c r="Q12" t="n">
         <v>0.06736348322224006</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02686554971687261</v>
+        <v>0.02686579427767111</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02835648813868419</v>
+        <v>0.02835612932912634</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1571427514928805</v>
+        <v>0.1571429159583126</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.07506220700968924</v>
+        <v>-0.0750624766623359</v>
       </c>
       <c r="V12" t="n">
-        <v>0.04428035533122232</v>
+        <v>0.0442805843673455</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05340247957321242</v>
+        <v>0.05340264393061367</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0129960393748858</v>
+        <v>0.01299637719390812</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.05122004395683666</v>
+        <v>0.05122013601220532</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.001699523628077126</v>
+        <v>-0.00169975207947537</v>
       </c>
       <c r="AA12" t="n">
         <v>0.06906166410824421</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.03268065723284175</v>
+        <v>0.03268057157981019</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.01209174576235095</v>
+        <v>-0.01209184451760481</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.02259388979228139</v>
+        <v>-0.02259380873418793</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.09542753692440842</v>
+        <v>0.09542746692560145</v>
       </c>
       <c r="AF12" t="n">
         <v>45.27999877929688</v>
@@ -1931,94 +1931,94 @@
         <v>44104</v>
       </c>
       <c r="B13" t="n">
-        <v>0.04087194836441799</v>
+        <v>0.0408719453732187</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05000005728088763</v>
+        <v>0.0500000537008285</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.05960251818573237</v>
+        <v>-0.05960251338007794</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05050018569362069</v>
+        <v>0.05050027048522843</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07226806297400024</v>
+        <v>0.07226814761783884</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02049705792985823</v>
+        <v>0.02049712173671026</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03412167908877195</v>
+        <v>0.03412190690053785</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01087371514281976</v>
+        <v>0.01087364959141301</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09216313341296378</v>
+        <v>0.09216293768780393</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.01965092581917982</v>
+        <v>-0.01965083284677771</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01747314130017785</v>
+        <v>0.01747295308773489</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0818153529112432</v>
+        <v>-0.08181544804415763</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08205593898502328</v>
+        <v>0.08205611077883335</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1221902659409675</v>
+        <v>0.1221901248294048</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04826677924320455</v>
+        <v>0.04826670210780959</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06456293827076265</v>
+        <v>0.06456281511991868</v>
       </c>
       <c r="R13" t="n">
         <v>0.01090124024163086</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.01895736003711157</v>
+        <v>-0.0189574763483854</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0489711366106429</v>
+        <v>-0.04897126516074846</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0173076126201348</v>
+        <v>0.01730779979046759</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03592478227122231</v>
+        <v>0.03592444540557227</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1040826381198698</v>
+        <v>0.1040826302112796</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.07114526298723978</v>
+        <v>-0.07114525829089235</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1344518597704294</v>
+        <v>-0.1344517910174251</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.07718501364647601</v>
+        <v>0.07718513700300833</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.07589810478826942</v>
+        <v>0.07589799731157809</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.04010365479962485</v>
+        <v>-0.0401034922410678</v>
       </c>
       <c r="AC13" t="n">
         <v>0.03467970097059081</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1062741756698862</v>
+        <v>0.1062741668563731</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0468844538994968</v>
+        <v>0.04688460180774556</v>
       </c>
       <c r="AF13" t="n">
         <v>40.95000076293945</v>
@@ -2050,73 +2050,73 @@
         <v>44135</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.05584634196570892</v>
+        <v>-0.0558465489718295</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1624149020858289</v>
+        <v>-0.1624149592020336</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09205241544992848</v>
+        <v>-0.09205240755748179</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.09090917896232198</v>
+        <v>-0.09090941377091222</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0837219043039078</v>
+        <v>-0.0837221345121566</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.07699336494360787</v>
+        <v>-0.07699336012957736</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08811398653249081</v>
+        <v>-0.0881140520044239</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02189780639070626</v>
+        <v>0.02189787482107275</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.02669376569032156</v>
+        <v>-0.02669330354781951</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0179431642056247</v>
+        <v>0.01794306766795795</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1281760878858464</v>
+        <v>-0.1281759266156055</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1112978389692567</v>
+        <v>0.1112980577203959</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04042478824768814</v>
+        <v>-0.04042486121264421</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.06558971865968255</v>
+        <v>-0.06558985265393802</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.04730007259772251</v>
+        <v>-0.04730000249448918</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.08960802518907651</v>
+        <v>-0.08960803555511954</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.06398284411711364</v>
+        <v>-0.0639827867595294</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.02386192147796329</v>
+        <v>-0.02386169432457486</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.07139761760145757</v>
+        <v>-0.07139776111027207</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2268430288380334</v>
+        <v>-0.2268431231274006</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.09891982318547521</v>
+        <v>-0.09891972779782754</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01869157077588557</v>
+        <v>-0.01869163831023668</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.04193862135336957</v>
+        <v>-0.04193876050641876</v>
       </c>
       <c r="Y14" t="n">
         <v>-0.04248538190141049</v>
@@ -2125,16 +2125,16 @@
         <v>-0.1027838490678528</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.01884766283486627</v>
+        <v>-0.01884766471765109</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.008810559364454185</v>
+        <v>-0.00881064501082951</v>
       </c>
       <c r="AC14" t="n">
         <v>-0.1244297637434432</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.05112748113543197</v>
+        <v>-0.05112747730266043</v>
       </c>
       <c r="AE14" t="n">
         <v>0.0005776826632108989</v>
@@ -2169,94 +2169,94 @@
         <v>44165</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04436231751739195</v>
+        <v>0.04436247306427687</v>
       </c>
       <c r="C15" t="n">
         <v>0.09644665008851372</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1983381044721222</v>
+        <v>0.1983379913115706</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07795775300659469</v>
+        <v>0.07795803321096706</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1088925091816348</v>
+        <v>0.1088927002479796</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.001318779163289263</v>
+        <v>-0.001318846814814534</v>
       </c>
       <c r="H15" t="n">
         <v>0.2150492466959759</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08039741801976663</v>
+        <v>0.08039774394920518</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1321453060617861</v>
+        <v>0.1321449910280315</v>
       </c>
       <c r="K15" t="n">
         <v>0.05610394682402253</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05428449457585782</v>
+        <v>0.05428463602663625</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1092285890096776</v>
+        <v>0.1092283923596942</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09440341630604454</v>
+        <v>0.09440332576902666</v>
       </c>
       <c r="O15" t="n">
-        <v>0.255878173058814</v>
+        <v>0.2558785110739286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1493848994744171</v>
+        <v>0.1493848222373537</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1107782483262547</v>
+        <v>0.1107783894711094</v>
       </c>
       <c r="R15" t="n">
-        <v>0.07680505482635014</v>
+        <v>0.07680486628483307</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09883010181361152</v>
+        <v>0.09883022101096528</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1258153906115707</v>
+        <v>0.1258157172040593</v>
       </c>
       <c r="U15" t="n">
         <v>0.09926658855115345</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2135645863481728</v>
+        <v>0.2135648213088674</v>
       </c>
       <c r="W15" t="n">
-        <v>0.148240233526983</v>
+        <v>0.1482400932637975</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1882043725059617</v>
+        <v>0.1882046089995162</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2077094983739629</v>
+        <v>0.2077094025302173</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2181709579668316</v>
+        <v>0.2181707209853501</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1591657376156224</v>
+        <v>0.1591657538208946</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1126880816801905</v>
+        <v>0.1126881688559402</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.04500243325525544</v>
+        <v>0.04500232156118811</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.06565082946607315</v>
+        <v>0.06565090328366296</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1250363161442762</v>
+        <v>0.1250361812653744</v>
       </c>
       <c r="AF15" t="n">
         <v>47.59000015258789</v>
@@ -2288,40 +2288,40 @@
         <v>44196</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01327433912282361</v>
+        <v>0.01327426781636443</v>
       </c>
       <c r="C16" t="n">
-        <v>0.009259200131873424</v>
+        <v>0.00925927438486962</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04623201515453945</v>
+        <v>0.04623217275821956</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.007839344222057343</v>
+        <v>-0.00783934357636229</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02568250310573006</v>
+        <v>-0.02568273618115247</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.08836798219047159</v>
+        <v>-0.08836805002078996</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01387475331964649</v>
+        <v>-0.01387462371809489</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05017563503066746</v>
+        <v>0.0501752668312212</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1024363976132572</v>
+        <v>0.1024364915898657</v>
       </c>
       <c r="K16" t="n">
         <v>-0.06876493427134256</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.02721575545761767</v>
+        <v>-0.02721588597368907</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1385705270512023</v>
+        <v>0.1385705386983653</v>
       </c>
       <c r="N16" t="n">
         <v>0.05430374819053529</v>
@@ -2330,52 +2330,52 @@
         <v>-0.05286345594931674</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01490814521699479</v>
+        <v>0.01490828061602301</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.009434111194594585</v>
+        <v>0.009433882402898552</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1255350021892339</v>
+        <v>0.1255349026618855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.08257119481985187</v>
+        <v>-0.08257140281598718</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1223937846530871</v>
+        <v>0.1223938428121985</v>
       </c>
       <c r="U16" t="n">
         <v>0.06539146293647691</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04652971262070627</v>
+        <v>0.04652951000001071</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03353757023983839</v>
+        <v>0.03353794080140116</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.06794609859848944</v>
+        <v>-0.06794627740004111</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.05166474523040843</v>
+        <v>-0.05166474933051957</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.02894970365422611</v>
+        <v>0.0289500010942807</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0104166373887673</v>
+        <v>0.01041681397111027</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.07151136180055151</v>
+        <v>-0.07151135619785276</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.01541256966834426</v>
+        <v>-0.01541246443166444</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.04884754574223793</v>
+        <v>-0.04884746436228737</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.005133684954276574</v>
+        <v>-0.005133505736994448</v>
       </c>
       <c r="AF16" t="n">
         <v>51.79999923706055</v>
@@ -2407,61 +2407,61 @@
         <v>44227</v>
       </c>
       <c r="B17" t="n">
-        <v>0.07772924590295904</v>
+        <v>0.07772932174526437</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01834872847363278</v>
+        <v>0.01834865355190929</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0296067274315559</v>
+        <v>-0.02960679829126833</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02271620508524075</v>
+        <v>0.02271603716593118</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08145317033577038</v>
+        <v>0.08145350877990376</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03802508800295246</v>
+        <v>0.0380250908322235</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05628007990642536</v>
+        <v>-0.05628007250981448</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07283635176023506</v>
+        <v>0.07283669925628722</v>
       </c>
       <c r="J17" t="n">
-        <v>0.240969732023109</v>
+        <v>0.240969654699406</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08203604085442318</v>
+        <v>0.08203632504197222</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01058600299909629</v>
+        <v>0.0105859340385015</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.02299950361686431</v>
+        <v>-0.02299943149214601</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.023739702140257</v>
+        <v>-0.02373984553577835</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04069773295957924</v>
+        <v>0.04069750668884575</v>
       </c>
       <c r="P17" t="n">
-        <v>0.003766574480373652</v>
+        <v>0.003766441807960819</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02536705105198345</v>
+        <v>0.02536728345498762</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.02471496039296395</v>
+        <v>-0.02471476314951238</v>
       </c>
       <c r="S17" t="n">
-        <v>0.009669769239655457</v>
+        <v>0.009669770383007092</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03633661371715147</v>
+        <v>0.03633649133907224</v>
       </c>
       <c r="U17" t="n">
         <v>-0.02045926887468097</v>
@@ -2470,31 +2470,31 @@
         <v>0.03725792477854584</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02896024005079378</v>
+        <v>0.02895987863198113</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0811833295891875</v>
+        <v>0.08118346898550999</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01452769205574089</v>
+        <v>0.01452794432173654</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.03290437233553689</v>
+        <v>0.03290427469231494</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.07497670106966026</v>
+        <v>0.07497643376749918</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.09478210328899328</v>
+        <v>0.09478192652879502</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.06353568968976098</v>
+        <v>0.06353601536127385</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.08068334279449996</v>
+        <v>0.08068324598351939</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0670796928128583</v>
+        <v>0.06707962851750504</v>
       </c>
       <c r="AF17" t="n">
         <v>55.88000106811523</v>
@@ -2529,91 +2529,91 @@
         <v>-0.01985415689798742</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1081079909521805</v>
+        <v>0.1081080631983358</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1898907647785004</v>
+        <v>0.1898906724219644</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02221139737694933</v>
+        <v>0.02221139917991111</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0586298522321711</v>
+        <v>0.05862984790916581</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.05426178001013982</v>
+        <v>-0.05426171221986298</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2163638479164307</v>
+        <v>0.2163635392595247</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1161633554069923</v>
+        <v>0.1161634363265038</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.09804672820853055</v>
+        <v>-0.0980466720086336</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.002366137108483657</v>
+        <v>-0.002366399128450714</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0505050891044504</v>
+        <v>-0.05050502431259873</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2892348952962638</v>
+        <v>0.2892347441753662</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03879790213647161</v>
+        <v>-0.03879776095271503</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1117319358887321</v>
+        <v>0.1117319601817346</v>
       </c>
       <c r="P18" t="n">
-        <v>0.04652895778364119</v>
+        <v>0.04652909277896389</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01692716032531361</v>
+        <v>0.01692693927917954</v>
       </c>
       <c r="R18" t="n">
-        <v>0.04353470523109904</v>
+        <v>0.04353491259797315</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1255500241826781</v>
+        <v>0.1255501559929308</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.05080498831589875</v>
+        <v>-0.0508050452892812</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.04774096147407603</v>
+        <v>-0.04774089272566151</v>
       </c>
       <c r="V18" t="n">
-        <v>0.08572804990044913</v>
+        <v>0.08572796072116073</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.01492021794402765</v>
+        <v>-0.0149201047932529</v>
       </c>
       <c r="X18" t="n">
-        <v>0.06370403392037405</v>
+        <v>0.06370396802386802</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.06229117866420664</v>
+        <v>0.06229108590293619</v>
       </c>
       <c r="Z18" t="n">
         <v>-0.05447838611439693</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.003051448053008832</v>
+        <v>0.003051529411726595</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.03437179340636676</v>
+        <v>-0.03437171897980629</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.07748884608671425</v>
+        <v>-0.07748923064611635</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.07057229561965483</v>
+        <v>-0.07057250181521135</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.04593790856574587</v>
+        <v>0.0459381344291625</v>
       </c>
       <c r="AF18" t="n">
         <v>66.12999725341797</v>
@@ -2648,28 +2648,28 @@
         <v>0.0996942364194624</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05691060037941176</v>
+        <v>0.05691066186672122</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01033296860553401</v>
+        <v>0.01033290337461712</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1856400371411893</v>
+        <v>0.1856400518826848</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1026756573105909</v>
+        <v>0.1026756501592032</v>
       </c>
       <c r="G19" t="n">
         <v>0.07759577503005177</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.03139023721169443</v>
+        <v>-0.0313901263145433</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1037949173190793</v>
+        <v>0.1037945101584177</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2208069003922291</v>
+        <v>0.2208066240626296</v>
       </c>
       <c r="K19" t="n">
         <v>0.1058328158725266</v>
@@ -2678,61 +2678,61 @@
         <v>0.1140981574933735</v>
       </c>
       <c r="M19" t="n">
-        <v>0.223014742797248</v>
+        <v>0.2230148861560015</v>
       </c>
       <c r="N19" t="n">
         <v>0.1449687974765366</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0113066241835047</v>
+        <v>-0.0113065286094014</v>
       </c>
       <c r="P19" t="n">
-        <v>0.09860167853538204</v>
+        <v>0.09860148322952234</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1145963934511751</v>
+        <v>0.1145968530941834</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01120807008866609</v>
+        <v>0.01120776978774662</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1268344233218881</v>
+        <v>0.1268343192772896</v>
       </c>
       <c r="T19" t="n">
-        <v>0.02073128949953196</v>
+        <v>0.02073111067534517</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06982989395987116</v>
+        <v>0.06982996111356865</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0524921997860146</v>
+        <v>0.05249228623539137</v>
       </c>
       <c r="W19" t="n">
-        <v>0.06402755313630082</v>
+        <v>0.06402743653197263</v>
       </c>
       <c r="X19" t="n">
         <v>0.1372260743402349</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1126814960931648</v>
+        <v>0.1126814096953517</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.1153029990501562</v>
+        <v>0.1153029022557075</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1079360318994</v>
+        <v>0.1079361212203103</v>
       </c>
       <c r="AB19" t="n">
         <v>0.05923519521211795</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.105584170396259</v>
+        <v>0.1055842927244866</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.109059182670348</v>
+        <v>0.1090592687352969</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.021266756535123</v>
+        <v>0.02126653599932715</v>
       </c>
       <c r="AF19" t="n">
         <v>63.54000091552734</v>
@@ -2767,91 +2767,91 @@
         <v>0.03355946042333691</v>
       </c>
       <c r="C20" t="n">
-        <v>0.138461584015094</v>
+        <v>0.1384613201841114</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1050472090368633</v>
+        <v>0.1050471512553233</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.03095139529390156</v>
+        <v>-0.0309513973668919</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.02845567637998014</v>
+        <v>-0.02845561141779374</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02434551103572491</v>
+        <v>0.02434565170511704</v>
       </c>
       <c r="H20" t="n">
         <v>0.04343771778609695</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06630259444451192</v>
+        <v>-0.0663022578850927</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.00417411971083792</v>
+        <v>-0.004173894305633419</v>
       </c>
       <c r="K20" t="n">
-        <v>0.003375102786247197</v>
+        <v>0.003375182142547173</v>
       </c>
       <c r="L20" t="n">
         <v>0.001449810776309679</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3007830092447363</v>
+        <v>0.3007831050878205</v>
       </c>
       <c r="N20" t="n">
-        <v>0.003007393461983865</v>
+        <v>0.003007259998764056</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06124516064713026</v>
+        <v>0.06124526560810128</v>
       </c>
       <c r="P20" t="n">
-        <v>0.02318773461347545</v>
+        <v>0.02318785202065676</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.03230917504709208</v>
+        <v>0.03230887621876688</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1292063181385317</v>
+        <v>0.1292064290905746</v>
       </c>
       <c r="S20" t="n">
-        <v>0.02279059254303339</v>
+        <v>0.02279077931444373</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1440177107529856</v>
+        <v>0.1440177446281279</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07121341228006783</v>
+        <v>0.07121326770320624</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.09548991196247836</v>
+        <v>-0.09548999000369995</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.03914604007052191</v>
+        <v>-0.03914582518503062</v>
       </c>
       <c r="X20" t="n">
         <v>0.0206670172316985</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.03499890891411228</v>
+        <v>0.03499883912927793</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04840178067285716</v>
+        <v>0.04840187166111876</v>
       </c>
       <c r="AA20" t="n">
         <v>-0.1192586710469377</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.03352820044533666</v>
+        <v>-0.03352812508972025</v>
       </c>
       <c r="AC20" t="n">
         <v>-0.04822147085123707</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.04896535577772687</v>
+        <v>-0.04896514586532752</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.004614082917320905</v>
+        <v>0.004613977193999474</v>
       </c>
       <c r="AF20" t="n">
         <v>67.25</v>
@@ -2886,91 +2886,91 @@
         <v>0.03210527741011138</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.06756767740125369</v>
+        <v>-0.06756746798501467</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09252780652025439</v>
+        <v>0.0925279341849079</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05636137341737335</v>
+        <v>0.05636137731278223</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.01988309682561817</v>
+        <v>-0.01988302922539975</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06237448392844969</v>
+        <v>0.0623744066997558</v>
       </c>
       <c r="H21" t="n">
         <v>0.02608901035102873</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03832436653025173</v>
+        <v>0.03832408109422181</v>
       </c>
       <c r="J21" t="n">
-        <v>0.04820131121822691</v>
+        <v>0.04820108391948952</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05157836668597771</v>
+        <v>-0.05157844169603654</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03655448311436538</v>
+        <v>0.03655454752868659</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.05059804345812668</v>
+        <v>-0.05059811341107379</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02477075066652934</v>
+        <v>0.02477088702566599</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01460741687610101</v>
+        <v>0.0146073236802986</v>
       </c>
       <c r="P21" t="n">
-        <v>0.06577230943695511</v>
+        <v>0.06577219729091044</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.08084479990206672</v>
+        <v>0.08084499645312704</v>
       </c>
       <c r="R21" t="n">
-        <v>0.009330327060906862</v>
+        <v>0.009330501088717913</v>
       </c>
       <c r="S21" t="n">
-        <v>0.01068670217947232</v>
+        <v>0.01068670121471871</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1707039657693372</v>
+        <v>0.1707041036690418</v>
       </c>
       <c r="U21" t="n">
         <v>-0.04422314591981968</v>
       </c>
       <c r="V21" t="n">
-        <v>0.04443356164773604</v>
+        <v>0.04443365176157665</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.07272727791147249</v>
+        <v>-0.07272738366913589</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.02393010220506364</v>
+        <v>-0.0239300018544788</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.05296398080625098</v>
+        <v>-0.05296398437734939</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.01567935338230098</v>
+        <v>0.01567943616314116</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.02424511609127689</v>
+        <v>0.02424519870940567</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.002285840730458455</v>
+        <v>0.002285762582434625</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.0205763852575811</v>
+        <v>0.02057606980915683</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.03339037965243796</v>
+        <v>0.03339029870918542</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.04955277115189238</v>
+        <v>0.04955288160447169</v>
       </c>
       <c r="AF21" t="n">
         <v>69.62999725341797</v>
@@ -3002,91 +3002,91 @@
         <v>44377</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02615747755327891</v>
+        <v>0.02615770471232359</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02898555777772205</v>
+        <v>0.02898555440896011</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.03387663831366994</v>
+        <v>-0.03387674526978557</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01137688985093166</v>
+        <v>0.01137702144988073</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04216405651078747</v>
+        <v>0.04216391545260434</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08076899560931072</v>
+        <v>0.08076886112570181</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01052646802596924</v>
+        <v>-0.01052635762545717</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03889185903852233</v>
+        <v>0.03889194728991452</v>
       </c>
       <c r="J22" t="n">
-        <v>0.03898693239898532</v>
+        <v>0.03898726612291692</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.02182621550843367</v>
+        <v>-0.02182613211792217</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.009078182260638057</v>
+        <v>-0.009078243839217182</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1480407503439969</v>
+        <v>-0.1480409055597507</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07275807589341787</v>
+        <v>0.07275814081674192</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.04177494728495956</v>
+        <v>-0.04177495112215812</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.03837887196962109</v>
+        <v>-0.03837887600804379</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.02948846415148632</v>
+        <v>0.02948837418230466</v>
       </c>
       <c r="R22" t="n">
-        <v>0.08754777301786154</v>
+        <v>0.087547499294375</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07154118673836085</v>
+        <v>0.07154100170514788</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.002216821181166617</v>
+        <v>-0.002216733563536244</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.05335551822189055</v>
+        <v>-0.05335545231051986</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.01851853104606027</v>
+        <v>0.0185185925449014</v>
       </c>
       <c r="X22" t="n">
-        <v>0.04243281747299332</v>
+        <v>0.04243260748874222</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.03850292789362886</v>
+        <v>0.03850293063487764</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.02658658080387644</v>
+        <v>-0.02658657863699243</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.02679760119528862</v>
+        <v>-0.02679759903372836</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.06815137853229092</v>
+        <v>0.06815145632427422</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0720464687772191</v>
+        <v>0.07204680013455667</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.04888166264491867</v>
+        <v>0.04888151329241319</v>
       </c>
       <c r="AE22" t="n">
         <v>-0.00775611819685218</v>
@@ -3121,91 +3121,91 @@
         <v>44408</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0812952940909526</v>
+        <v>0.08129505472617993</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2605635393636994</v>
+        <v>0.2605632840370855</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1888851802218448</v>
+        <v>0.1888852011326603</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07098538054142489</v>
+        <v>0.07098524656668714</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1106869898610623</v>
+        <v>0.1106870464658429</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0401361275261457</v>
+        <v>-0.04013601032318803</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01975680889243847</v>
+        <v>0.01975680668807267</v>
       </c>
       <c r="I23" t="n">
-        <v>0.030769217700366</v>
+        <v>0.03076921508659436</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3361234316393391</v>
+        <v>0.336123605272753</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.08079198727165138</v>
+        <v>-0.08079206563525199</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.008104213860087639</v>
+        <v>-0.00810440199619944</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1088433304408138</v>
+        <v>0.1088436235509314</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1238171516356561</v>
+        <v>0.123816841542236</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1127093179003644</v>
+        <v>-0.1127092328459693</v>
       </c>
       <c r="P23" t="n">
-        <v>0.05268199495748904</v>
+        <v>0.05268211014695745</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.08136879934431818</v>
+        <v>0.08136888423320499</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2630000062623032</v>
+        <v>0.2630001063798924</v>
       </c>
       <c r="S23" t="n">
-        <v>0.05920635348010062</v>
+        <v>0.05920644177343171</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1419684065814386</v>
+        <v>0.1419685825962056</v>
       </c>
       <c r="U23" t="n">
-        <v>0.150594486918433</v>
+        <v>0.1505943371804657</v>
       </c>
       <c r="V23" t="n">
         <v>0.02607501765777376</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1408200022352928</v>
+        <v>0.1408198125904578</v>
       </c>
       <c r="X23" t="n">
-        <v>0.05427412039025081</v>
+        <v>0.05427422436897911</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.005592337497393185</v>
+        <v>0.005592406437019193</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.07048457485849391</v>
+        <v>0.07048448522790407</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.05002295045172356</v>
+        <v>0.05002302918917612</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.05350405039973083</v>
+        <v>0.05350382801728193</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.08447706818431255</v>
+        <v>0.08447687597342801</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.005002615003297128</v>
+        <v>-0.00500254712521031</v>
       </c>
       <c r="AE23" t="n">
         <v>-0.01529860225634982</v>
@@ -3240,70 +3240,70 @@
         <v>44439</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0184772853085784</v>
+        <v>0.01847718294588363</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01799769061415746</v>
+        <v>0.01799778182815848</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.02615467347048051</v>
+        <v>-0.0261545827880505</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.001086478414614955</v>
+        <v>-0.001086478480242126</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01786943313747758</v>
+        <v>0.01786931647563605</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02325078631535904</v>
+        <v>0.02325072256464522</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1031296264748782</v>
+        <v>-0.1031296151911221</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.05796002265996847</v>
+        <v>-0.05796026511897179</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05951826609660071</v>
+        <v>0.05951809594577928</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0346919927614997</v>
+        <v>0.03469190001728761</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.01669636844613276</v>
+        <v>-0.01669618193968769</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0728193065801247</v>
+        <v>-0.07281946490136826</v>
       </c>
       <c r="N24" t="n">
-        <v>0.04912255948646571</v>
+        <v>0.04912289318105234</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.03975129887899542</v>
+        <v>-0.03975140691409518</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.08765563433236878</v>
+        <v>-0.08765553038384244</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.03234867024245447</v>
+        <v>-0.03234882470568479</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01108463489135358</v>
+        <v>0.01108457212836078</v>
       </c>
       <c r="S24" t="n">
         <v>0.005153574310905684</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1702336460302138</v>
+        <v>0.1702333885924958</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.01569074680182447</v>
+        <v>-0.01569068723797717</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.01917067768303338</v>
+        <v>-0.01917075819319736</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.04843760320850365</v>
+        <v>-0.04843739662608715</v>
       </c>
       <c r="X24" t="n">
         <v>-0.005576994299802185</v>
@@ -3312,22 +3312,22 @@
         <v>-0.0004119131949867905</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.0226338259688299</v>
+        <v>0.02263366953688006</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.03846146256252148</v>
+        <v>-0.03846161436054352</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.006795467623571749</v>
+        <v>-0.006795261173430212</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.02293392857047905</v>
+        <v>0.02293419849276512</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.01984651325723918</v>
+        <v>-0.01984644368396538</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.03753401692497871</v>
+        <v>-0.03753391430208119</v>
       </c>
       <c r="AF24" t="n">
         <v>72.98999786376953</v>
@@ -3359,94 +3359,94 @@
         <v>44469</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0794493940113925</v>
+        <v>-0.07944930149087037</v>
       </c>
       <c r="C25" t="n">
         <v>-0.138121537235661</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.06114275136118097</v>
+        <v>-0.06114294259871533</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.07287903401606122</v>
+        <v>-0.07287897795376208</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1016204502601943</v>
+        <v>-0.1016205065610163</v>
       </c>
       <c r="G25" t="n">
         <v>0.04534654943501604</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0618145428301089</v>
+        <v>-0.06181471828094987</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.03881723160873829</v>
+        <v>-0.03881697595328437</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1676142759270095</v>
+        <v>-0.1676143372865088</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.02139569153324927</v>
+        <v>-0.02139551418180985</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.01734096798784412</v>
+        <v>-0.01734090368988017</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.04013238827324994</v>
+        <v>-0.04013230322531203</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0906353116932741</v>
+        <v>-0.09063540504989187</v>
       </c>
       <c r="O25" t="n">
-        <v>0.03122103285632805</v>
+        <v>0.03122114887635452</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.0957445499463021</v>
+        <v>-0.09574465297320112</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.08362406056515359</v>
+        <v>-0.08362406734920913</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.07595927314495787</v>
+        <v>-0.07595921578520493</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1151645761889102</v>
+        <v>0.1151646544839573</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.08021615374954882</v>
+        <v>-0.08021602732110233</v>
       </c>
       <c r="U25" t="n">
         <v>-0.03265937689486653</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.08545461724052927</v>
+        <v>-0.08545446008742252</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1041050865856126</v>
+        <v>-0.1041051306262371</v>
       </c>
       <c r="X25" t="n">
         <v>0.0690250331772877</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.01298177197981976</v>
+        <v>0.01298170377675167</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.1118713023408642</v>
+        <v>-0.111871089999255</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.05636363636363639</v>
+        <v>-0.05636371845600674</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.06409797745201162</v>
+        <v>0.06409790338774535</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.003865448200187194</v>
+        <v>0.003865361232985975</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.02470295642168363</v>
+        <v>-0.02470302258368173</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.009839031495627149</v>
+        <v>0.009839137071490311</v>
       </c>
       <c r="AF25" t="n">
         <v>78.51999664306641</v>
@@ -3484,76 +3484,76 @@
         <v>0.2307692936139063</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1189895256577844</v>
+        <v>0.1189898554327622</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.01642546264017153</v>
+        <v>-0.01642539741757654</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04386556807374919</v>
+        <v>0.04386569616139213</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01117633415727082</v>
+        <v>0.01117645064779804</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07297209437498897</v>
+        <v>0.07297216413561647</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1808853824126739</v>
+        <v>0.1808852749340297</v>
       </c>
       <c r="J26" t="n">
-        <v>0.236611963786463</v>
+        <v>0.2366120523454402</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.05146319199289673</v>
+        <v>-0.0514633704678098</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02132338146666579</v>
+        <v>0.02132331463879611</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0409110688256733</v>
+        <v>0.04091097651730502</v>
       </c>
       <c r="N26" t="n">
-        <v>0.01507907343779369</v>
+        <v>0.01507896054428226</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.06073520001789257</v>
+        <v>-0.06073498181556336</v>
       </c>
       <c r="P26" t="n">
-        <v>0.02536758114076565</v>
+        <v>0.02536751814107574</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.04631471110008234</v>
+        <v>0.04631498078659946</v>
       </c>
       <c r="R26" t="n">
         <v>0.0597458157708477</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0651424671797336</v>
+        <v>-0.06514246260611978</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1554449749528968</v>
+        <v>0.1554449638232005</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.04019294872813362</v>
+        <v>-0.04019301228173311</v>
       </c>
       <c r="V26" t="n">
-        <v>0.08101404725043793</v>
+        <v>0.08101386047189574</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.01832835453204196</v>
+        <v>-0.01832841547910014</v>
       </c>
       <c r="X26" t="n">
         <v>0.08353501264987351</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.04404617235541886</v>
+        <v>0.04404630997904979</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.01223381882680319</v>
+        <v>-0.01223390389231538</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.04142590587823447</v>
+        <v>-0.04142573549056183</v>
       </c>
       <c r="AB26" t="n">
         <v>0.09138518801575124</v>
@@ -3562,10 +3562,10 @@
         <v>-0.04480363711270952</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.03716850990480169</v>
+        <v>-0.03716857861590339</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.01451344237702168</v>
+        <v>0.01451333372611363</v>
       </c>
       <c r="AF26" t="n">
         <v>84.37999725341797</v>
@@ -3597,94 +3597,94 @@
         <v>44530</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1000352554036121</v>
+        <v>0.1000354817625437</v>
       </c>
       <c r="C27" t="n">
         <v>0.07291659060661071</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.04786511143448069</v>
+        <v>-0.04786519809394396</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0164591184788232</v>
+        <v>0.01645911738738959</v>
       </c>
       <c r="F27" t="n">
-        <v>0.005799218189791011</v>
+        <v>0.005799217841630178</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.06219555452436087</v>
+        <v>-0.06219566256221531</v>
       </c>
       <c r="H27" t="n">
         <v>0.02872235745240426</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0266730041876504</v>
+        <v>0.02667277296627502</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1825202483780994</v>
+        <v>0.1825200920786678</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.03021269339076693</v>
+        <v>-0.0302126963082201</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03815711902622998</v>
+        <v>0.03815705495971566</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3155772639164759</v>
+        <v>-0.3155772032216159</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.04347818833708461</v>
+        <v>-0.04347808195609326</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.006334679115793329</v>
+        <v>-0.006334677644172726</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.04302620412839808</v>
+        <v>-0.04302614533089244</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0659949303333307</v>
+        <v>0.06599458072540432</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.01919238635976095</v>
+        <v>-0.01919232296938767</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01960785786308272</v>
+        <v>0.01960785639049889</v>
       </c>
       <c r="T27" t="n">
-        <v>0.00899494204143636</v>
+        <v>0.00899487951749367</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.01172521527150394</v>
+        <v>-0.01172521604788879</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0317239662650306</v>
+        <v>0.03172405192624494</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1011949221028272</v>
+        <v>0.1011947956145502</v>
       </c>
       <c r="X27" t="n">
-        <v>0.01032135005698431</v>
+        <v>0.01032126884214679</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.02542196466930602</v>
+        <v>-0.02542209200696144</v>
       </c>
       <c r="Z27" t="n">
         <v>-0.04357794065810028</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.04170863725423546</v>
+        <v>0.04170854271356794</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.02094077982562192</v>
+        <v>-0.02094089969202129</v>
       </c>
       <c r="AC27" t="n">
         <v>0.0656210913798132</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.03299309008446238</v>
+        <v>0.03299301596600523</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.02250895050164436</v>
+        <v>-0.02250905223460176</v>
       </c>
       <c r="AF27" t="n">
         <v>70.56999969482422</v>
@@ -3716,94 +3716,94 @@
         <v>44561</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1059879381306787</v>
+        <v>0.1059877105468852</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04854368631706563</v>
+        <v>0.04854376365262669</v>
       </c>
       <c r="D28" t="n">
-        <v>0.04084546436704217</v>
+        <v>0.04084536877558631</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08825845170177016</v>
+        <v>0.08825844594396237</v>
       </c>
       <c r="F28" t="n">
-        <v>0.127567639711379</v>
+        <v>0.1275675724072685</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06152630572278972</v>
+        <v>0.06152618287950307</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1232347297949843</v>
+        <v>0.1232348476004153</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04466718966416794</v>
+        <v>0.04466750000957154</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.07677910095406648</v>
+        <v>-0.07677910560385937</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0946687274120559</v>
+        <v>0.09466873683842625</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02427160979597831</v>
+        <v>0.02427173471737221</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3527555528173187</v>
+        <v>0.3527556823868891</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0882573549733674</v>
+        <v>0.08825747124512273</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1130001442501807</v>
+        <v>0.1129998840387796</v>
       </c>
       <c r="P28" t="n">
-        <v>0.06444363291205546</v>
+        <v>0.06444356870854384</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.08478200339838859</v>
+        <v>0.08478217560090506</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1035467375313144</v>
+        <v>0.103546666208219</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0315533812529103</v>
+        <v>0.0315533052713175</v>
       </c>
       <c r="T28" t="n">
         <v>0.06007752675906386</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.02415256673156341</v>
+        <v>-0.02415250134922409</v>
       </c>
       <c r="V28" t="n">
         <v>0.1256685703396394</v>
       </c>
       <c r="W28" t="n">
-        <v>0.09020015724959096</v>
+        <v>0.09020039733955265</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.04441914812958214</v>
+        <v>-0.04441907131506184</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.02107690091481706</v>
+        <v>0.02107690230949122</v>
       </c>
       <c r="Z28" t="n">
         <v>0.1232613627309971</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.03473218494779795</v>
+        <v>0.0347320978261314</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.001316185680308668</v>
+        <v>-0.001316185841449546</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.01417932165874913</v>
+        <v>0.01417932267613198</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.07281749337876153</v>
+        <v>0.07281738690658401</v>
       </c>
       <c r="AF28" t="n">
         <v>77.77999877929688</v>
@@ -3838,91 +3838,91 @@
         <v>-0.07701222574723521</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.212962935646218</v>
+        <v>-0.212962919939093</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1451702432608121</v>
+        <v>-0.1451699810726514</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.08399692374999168</v>
+        <v>-0.08399703860898544</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.131991117654551</v>
+        <v>-0.1319910117812619</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01750106031438547</v>
+        <v>0.01750094661639023</v>
       </c>
       <c r="H29" t="n">
-        <v>0.06714303394143051</v>
+        <v>0.06714292201893701</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1404886988358284</v>
+        <v>-0.1404886168785396</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2705882870001022</v>
+        <v>-0.2705881735556246</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1504158327438303</v>
+        <v>0.1504159373868104</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.1134054960726415</v>
+        <v>-0.1134055494894435</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1172445830515747</v>
+        <v>-0.1172447633855508</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.135398492371791</v>
+        <v>-0.1353985313265959</v>
       </c>
       <c r="O29" t="n">
-        <v>0.02953729504662772</v>
+        <v>0.02953719001841248</v>
       </c>
       <c r="P29" t="n">
-        <v>0.009855776016375106</v>
+        <v>0.009855836927342265</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.1203073254968346</v>
+        <v>-0.1203072523282783</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.2035463964427219</v>
+        <v>-0.2035463378762923</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.00506785632119644</v>
+        <v>-0.00506771351238422</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.3597075625987406</v>
+        <v>-0.3597074467314713</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.04646124348195713</v>
+        <v>-0.04646117482309875</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.04077594623020653</v>
+        <v>-0.04077601772042294</v>
       </c>
       <c r="W29" t="n">
-        <v>0.001244102550378656</v>
+        <v>0.001243997058321566</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.05125144174201379</v>
+        <v>-0.05125152586378545</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.008992385689430282</v>
+        <v>0.008992515881887542</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.03458579178634313</v>
+        <v>-0.03458571063142424</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.0545454591380351</v>
+        <v>-0.0545453795332993</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.003075453864514244</v>
+        <v>-0.0030752703542124</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.04531365914330121</v>
+        <v>0.04531357436024819</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.03403474321374511</v>
+        <v>0.03403495786566824</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.006677725248302013</v>
+        <v>-0.006677725911035437</v>
       </c>
       <c r="AF29" t="n">
         <v>91.20999908447266</v>
@@ -3957,28 +3957,28 @@
         <v>0.005018907076441259</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.07647052484154393</v>
+        <v>-0.07647061138779199</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.004815318773135902</v>
+        <v>-0.004815532612067019</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.005533709153833222</v>
+        <v>-0.005533774960298166</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0898379941803219</v>
+        <v>-0.08983792223626463</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06201452436310473</v>
+        <v>0.06201465220212365</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1338687583084797</v>
+        <v>0.1338688565900654</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.09111658182599536</v>
+        <v>-0.09111673380484031</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.107619497705171</v>
+        <v>-0.1076195779583484</v>
       </c>
       <c r="K30" t="n">
         <v>-0.2343204937823749</v>
@@ -3987,61 +3987,61 @@
         <v>-0.06567383849426345</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.03047371928567444</v>
+        <v>-0.03047361408877591</v>
       </c>
       <c r="N30" t="n">
-        <v>0.03663458441985656</v>
+        <v>0.03663452036938941</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.1247954217314123</v>
+        <v>-0.1247953324474352</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.09759504086966597</v>
+        <v>-0.09759510059749932</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.03119541631816281</v>
+        <v>-0.03119549689860746</v>
       </c>
       <c r="R30" t="n">
-        <v>0.005565936515586456</v>
+        <v>0.005565789038285418</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.03874832385563587</v>
+        <v>-0.03874860536627356</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.03015072785247352</v>
+        <v>-0.03015081287634569</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3028234456835099</v>
+        <v>0.3028232078661486</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.1460998451506486</v>
+        <v>-0.1460997815101349</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.03386135327765893</v>
+        <v>-0.03386145850773026</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.08123963272400858</v>
+        <v>-0.08123946259512205</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.08041327693748856</v>
+        <v>-0.08041327177276181</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.04688186946439388</v>
+        <v>-0.04688203364794197</v>
       </c>
       <c r="AA30" t="n">
         <v>-0.1331360174761232</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.1543460636100247</v>
+        <v>-0.1543460541200788</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.06817334610726533</v>
+        <v>-0.06817327052888345</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.03537295125037765</v>
+        <v>-0.03537294640998823</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.117502973148198</v>
+        <v>-0.1175028849756463</v>
       </c>
       <c r="AF30" t="n">
         <v>100.9899978637695</v>
@@ -4079,88 +4079,88 @@
         <v>0.1592355414649105</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04935476993082677</v>
+        <v>0.0493548778875037</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01311602409406243</v>
+        <v>0.0131160916288382</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.005461054049566427</v>
+        <v>-0.005461186963721998</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08892767270070623</v>
+        <v>0.08892778931570722</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1289256076567964</v>
+        <v>0.128925596481771</v>
       </c>
       <c r="I31" t="n">
         <v>0.1292933085857846</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1595513118516061</v>
+        <v>0.1595511102972795</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.003699573484386653</v>
+        <v>-0.003699470219342138</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.06217716710163212</v>
+        <v>-0.06217723983426848</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1205488097014061</v>
+        <v>-0.1205488656583157</v>
       </c>
       <c r="N31" t="n">
         <v>0.0310679079270717</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.2136358518263638</v>
+        <v>-0.2136357935457219</v>
       </c>
       <c r="P31" t="n">
-        <v>0.01931248902530247</v>
+        <v>0.01931249030354598</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.06208134142793198</v>
+        <v>0.0620811697212007</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1111622431295545</v>
+        <v>0.1111623243855138</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.07307314235320173</v>
+        <v>-0.07307307860352641</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2370468535135004</v>
+        <v>0.2370465515203415</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1946869014835995</v>
+        <v>0.1946872546106666</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.02851616975585947</v>
+        <v>-0.02851625703680827</v>
       </c>
       <c r="W31" t="n">
-        <v>0.1797426764226866</v>
+        <v>0.1797426959999355</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.01347447938063895</v>
+        <v>-0.01347467109256739</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.01057467773790943</v>
+        <v>0.01057467699933534</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0259732596899096</v>
+        <v>0.02597335017780988</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.08441926409634803</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.01197824086568888</v>
+        <v>-0.01197831270166616</v>
       </c>
       <c r="AC31" t="n">
         <v>0.1316102503075183</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0686677577332786</v>
+        <v>0.06866767706399957</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.03906860569024651</v>
+        <v>-0.03906837925873796</v>
       </c>
       <c r="AF31" t="n">
         <v>107.9100036621094</v>
@@ -4192,76 +4192,76 @@
         <v>44681</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.02028129628462938</v>
+        <v>-0.02028140111215715</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.03571417004480937</v>
+        <v>-0.03571425757846713</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1297853828753824</v>
+        <v>-0.1297853695231801</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.007018745213111521</v>
+        <v>-0.007018615756006708</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.07284817336869742</v>
+        <v>-0.0728483032084396</v>
       </c>
       <c r="G32" t="n">
         <v>0.05484377702975873</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.07526074051927512</v>
+        <v>-0.07526081152008535</v>
       </c>
       <c r="I32" t="n">
-        <v>0.004618548417577584</v>
+        <v>0.004618629874894697</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2356893200575834</v>
+        <v>-0.2356891872043414</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.08053301862884854</v>
+        <v>-0.08053301028172277</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1746173622024252</v>
+        <v>0.1746175308543931</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06170764006594576</v>
+        <v>0.06170764399222284</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.03201508496478433</v>
+        <v>-0.03201514277221551</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.007925164955669417</v>
+        <v>-0.007925238482360486</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.02597614010335569</v>
+        <v>-0.0259760768567</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.07281093109331949</v>
+        <v>-0.07281094286466749</v>
       </c>
       <c r="R32" t="n">
         <v>-0.1311747501656305</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01767715068147124</v>
+        <v>0.01767723265224452</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.07244179808928186</v>
+        <v>-0.07244158276852586</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2428383686683904</v>
+        <v>0.2428380461640351</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.03882615906132836</v>
+        <v>-0.03882616254958426</v>
       </c>
       <c r="W32" t="n">
-        <v>0.06631517809653853</v>
+        <v>0.06631527654269198</v>
       </c>
       <c r="X32" t="n">
-        <v>0.08882377051986756</v>
+        <v>0.08882387703329031</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1505178726056129</v>
+        <v>0.1505179313157003</v>
       </c>
       <c r="Z32" t="n">
         <v>-0.103358549829537</v>
@@ -4270,16 +4270,16 @@
         <v>0.05456332564920063</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.1131205143766232</v>
+        <v>0.1131205879649653</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.02707328826682387</v>
+        <v>0.02707336518525616</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.1120863781205799</v>
+        <v>0.112086237939766</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.02868492339187989</v>
+        <v>-0.0286851522701197</v>
       </c>
       <c r="AF32" t="n">
         <v>109.3399963378906</v>
@@ -4311,52 +4311,52 @@
         <v>44712</v>
       </c>
       <c r="B33" t="n">
-        <v>0.003338859401545324</v>
+        <v>0.003338966756384121</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.06039902063983749</v>
+        <v>-0.06039893534695495</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.04803168698796279</v>
+        <v>-0.04803179953219294</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.04302785711968127</v>
+        <v>-0.04302785430498668</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.03217518358926985</v>
+        <v>-0.03217525859498038</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.02239085320300405</v>
+        <v>-0.02239075997032591</v>
       </c>
       <c r="H33" t="n">
         <v>-0.009121957801002556</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06299600902192459</v>
+        <v>-0.06299616607968106</v>
       </c>
       <c r="J33" t="n">
-        <v>0.006329036917278374</v>
+        <v>0.006329150628213043</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.002016342894851531</v>
+        <v>-0.002016455394266203</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01839069425153061</v>
+        <v>-0.0183906930372747</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.004871448697299385</v>
+        <v>-0.004871389060235876</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.07391535773294833</v>
+        <v>-0.07391530242777089</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1045201386784667</v>
+        <v>0.1045200639723456</v>
       </c>
       <c r="P33" t="n">
         <v>0.01037928492244755</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.02651458251472238</v>
+        <v>-0.02651432558925393</v>
       </c>
       <c r="R33" t="n">
         <v>-0.03320501469083204</v>
@@ -4365,13 +4365,13 @@
         <v>0.00201977318293034</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.1217628858309826</v>
+        <v>-0.1217630385423</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.009073545874995648</v>
+        <v>-0.009073472105747271</v>
       </c>
       <c r="V33" t="n">
-        <v>0.06241701431272628</v>
+        <v>0.06241711361907121</v>
       </c>
       <c r="W33" t="n">
         <v>-0.07962529395665552</v>
@@ -4380,22 +4380,22 @@
         <v>-0.03361720146161828</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.03900778983209963</v>
+        <v>-0.0390078452166549</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.1115801360007064</v>
+        <v>-0.1115800401269866</v>
       </c>
       <c r="AA33" t="n">
         <v>0.06128727819811264</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.05989151621584532</v>
+        <v>-0.05989157836636638</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.08326938275453033</v>
+        <v>-0.08326945140929665</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.02103730667281301</v>
+        <v>-0.02103712888438125</v>
       </c>
       <c r="AE33" t="n">
         <v>0.07965137199482952</v>
@@ -4430,37 +4430,37 @@
         <v>44742</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.09251247519118422</v>
+        <v>-0.09251236854966793</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1910247858959003</v>
+        <v>-0.1910248342013172</v>
       </c>
       <c r="D34" t="n">
         <v>-0.06449168610461631</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0953372192403048</v>
+        <v>-0.09533721272334927</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1259374448371392</v>
+        <v>-0.1259373135818821</v>
       </c>
       <c r="G34" t="n">
-        <v>0.04736025052042336</v>
+        <v>0.04736015063572818</v>
       </c>
       <c r="H34" t="n">
         <v>-0.2058823258318762</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1638433029457173</v>
+        <v>-0.1638433171237573</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2646027271757564</v>
+        <v>-0.2646028667704193</v>
       </c>
       <c r="K34" t="n">
         <v>-0.03687342456741827</v>
       </c>
       <c r="L34" t="n">
-        <v>0.04254491962459417</v>
+        <v>0.0425448495003502</v>
       </c>
       <c r="M34" t="n">
         <v>-0.08938716209603959</v>
@@ -4469,25 +4469,25 @@
         <v>-0.1063919724408131</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.09255672759472722</v>
+        <v>-0.09255673385496133</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.101145799710901</v>
+        <v>-0.1011457337306576</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.08108407520498584</v>
+        <v>-0.08108406794330225</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.1824290475442056</v>
+        <v>-0.1824289691952132</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.09292473538531199</v>
+        <v>-0.09292465639703174</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.09753231699058418</v>
+        <v>-0.09753232601995798</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01831333306237748</v>
+        <v>0.01831318280961103</v>
       </c>
       <c r="V34" t="n">
         <v>-0.1707500223030822</v>
@@ -4499,22 +4499,22 @@
         <v>-0.06864570579096951</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.09013323001781015</v>
+        <v>-0.09013334940241335</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.06888357635943332</v>
+        <v>-0.06888367684073626</v>
       </c>
       <c r="AA34" t="n">
         <v>-0.1265235191291805</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.1236869371545538</v>
+        <v>-0.1236868668329351</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.02469650269510781</v>
+        <v>-0.02469658438856082</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.02098936010409691</v>
+        <v>-0.02098960140021711</v>
       </c>
       <c r="AE34" t="n">
         <v>-0.07412584010678591</v>
@@ -4549,16 +4549,16 @@
         <v>44773</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1265125382768986</v>
+        <v>0.1265125234100415</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2968516144087352</v>
+        <v>0.2968516918461654</v>
       </c>
       <c r="D35" t="n">
         <v>0.2246553309799624</v>
       </c>
       <c r="E35" t="n">
-        <v>0.09940174869969609</v>
+        <v>0.09940166562821173</v>
       </c>
       <c r="F35" t="n">
         <v>0.2349062817057701</v>
@@ -4567,13 +4567,13 @@
         <v>0.005559674811198345</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03565386254134384</v>
+        <v>0.0356539680576744</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1313706322162518</v>
+        <v>0.1313707493021905</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3065903873177516</v>
+        <v>0.3065903340456162</v>
       </c>
       <c r="K35" t="n">
         <v>0.007866955000886078</v>
@@ -4582,58 +4582,58 @@
         <v>-0.03406971650291002</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05192998537118299</v>
+        <v>0.05192991923729107</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1195293874498653</v>
+        <v>0.1195294596133236</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05861157242363069</v>
+        <v>0.05861165132776036</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1472528130751038</v>
+        <v>0.1472526554563791</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1226068109469702</v>
+        <v>0.1226067989977224</v>
       </c>
       <c r="R35" t="n">
-        <v>0.1963470976014352</v>
+        <v>0.196346887122375</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1101111500166019</v>
+        <v>0.1101109662677524</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3255207470456729</v>
+        <v>0.3255208830222078</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.1325130748295605</v>
+        <v>-0.1325128730559834</v>
       </c>
       <c r="V35" t="n">
-        <v>0.1223997182923158</v>
+        <v>0.1223998243889128</v>
       </c>
       <c r="W35" t="n">
         <v>-0.03239534350213336</v>
       </c>
       <c r="X35" t="n">
-        <v>0.09213154384953026</v>
+        <v>0.09213144402782181</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.04232443676115194</v>
+        <v>0.04232457707231818</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.09948971106420323</v>
+        <v>0.09948982696257369</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.1308971324459272</v>
+        <v>0.1308970176693889</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.08430002384142576</v>
+        <v>0.08429993682945502</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.004721082313334568</v>
+        <v>-0.004721082708782243</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.043644773146016</v>
+        <v>-0.04364490312334479</v>
       </c>
       <c r="AE35" t="n">
         <v>0.146356760176694</v>
@@ -4668,16 +4668,16 @@
         <v>44804</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.04329413914836255</v>
+        <v>-0.04329423894778028</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1225353030956293</v>
+        <v>-0.1225353951830541</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.05463582009500334</v>
+        <v>-0.05463571169812598</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.09292588939271729</v>
+        <v>-0.09292602685044216</v>
       </c>
       <c r="F36" t="n">
         <v>-0.07863075838776967</v>
@@ -4686,73 +4686,73 @@
         <v>-0.02082148042872844</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01958736050200183</v>
+        <v>0.01958735850636772</v>
       </c>
       <c r="I36" t="n">
         <v>-0.08421939057117644</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1217105131633569</v>
+        <v>-0.1217105274762984</v>
       </c>
       <c r="K36" t="n">
-        <v>0.04045796961003556</v>
+        <v>0.04045773688297949</v>
       </c>
       <c r="L36" t="n">
         <v>-0.0810077131564495</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.1225470913139107</v>
+        <v>-0.1225469732801276</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.07986554421647463</v>
+        <v>-0.07986553906844229</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.1412002447125342</v>
+        <v>-0.1412001743038179</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.1003832078048166</v>
+        <v>-0.1003830862613672</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.1064619366918976</v>
+        <v>-0.1064618406336227</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.1529262159891124</v>
+        <v>-0.1529261481356461</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.007606908265662682</v>
+        <v>-0.007606830419602861</v>
       </c>
       <c r="T36" t="n">
         <v>-0.0152259196323119</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.02673215348319546</v>
+        <v>-0.02673215120976313</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.05766659646493311</v>
+        <v>-0.05766659101390803</v>
       </c>
       <c r="W36" t="n">
         <v>0.08454518325943483</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.02735973585896923</v>
+        <v>-0.02735973835967154</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.03884979061731997</v>
+        <v>-0.03884991988066233</v>
       </c>
       <c r="Z36" t="n">
-        <v>-0.0826564977324501</v>
+        <v>-0.08265669984163049</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.05669806883849182</v>
+        <v>-0.05669797310127755</v>
       </c>
       <c r="AB36" t="n">
         <v>-0.01355201980342224</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.02026735255461254</v>
+        <v>-0.02026727010088691</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.00293580084373013</v>
+        <v>0.00293586672106616</v>
       </c>
       <c r="AE36" t="n">
         <v>-0.06763593222212028</v>
@@ -4787,52 +4787,52 @@
         <v>44834</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.002041487011157472</v>
+        <v>-0.002041596047477001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.01798815251550467</v>
+        <v>-0.01798794450897534</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.02486858931838665</v>
+        <v>-0.02486881578989608</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.03230272961615077</v>
+        <v>-0.032302658741443</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.03623309803961838</v>
+        <v>-0.03623317353735034</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.06779661487174815</v>
+        <v>-0.06779670734946297</v>
       </c>
       <c r="H37" t="n">
-        <v>0.008732475517761573</v>
+        <v>0.008732274792207839</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.02138703323398028</v>
+        <v>-0.02138713311971108</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.08822308608043772</v>
+        <v>-0.08822296399841467</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1656646845856218</v>
+        <v>-0.1656644979635276</v>
       </c>
       <c r="L37" t="n">
         <v>-0.06874737894067406</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0329645220835717</v>
+        <v>0.03296437642260153</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.04339870433038517</v>
+        <v>-0.04339884139736772</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.06843133959425618</v>
+        <v>-0.06843141596892632</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.04897783583283244</v>
+        <v>-0.04897790347205144</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.03034961681263582</v>
+        <v>-0.03034970807461379</v>
       </c>
       <c r="R37" t="n">
         <v>-0.06158012679059632</v>
@@ -4841,37 +4841,37 @@
         <v>-0.03509832090695131</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.00149630869917261</v>
+        <v>-0.001496230111530772</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.02578474679987686</v>
+        <v>-0.0257848319275229</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.0862532662572566</v>
+        <v>-0.08625345822742148</v>
       </c>
       <c r="W37" t="n">
         <v>-0.1144372345619784</v>
       </c>
       <c r="X37" t="n">
-        <v>0.001406382793978755</v>
+        <v>0.001406476898003772</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.04612920726005032</v>
+        <v>0.04612921042341545</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.1179260849940753</v>
+        <v>-0.1179259261812794</v>
       </c>
       <c r="AA37" t="n">
         <v>-0.06415453371529867</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.06182208830095637</v>
+        <v>0.0618221633259417</v>
       </c>
       <c r="AC37" t="n">
         <v>-0.1549295823042468</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1476851574730713</v>
+        <v>-0.1476849265487573</v>
       </c>
       <c r="AE37" t="n">
         <v>-0.06616260147094988</v>
@@ -4906,67 +4906,67 @@
         <v>44865</v>
       </c>
       <c r="B38" t="n">
-        <v>0.09062212613710319</v>
+        <v>0.09062213603842095</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.09362274175306451</v>
+        <v>-0.09362283861717668</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.02262936660349968</v>
+        <v>-0.02262919288582954</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06342400788753988</v>
+        <v>0.06342401285358412</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1362664141528875</v>
+        <v>0.1362665031635641</v>
       </c>
       <c r="G38" t="n">
-        <v>0.05252530603494754</v>
+        <v>0.0525253112456352</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.07199537264236266</v>
+        <v>-0.07199537977432813</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06512553171401381</v>
+        <v>0.06512574249866598</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.006846155275119004</v>
+        <v>-0.00684622870020779</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.06245219189260287</v>
+        <v>-0.06245225891527162</v>
       </c>
       <c r="L38" t="n">
-        <v>0.05706519194135407</v>
+        <v>0.05706511389483948</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1648623841056571</v>
+        <v>0.1648626036301002</v>
       </c>
       <c r="N38" t="n">
-        <v>0.04297995045723724</v>
+        <v>0.04297995360473572</v>
       </c>
       <c r="O38" t="n">
         <v>0.07481138454354341</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1110613870703967</v>
+        <v>0.1110613122849076</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1025797132961623</v>
+        <v>0.102579602817078</v>
       </c>
       <c r="R38" t="n">
-        <v>0.02144693176765933</v>
+        <v>0.02144703253790681</v>
       </c>
       <c r="S38" t="n">
         <v>0.1029580229275653</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.1198800655490131</v>
+        <v>-0.1198801348192073</v>
       </c>
       <c r="U38" t="n">
         <v>0.1225547318506166</v>
       </c>
       <c r="V38" t="n">
-        <v>0.1314322060896758</v>
+        <v>0.13143233029839</v>
       </c>
       <c r="W38" t="n">
         <v>-0.08239433451446299</v>
@@ -4975,22 +4975,22 @@
         <v>0.09082396107521729</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1203885101495288</v>
+        <v>0.1203885835935814</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.2315414497647299</v>
+        <v>0.2315413695474</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.06356059690675298</v>
+        <v>0.0635607118742707</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.1212121490466309</v>
+        <v>0.1212120698253378</v>
       </c>
       <c r="AC38" t="n">
         <v>-0.02188823594227818</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.05253616012830931</v>
+        <v>-0.05253607995507104</v>
       </c>
       <c r="AE38" t="n">
         <v>0.1437247501295831</v>
@@ -5025,73 +5025,73 @@
         <v>44895</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06681877447854645</v>
+        <v>0.0668189815340765</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1519461497937309</v>
+        <v>0.1519460318852761</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09408317097742946</v>
+        <v>0.09408310516384977</v>
       </c>
       <c r="E39" t="n">
-        <v>0.07805061834584803</v>
+        <v>0.07805069772191797</v>
       </c>
       <c r="F39" t="n">
-        <v>0.09420526055190015</v>
+        <v>0.09420532949355875</v>
       </c>
       <c r="G39" t="n">
-        <v>0.08944328126122203</v>
+        <v>0.08944347819694154</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2061567013817613</v>
+        <v>0.2061568301350238</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1824904141017947</v>
+        <v>0.1824902049584769</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08733252634927635</v>
+        <v>0.08733268066835609</v>
       </c>
       <c r="K39" t="n">
-        <v>0.06058633230482324</v>
+        <v>0.06058633663597068</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0951157043898494</v>
+        <v>0.09511578524576114</v>
       </c>
       <c r="M39" t="n">
-        <v>0.03291387464876716</v>
+        <v>0.03291375163677346</v>
       </c>
       <c r="N39" t="n">
-        <v>0.08195966108271224</v>
+        <v>0.08195980726540664</v>
       </c>
       <c r="O39" t="n">
-        <v>0.07874679248515037</v>
+        <v>0.07874671060334926</v>
       </c>
       <c r="P39" t="n">
-        <v>0.07255137835974268</v>
+        <v>0.07255138324317278</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.07612228545432198</v>
+        <v>0.07612219457603864</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1250391411383576</v>
+        <v>0.1250389314938891</v>
       </c>
       <c r="S39" t="n">
-        <v>0.03771801809021613</v>
+        <v>0.0377180923625533</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1121454692698152</v>
+        <v>0.1121453798440379</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.005638227992793232</v>
+        <v>-0.005638148091595907</v>
       </c>
       <c r="V39" t="n">
         <v>0.1066049157636153</v>
       </c>
       <c r="W39" t="n">
-        <v>0.08288576109326917</v>
+        <v>0.08288563341308652</v>
       </c>
       <c r="X39" t="n">
-        <v>0.027897051274695</v>
+        <v>0.02789696524809093</v>
       </c>
       <c r="Y39" t="n">
         <v>0.02922560427627263</v>
@@ -5100,7 +5100,7 @@
         <v>-0.01949954393310438</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.08479373937813639</v>
+        <v>0.08479362211539621</v>
       </c>
       <c r="AB39" t="n">
         <v>0.02763432372401575</v>
@@ -5109,7 +5109,7 @@
         <v>0.02540877263869223</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.02153842047509824</v>
+        <v>-0.02153841701193027</v>
       </c>
       <c r="AE39" t="n">
         <v>0.0618361158504781</v>
@@ -5144,34 +5144,34 @@
         <v>44926</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.03391380754717588</v>
+        <v>-0.03391389826854097</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.03378818577795839</v>
+        <v>-0.03378808688049362</v>
       </c>
       <c r="D40" t="n">
         <v>0.01142082189539395</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.06126731853955647</v>
+        <v>-0.06126725024104251</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0469185992699982</v>
+        <v>-0.0469185963138381</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.01092306977564261</v>
+        <v>-0.01092315534519828</v>
       </c>
       <c r="H40" t="n">
         <v>0.008636243797260468</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.05027505446225844</v>
+        <v>-0.05027505853649883</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.06207481293366923</v>
+        <v>-0.06207487670621314</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.06480351786808747</v>
+        <v>-0.06480345483259331</v>
       </c>
       <c r="L40" t="n">
         <v>0.06924877153173625</v>
@@ -5180,37 +5180,37 @@
         <v>-0.04835985498822992</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.07744391578654175</v>
+        <v>-0.07744397565599626</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.03788791310203032</v>
+        <v>-0.03788791597789598</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.0492296156632076</v>
+        <v>-0.04922955599584378</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.02300513167493123</v>
+        <v>-0.023005049167929</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.02980504812414064</v>
+        <v>-0.02980496304797009</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01990874903206796</v>
+        <v>0.01990860446164477</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.00898161221949545</v>
+        <v>-0.008981532533339887</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0585052887562223</v>
+        <v>0.05850520370082735</v>
       </c>
       <c r="V40" t="n">
         <v>-0.0136126397208538</v>
       </c>
       <c r="W40" t="n">
-        <v>-0.06484780048568395</v>
+        <v>-0.06484763127068172</v>
       </c>
       <c r="X40" t="n">
-        <v>0.001669987140747509</v>
+        <v>0.001670070972367155</v>
       </c>
       <c r="Y40" t="n">
         <v>-0.005205948713634112</v>
@@ -5225,10 +5225,10 @@
         <v>0.04787234336123691</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.08317162359750352</v>
+        <v>-0.08317172494585212</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.06848365445543769</v>
+        <v>-0.06848364320154254</v>
       </c>
       <c r="AE40" t="n">
         <v>-0.01823103610759436</v>
@@ -5269,73 +5269,73 @@
         <v>0.1190314765358755</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0860180052653523</v>
+        <v>0.08601789654446979</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09700474115022284</v>
+        <v>0.09700473409253818</v>
       </c>
       <c r="F41" t="n">
-        <v>0.001949652272787317</v>
+        <v>0.001949652143900193</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.02885661828700481</v>
+        <v>-0.02885644334698745</v>
       </c>
       <c r="H41" t="n">
         <v>0.1948881548052335</v>
       </c>
       <c r="I41" t="n">
-        <v>0.06873841286684934</v>
+        <v>0.06873850406114457</v>
       </c>
       <c r="J41" t="n">
-        <v>0.06029021644589827</v>
+        <v>0.06029014395268106</v>
       </c>
       <c r="K41" t="n">
         <v>-0.008538622075267899</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.002195289736503403</v>
+        <v>-0.002195352790551497</v>
       </c>
       <c r="M41" t="n">
         <v>0.1524521277555975</v>
       </c>
       <c r="N41" t="n">
-        <v>0.09403667336986854</v>
+        <v>0.09403674371268833</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1414823979922506</v>
+        <v>0.1414824091543181</v>
       </c>
       <c r="P41" t="n">
-        <v>0.08498016906067196</v>
+        <v>0.08498030107331567</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.07313319640354443</v>
+        <v>0.07313328284184228</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0964685481168206</v>
+        <v>0.09646863850047027</v>
       </c>
       <c r="S41" t="n">
-        <v>0.09043689812980493</v>
+        <v>0.09043690447627317</v>
       </c>
       <c r="T41" t="n">
         <v>0.1570546263555979</v>
       </c>
       <c r="U41" t="n">
-        <v>0.03993187876034776</v>
+        <v>0.03993180284740339</v>
       </c>
       <c r="V41" t="n">
         <v>0.1433122109006473</v>
       </c>
       <c r="W41" t="n">
-        <v>0.09662749732970721</v>
+        <v>0.09662742819634795</v>
       </c>
       <c r="X41" t="n">
-        <v>0.0516883040709446</v>
+        <v>0.05168838762326167</v>
       </c>
       <c r="Y41" t="n">
         <v>0.0356803173036504</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.1139394574860144</v>
+        <v>0.1139395676245896</v>
       </c>
       <c r="AA41" t="n">
         <v>0.1583412005507667</v>
@@ -5344,10 +5344,10 @@
         <v>0.130287714200874</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.05992931038828209</v>
+        <v>0.05992953809770118</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.0120031771611333</v>
+        <v>0.01200308683818463</v>
       </c>
       <c r="AE41" t="n">
         <v>0.09746398139412138</v>
@@ -5382,91 +5382,91 @@
         <v>44985</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.03623783005441661</v>
+        <v>-0.03623800009845546</v>
       </c>
       <c r="C42" t="n">
         <v>0.1298078120066968</v>
       </c>
       <c r="D42" t="n">
-        <v>0.05504589176525054</v>
+        <v>0.05504589727587605</v>
       </c>
       <c r="E42" t="n">
-        <v>0.03952747349388597</v>
+        <v>0.03952747087232567</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01086439875927447</v>
+        <v>0.01086433206325577</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00957767770700646</v>
+        <v>0.009577405774454872</v>
       </c>
       <c r="H42" t="n">
         <v>-0.07989305276205705</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.006900080136195585</v>
+        <v>-0.006900000295410935</v>
       </c>
       <c r="J42" t="n">
-        <v>0.004702701568111811</v>
+        <v>0.004702838631866602</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.03776082727894337</v>
+        <v>-0.03776075458410044</v>
       </c>
       <c r="L42" t="n">
-        <v>0.03777038450401959</v>
+        <v>0.03777045008361357</v>
       </c>
       <c r="M42" t="n">
         <v>0.08237918886252138</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.02599575153897082</v>
+        <v>-0.02599587846069107</v>
       </c>
       <c r="O42" t="n">
-        <v>0.03059628988727803</v>
+        <v>0.03059643023216596</v>
       </c>
       <c r="P42" t="n">
-        <v>0.04772319958991389</v>
+        <v>0.04772319378329626</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.001235439008555828</v>
+        <v>0.001235519456632472</v>
       </c>
       <c r="R42" t="n">
-        <v>0.09766965060792066</v>
+        <v>0.09766956012526973</v>
       </c>
       <c r="S42" t="n">
-        <v>0.08917720166706578</v>
+        <v>0.08917714305057722</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.03515790831871834</v>
+        <v>-0.03515797844253599</v>
       </c>
       <c r="U42" t="n">
-        <v>0.4151251557959752</v>
+        <v>0.4151252590972847</v>
       </c>
       <c r="V42" t="n">
-        <v>0.001856936580220125</v>
+        <v>0.001857014328360274</v>
       </c>
       <c r="W42" t="n">
         <v>0.01105738889809316</v>
       </c>
       <c r="X42" t="n">
-        <v>0.03884268624679565</v>
+        <v>0.03884268316090389</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.02067067692836355</v>
+        <v>0.02067056657646127</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.03699680669758032</v>
+        <v>0.03699670416656864</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.08136709348007232</v>
+        <v>0.0813669997785833</v>
       </c>
       <c r="AB42" t="n">
         <v>0.06686619843010355</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.06807098167200598</v>
+        <v>0.06807087028057102</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.002594383263953004</v>
+        <v>0.002594383037828552</v>
       </c>
       <c r="AE42" t="n">
         <v>0.01426153903615268</v>
@@ -5501,91 +5501,91 @@
         <v>45016</v>
       </c>
       <c r="B43" t="n">
-        <v>0.02520413407787725</v>
+        <v>0.02520431496263043</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0228723955577419</v>
+        <v>0.02287231176747939</v>
       </c>
       <c r="D43" t="n">
-        <v>0.07159416876690106</v>
+        <v>0.07159417556022429</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.02665621442517785</v>
+        <v>-0.0266562765251025</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05502071802830066</v>
+        <v>0.05502084856845757</v>
       </c>
       <c r="G43" t="n">
-        <v>0.04983618409759938</v>
+        <v>0.04983627775835386</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.05195861883589015</v>
+        <v>-0.05195869864465563</v>
       </c>
       <c r="I43" t="n">
-        <v>0.02134002609960173</v>
+        <v>0.02133994398844563</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.1038297585077976</v>
+        <v>-0.1038296833909907</v>
       </c>
       <c r="K43" t="n">
-        <v>0.06801767904078138</v>
+        <v>0.06801752280705786</v>
       </c>
       <c r="L43" t="n">
-        <v>0.07357418679910444</v>
+        <v>0.07357430858476244</v>
       </c>
       <c r="M43" t="n">
-        <v>0.09600485562027949</v>
+        <v>0.09600495274822562</v>
       </c>
       <c r="N43" t="n">
-        <v>0.02324581994817221</v>
+        <v>0.02324582148269005</v>
       </c>
       <c r="O43" t="n">
-        <v>0.119509408399789</v>
+        <v>0.119509333321888</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.02920716967919468</v>
+        <v>-0.02920734048342433</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01702863264276067</v>
+        <v>0.01702846900652921</v>
       </c>
       <c r="R43" t="n">
         <v>0.06393127191327697</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.1600037720740782</v>
+        <v>-0.160003672809405</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0867157865680519</v>
+        <v>0.08671586554954103</v>
       </c>
       <c r="U43" t="n">
-        <v>0.04401044310353219</v>
+        <v>0.04401064944004407</v>
       </c>
       <c r="V43" t="n">
-        <v>0.01853572362037093</v>
+        <v>0.01853564457789569</v>
       </c>
       <c r="W43" t="n">
-        <v>-0.05026418625130713</v>
+        <v>-0.05026424310957411</v>
       </c>
       <c r="X43" t="n">
-        <v>-0.1274323091520463</v>
+        <v>-0.1274324523573689</v>
       </c>
       <c r="Y43" t="n">
-        <v>-0.1193359775159784</v>
+        <v>-0.1193358823011722</v>
       </c>
       <c r="Z43" t="n">
         <v>-0.1270540531109061</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.05977997243459887</v>
+        <v>0.05978015091651145</v>
       </c>
       <c r="AB43" t="n">
         <v>-0.1582897240665401</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.07172530172904534</v>
+        <v>0.0717252040836851</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.02513854413621897</v>
+        <v>-0.02513854195083132</v>
       </c>
       <c r="AE43" t="n">
         <v>0.01930404526256035</v>
@@ -5623,52 +5623,52 @@
         <v>0.03929269601903163</v>
       </c>
       <c r="C44" t="n">
-        <v>0.06604258206797398</v>
+        <v>0.0660427513112396</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03188332469851707</v>
+        <v>0.03188332752169276</v>
       </c>
       <c r="E44" t="n">
         <v>-0.007765062802069123</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1347556280571935</v>
+        <v>0.1347554876512689</v>
       </c>
       <c r="G44" t="n">
         <v>0.04712406184677276</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.06370060964332347</v>
+        <v>-0.06370053082302485</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.003887297344399077</v>
+        <v>-0.003887139912949866</v>
       </c>
       <c r="J44" t="n">
-        <v>0.04368459727751683</v>
+        <v>0.04368443877223638</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.06980205163464437</v>
+        <v>-0.06980191509964018</v>
       </c>
       <c r="L44" t="n">
-        <v>0.04824579514016358</v>
+        <v>0.04824556278832759</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.01501018908405471</v>
+        <v>-0.01501027637384023</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.01682801576542259</v>
+        <v>-0.01682795233806966</v>
       </c>
       <c r="O44" t="n">
         <v>0.01393585371510953</v>
       </c>
       <c r="P44" t="n">
-        <v>0.07284679404496619</v>
+        <v>0.07284673858978352</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.06673129236364739</v>
+        <v>0.06673145056608787</v>
       </c>
       <c r="R44" t="n">
-        <v>0.04708513073458209</v>
+        <v>0.04708520131893934</v>
       </c>
       <c r="S44" t="n">
         <v>0.02874185131944684</v>
@@ -5677,34 +5677,34 @@
         <v>-0.02801356905788255</v>
       </c>
       <c r="U44" t="n">
-        <v>-0.08018939288756854</v>
+        <v>-0.08018957467739252</v>
       </c>
       <c r="V44" t="n">
         <v>-0.02844215726925059</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02931469843026324</v>
+        <v>0.02931476005271927</v>
       </c>
       <c r="X44" t="n">
-        <v>0.08274345222105417</v>
+        <v>0.08274354711710585</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.008682189367008153</v>
+        <v>0.008682250750831511</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.05581839402804967</v>
+        <v>0.05581828480530282</v>
       </c>
       <c r="AA44" t="n">
-        <v>-0.09166655219825148</v>
+        <v>-0.09166670822959977</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.04613578241989402</v>
+        <v>0.04613566710436601</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.05520572691049708</v>
+        <v>0.05520591416120535</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.1037810049792025</v>
+        <v>0.1037809065490025</v>
       </c>
       <c r="AE44" t="n">
         <v>0.05419182324994032</v>
@@ -5742,10 +5742,10 @@
         <v>0.07237380284171713</v>
       </c>
       <c r="C45" t="n">
-        <v>0.08487807127077129</v>
+        <v>0.0848779879067918</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03808246776354474</v>
+        <v>0.03808255684258932</v>
       </c>
       <c r="E45" t="n">
         <v>-0.01271003877638943</v>
@@ -5754,49 +5754,49 @@
         <v>0.06718432441727251</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0426869905278886</v>
+        <v>0.04268690937268005</v>
       </c>
       <c r="H45" t="n">
         <v>-0.06874221771752564</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.06538229150318797</v>
+        <v>-0.06538236019268939</v>
       </c>
       <c r="J45" t="n">
         <v>-0.06004779994597065</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.004434980476002437</v>
+        <v>-0.004435056183056285</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.07177344788896278</v>
+        <v>-0.07177334743779473</v>
       </c>
       <c r="M45" t="n">
         <v>0.04408957891840748</v>
       </c>
       <c r="N45" t="n">
-        <v>0.07769736975498076</v>
+        <v>0.077697435372162</v>
       </c>
       <c r="O45" t="n">
         <v>-0.07583058706201951</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.007526500695103855</v>
+        <v>-0.007526390032249752</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.01916518811960777</v>
+        <v>0.01916503697151883</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.01122132625650674</v>
+        <v>-0.01122139291040181</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.06273065783577159</v>
+        <v>-0.06273058945978738</v>
       </c>
       <c r="T45" t="n">
         <v>-0.09035160968660572</v>
       </c>
       <c r="U45" t="n">
-        <v>0.02640712839265325</v>
+        <v>0.02640723582692206</v>
       </c>
       <c r="V45" t="n">
         <v>-0.0856115458275003</v>
@@ -5808,22 +5808,22 @@
         <v>-0.02618029815758138</v>
       </c>
       <c r="Y45" t="n">
-        <v>-0.05385124417172005</v>
+        <v>-0.05385130175003872</v>
       </c>
       <c r="Z45" t="n">
-        <v>-0.1457587750382682</v>
+        <v>-0.1457586349441358</v>
       </c>
       <c r="AA45" t="n">
-        <v>-0.07231528468201265</v>
+        <v>-0.0723152911914352</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.06713479870131445</v>
+        <v>-0.06713480610158284</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.06506564025802275</v>
+        <v>-0.06506580732752854</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1151960617979471</v>
+        <v>-0.1151961425888708</v>
       </c>
       <c r="AE45" t="n">
         <v>-0.05004750511814904</v>
@@ -5861,25 +5861,25 @@
         <v>0.06799297584706232</v>
       </c>
       <c r="C46" t="n">
-        <v>0.05575538243469547</v>
+        <v>0.05575531160479863</v>
       </c>
       <c r="D46" t="n">
         <v>0.008209357250419602</v>
       </c>
       <c r="E46" t="n">
-        <v>0.07558137706494072</v>
+        <v>0.07558144397622168</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.01676699494564537</v>
+        <v>-0.01676689277141863</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.01745477527346539</v>
+        <v>-0.01745477663201889</v>
       </c>
       <c r="H46" t="n">
         <v>-0.0571948104459572</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07315788200968387</v>
+        <v>0.07315787582410849</v>
       </c>
       <c r="J46" t="n">
         <v>0.0112139067832242</v>
@@ -5888,37 +5888,37 @@
         <v>0.04080551754649009</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.004507686991363724</v>
+        <v>-0.004507803577516012</v>
       </c>
       <c r="M46" t="n">
         <v>-0.04194720065476343</v>
       </c>
       <c r="N46" t="n">
-        <v>0.05524642821741721</v>
+        <v>0.05524636396719851</v>
       </c>
       <c r="O46" t="n">
         <v>0.3672474934110483</v>
       </c>
       <c r="P46" t="n">
-        <v>0.02447437310855705</v>
+        <v>0.0244742607609103</v>
       </c>
       <c r="Q46" t="n">
         <v>-0.02266033493343766</v>
       </c>
       <c r="R46" t="n">
-        <v>0.02269755137319462</v>
+        <v>0.02269748319784393</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0995501686256679</v>
+        <v>0.09955001545859798</v>
       </c>
       <c r="T46" t="n">
         <v>-0.01110582209610955</v>
       </c>
       <c r="U46" t="n">
-        <v>-0.01286376175381243</v>
+        <v>-0.01286396974779502</v>
       </c>
       <c r="V46" t="n">
-        <v>0.1025440644086133</v>
+        <v>0.1025439786439004</v>
       </c>
       <c r="W46" t="n">
         <v>-0.0448227640589075</v>
@@ -5927,22 +5927,22 @@
         <v>0.05024245991959408</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.05365045151386005</v>
+        <v>0.05365051583299008</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.0569931276481872</v>
+        <v>0.05699294254760501</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.09133218273597454</v>
+        <v>0.09133228862938392</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.0951519095288742</v>
+        <v>0.09515203893512592</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.09614596242517237</v>
+        <v>-0.09614597130451796</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.06410742223132071</v>
+        <v>-0.06410761070376458</v>
       </c>
       <c r="AE46" t="n">
         <v>0.1136079607712011</v>
@@ -5977,37 +5977,37 @@
         <v>45138</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.006837944701178378</v>
+        <v>-0.006838089288003113</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1643951680939357</v>
+        <v>-0.1643951791230944</v>
       </c>
       <c r="D47" t="n">
         <v>0.002290063693139555</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.02316597488767935</v>
+        <v>-0.02316609786534651</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0366794407873885</v>
+        <v>-0.03667954089237124</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.02713168776438157</v>
+        <v>-0.0271317691290871</v>
       </c>
       <c r="H47" t="n">
         <v>-0.004654156796206621</v>
       </c>
       <c r="I47" t="n">
-        <v>0.03040727047825764</v>
+        <v>0.0304071892954112</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2121505480628672</v>
+        <v>0.2121504715161704</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.09450454303673061</v>
+        <v>-0.09450446964831094</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.09125744669787528</v>
+        <v>-0.09125728171428782</v>
       </c>
       <c r="M47" t="n">
         <v>-0.04964123988331004</v>
@@ -6019,37 +6019,37 @@
         <v>-0.04525319243365589</v>
       </c>
       <c r="P47" t="n">
-        <v>0.003028253316120555</v>
+        <v>0.00302836331191858</v>
       </c>
       <c r="Q47" t="n">
         <v>-0.003246044081521293</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.09389675492685912</v>
+        <v>-0.09389669452394667</v>
       </c>
       <c r="S47" t="n">
-        <v>0.01517471966384676</v>
+        <v>0.01517478701808872</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.07480473212467009</v>
+        <v>-0.07480465563377259</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.04869696128170786</v>
+        <v>-0.04869675437677523</v>
       </c>
       <c r="V47" t="n">
-        <v>0.01712658700188729</v>
+        <v>0.01712658833413072</v>
       </c>
       <c r="W47" t="n">
         <v>0.01709725079906188</v>
       </c>
       <c r="X47" t="n">
-        <v>0.07049943723253116</v>
+        <v>0.07049935808655428</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.02280283559551521</v>
+        <v>0.02280271211537044</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.1101554566917686</v>
+        <v>0.1101555838823722</v>
       </c>
       <c r="AA47" t="n">
         <v>0.06929643744727576</v>
@@ -6058,10 +6058,10 @@
         <v>0.06103940803784136</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.1110863276023825</v>
+        <v>-0.1110861345995335</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.02302685624259249</v>
+        <v>-0.02302657029033395</v>
       </c>
       <c r="AE47" t="n">
         <v>0.04058302535626179</v>
@@ -6096,37 +6096,37 @@
         <v>45169</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.01092129361818839</v>
+        <v>-0.01092114962580615</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.04202298622445144</v>
+        <v>-0.04202282902175658</v>
       </c>
       <c r="D48" t="n">
         <v>-0.02208681148199088</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.02411078289418045</v>
+        <v>-0.02411072074493814</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.03173007676697592</v>
+        <v>-0.03173018464030497</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.006836168335668136</v>
+        <v>-0.006836006599630795</v>
       </c>
       <c r="H48" t="n">
         <v>-0.05981944072923306</v>
       </c>
       <c r="I48" t="n">
-        <v>0.002379731353310488</v>
+        <v>0.00237980781545577</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.1217183180081083</v>
+        <v>-0.1217182625450588</v>
       </c>
       <c r="K48" t="n">
-        <v>0.06504078285047887</v>
+        <v>0.06504069653126776</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.01993094756333413</v>
+        <v>-0.01993101071645909</v>
       </c>
       <c r="M48" t="n">
         <v>-0.08613261541484263</v>
@@ -6135,49 +6135,49 @@
         <v>-0.03972535729824234</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.05271503973496439</v>
+        <v>-0.05271494178839464</v>
       </c>
       <c r="P48" t="n">
         <v>-0.04327406558338465</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.01791112218151314</v>
+        <v>-0.01791119686938325</v>
       </c>
       <c r="R48" t="n">
         <v>-0.05416862884766194</v>
       </c>
       <c r="S48" t="n">
-        <v>0.009237437118849723</v>
+        <v>0.00923750247452948</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.1325733258539646</v>
+        <v>-0.132573397568814</v>
       </c>
       <c r="U48" t="n">
-        <v>0.04289830421571939</v>
+        <v>0.04289829943418511</v>
       </c>
       <c r="V48" t="n">
-        <v>-0.02993471591138963</v>
+        <v>-0.02993456524432492</v>
       </c>
       <c r="W48" t="n">
-        <v>0.04434902228383897</v>
+        <v>0.04434890541811698</v>
       </c>
       <c r="X48" t="n">
-        <v>-0.003136119396408232</v>
+        <v>-0.003136045694574596</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.01125540505456535</v>
+        <v>-0.01125540572632333</v>
       </c>
       <c r="Z48" t="n">
-        <v>-0.04290812013642042</v>
+        <v>-0.04290832654007315</v>
       </c>
       <c r="AA48" t="n">
         <v>-0.1139083438987951</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.006219211678642145</v>
+        <v>0.006219109989411109</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.0237314183412789</v>
+        <v>-0.02373141561345948</v>
       </c>
       <c r="AD48" t="n">
         <v>-0.02297829785814709</v>
@@ -6215,19 +6215,19 @@
         <v>45199</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.06144983289172712</v>
+        <v>-0.06144975929682128</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.05501608277304071</v>
+        <v>-0.05501616197239756</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.02440295874351939</v>
+        <v>-0.02440304239378965</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0352369223315746</v>
+        <v>-0.03523698758972671</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01586744192005551</v>
+        <v>0.01586766650449323</v>
       </c>
       <c r="G49" t="n">
         <v>-0.002675583803613546</v>
@@ -6236,13 +6236,13 @@
         <v>0.07854576206011421</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.01234571291484265</v>
+        <v>-0.01234586453432862</v>
       </c>
       <c r="J49" t="n">
         <v>-0.01766310209335997</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02879164404010204</v>
+        <v>-0.02879156794179027</v>
       </c>
       <c r="L49" t="n">
         <v>-0.07743452435116083</v>
@@ -6251,55 +6251,55 @@
         <v>-0.06727350078955963</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.04616959609935778</v>
+        <v>-0.04616967433752805</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.07176972295559525</v>
+        <v>-0.07176981893195511</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01192146824217777</v>
+        <v>0.0119213539642995</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.006158301748496187</v>
+        <v>-0.006158150116801431</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.04407373928713854</v>
+        <v>-0.04407366150340863</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.0004992154630516499</v>
+        <v>-0.0004992801882059972</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.1263080140927024</v>
+        <v>-0.1263081094038242</v>
       </c>
       <c r="U49" t="n">
-        <v>-0.03767711295502851</v>
+        <v>-0.03767721580543215</v>
       </c>
       <c r="V49" t="n">
-        <v>-0.02796517180499902</v>
+        <v>-0.02796524843847159</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02705477290641922</v>
+        <v>0.02705488783687682</v>
       </c>
       <c r="X49" t="n">
-        <v>0.02752652093732832</v>
+        <v>0.02752644677104099</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.06786343867080702</v>
+        <v>0.06786338240466661</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.120796762383192</v>
+        <v>0.1207971119195859</v>
       </c>
       <c r="AA49" t="n">
         <v>0.02475387027306919</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.03682723125379361</v>
+        <v>0.03682733603630339</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.08197586408231317</v>
+        <v>0.08197573669089042</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.02080508656912428</v>
+        <v>0.02080498435693556</v>
       </c>
       <c r="AE49" t="n">
         <v>0.01989156099026079</v>
@@ -6334,64 +6334,64 @@
         <v>45230</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.04347818927472547</v>
+        <v>-0.04347834269223283</v>
       </c>
       <c r="C50" t="n">
         <v>-0.06735161670114476</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.04044703471068034</v>
+        <v>-0.04044695243606444</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.002938690839442204</v>
+        <v>-0.002938623396580242</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.01290037655663001</v>
+        <v>-0.01290059447818626</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.05868536206761477</v>
+        <v>-0.05868544427266331</v>
       </c>
       <c r="H50" t="n">
         <v>-0.09127045284531576</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1101851425633884</v>
+        <v>-0.1101850738393081</v>
       </c>
       <c r="J50" t="n">
         <v>-0.06454592844347495</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.06225394803608186</v>
+        <v>-0.06225402151247372</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0779992038126911</v>
+        <v>0.0779991325463727</v>
       </c>
       <c r="M50" t="n">
         <v>-0.1034888216430454</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.02869989416282948</v>
+        <v>-0.02869989651694538</v>
       </c>
       <c r="O50" t="n">
         <v>-0.03962425795022106</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.004851088434452255</v>
+        <v>-0.004850976050712608</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.02573884138407045</v>
+        <v>-0.02573883941450228</v>
       </c>
       <c r="R50" t="n">
-        <v>0.06173485744787843</v>
+        <v>0.06173477105450886</v>
       </c>
       <c r="S50" t="n">
-        <v>-0.02347646551519156</v>
+        <v>-0.02347653030502206</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.1061281675256964</v>
+        <v>-0.1061281245581852</v>
       </c>
       <c r="U50" t="n">
-        <v>0.02729886110642799</v>
+        <v>0.02729897216815358</v>
       </c>
       <c r="V50" t="n">
         <v>-0.05952379214387615</v>
@@ -6400,13 +6400,13 @@
         <v>0.02000667677334911</v>
       </c>
       <c r="X50" t="n">
-        <v>-0.04860310771460341</v>
+        <v>-0.04860303904330476</v>
       </c>
       <c r="Y50" t="n">
-        <v>-0.02624037721693973</v>
+        <v>-0.02624015407759928</v>
       </c>
       <c r="Z50" t="n">
-        <v>-0.07027770837508318</v>
+        <v>-0.07027779782091059</v>
       </c>
       <c r="AA50" t="n">
         <v>-0.01125436805793445</v>
@@ -6415,10 +6415,10 @@
         <v>-0.09215105021721925</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.01468350402695928</v>
+        <v>-0.01468339520786843</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.06762952711978842</v>
+        <v>0.06762983427848446</v>
       </c>
       <c r="AE50" t="n">
         <v>-0.02083339141628271</v>
@@ -6453,10 +6453,10 @@
         <v>45260</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1152406342806369</v>
+        <v>0.1152406437277922</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1940024536255547</v>
+        <v>0.1940025487199486</v>
       </c>
       <c r="D51" t="n">
         <v>0.08541318882302895</v>
@@ -6465,10 +6465,10 @@
         <v>0.1423660321746791</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1227460715926445</v>
+        <v>0.1227460852299089</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.04488781713577894</v>
+        <v>-0.04488773372578292</v>
       </c>
       <c r="H51" t="n">
         <v>-0.02047245307691381</v>
@@ -6477,40 +6477,40 @@
         <v>0.06594016182267426</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2273300412793864</v>
+        <v>0.227330119523764</v>
       </c>
       <c r="K51" t="n">
         <v>0.03899221835107514</v>
       </c>
       <c r="L51" t="n">
-        <v>0.03224538849394532</v>
+        <v>0.03224545673549217</v>
       </c>
       <c r="M51" t="n">
-        <v>0.09627985283783547</v>
+        <v>0.0962799766866913</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1565601861524382</v>
+        <v>0.1565601993737775</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1475173601586433</v>
+        <v>0.1475174761462739</v>
       </c>
       <c r="P51" t="n">
         <v>0.09958211359011448</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.07121347060215588</v>
+        <v>0.07121346500884718</v>
       </c>
       <c r="R51" t="n">
         <v>0.1172718175710075</v>
       </c>
       <c r="S51" t="n">
-        <v>-0.0003410258096161467</v>
+        <v>-0.0003409594848041708</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.03459023359850655</v>
+        <v>-0.03459017468814407</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.0573426390470454</v>
+        <v>-0.05734274095813074</v>
       </c>
       <c r="V51" t="n">
         <v>0.09177211478292779</v>
@@ -6519,13 +6519,13 @@
         <v>0.01896042699041378</v>
       </c>
       <c r="X51" t="n">
-        <v>0.02172165138355253</v>
+        <v>0.02172157551675147</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.04631589237443867</v>
+        <v>0.04631565479836541</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.00687175236566695</v>
+        <v>0.006871855845004493</v>
       </c>
       <c r="AA51" t="n">
         <v>0.09439199641993445</v>
@@ -6534,10 +6534,10 @@
         <v>0.05253075199457169</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.03942403382844284</v>
+        <v>0.03942380859295191</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.05463800795701523</v>
+        <v>0.05463771634965497</v>
       </c>
       <c r="AE51" t="n">
         <v>0.1011770333488036</v>
@@ -6572,55 +6572,55 @@
         <v>45291</v>
       </c>
       <c r="B52" t="n">
-        <v>0.06760960544114081</v>
+        <v>0.06760961041089875</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1348026369286772</v>
+        <v>0.134802546549164</v>
       </c>
       <c r="D52" t="n">
-        <v>0.03065922402894938</v>
+        <v>0.03065914170374318</v>
       </c>
       <c r="E52" t="n">
-        <v>0.08038684771915272</v>
+        <v>0.0803869664919401</v>
       </c>
       <c r="F52" t="n">
-        <v>0.07195805175667025</v>
+        <v>0.07195805887728524</v>
       </c>
       <c r="G52" t="n">
-        <v>0.009697799477379698</v>
+        <v>0.009697890911710916</v>
       </c>
       <c r="H52" t="n">
         <v>0.1236156576231116</v>
       </c>
       <c r="I52" t="n">
-        <v>0.03374228657756806</v>
+        <v>0.03374220514900483</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1515152249262011</v>
+        <v>0.1515151515151516</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2145881573716881</v>
+        <v>0.214588237791874</v>
       </c>
       <c r="L52" t="n">
         <v>-0.04761906286777651</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1055728377510632</v>
+        <v>0.1055727128523749</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1530026690748749</v>
+        <v>0.1530028262813572</v>
       </c>
       <c r="O52" t="n">
-        <v>0.05193579668802961</v>
+        <v>0.05193569036150891</v>
       </c>
       <c r="P52" t="n">
         <v>0.03958200844255999</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.07208452547793454</v>
+        <v>0.07208444687121918</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0856389610865318</v>
+        <v>0.08563902968105674</v>
       </c>
       <c r="S52" t="n">
         <v>0.06361929385831977</v>
@@ -6638,25 +6638,25 @@
         <v>-0.03047799236226145</v>
       </c>
       <c r="X52" t="n">
-        <v>0.09291336524616756</v>
+        <v>0.09291344639923582</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.1011064951665734</v>
+        <v>0.1011067283058071</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.08219597762506159</v>
+        <v>0.08219576363133529</v>
       </c>
       <c r="AA52" t="n">
         <v>0.02130894968609032</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.05692744578026399</v>
+        <v>0.05692754778669995</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.05203005355413048</v>
+        <v>0.05203005908242142</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.03333330072659946</v>
+        <v>0.03333330369084542</v>
       </c>
       <c r="AE52" t="n">
         <v>0.07584798753668731</v>
@@ -6691,34 +6691,34 @@
         <v>45322</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.007859897365605217</v>
+        <v>-0.007859829055121281</v>
       </c>
       <c r="C53" t="n">
         <v>-0.02258356271926354</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.04784340482471794</v>
+        <v>-0.0478432488937337</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.01240082587888702</v>
+        <v>-0.0124008245155971</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.03802949844338133</v>
+        <v>-0.03802940964151935</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02918370706756224</v>
+        <v>0.02918352331254326</v>
       </c>
       <c r="H53" t="n">
         <v>-0.1193958234743041</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.08778430891584632</v>
+        <v>-0.08778439460134202</v>
       </c>
       <c r="J53" t="n">
         <v>-0.01052633793479996</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.08524801586119235</v>
+        <v>-0.0852480764286524</v>
       </c>
       <c r="L53" t="n">
         <v>-0.02119998722308991</v>
@@ -6727,7 +6727,7 @@
         <v>0.01730170491058836</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.05746164288448241</v>
+        <v>-0.05746170257351535</v>
       </c>
       <c r="O53" t="n">
         <v>-0.1649869754508146</v>
@@ -6739,43 +6739,43 @@
         <v>0.05310477558825677</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02022657116009552</v>
+        <v>0.02022650669856163</v>
       </c>
       <c r="S53" t="n">
-        <v>0.02822324074618909</v>
+        <v>0.02822317834597876</v>
       </c>
       <c r="T53" t="n">
         <v>-0.1138418931953928</v>
       </c>
       <c r="U53" t="n">
-        <v>0.107307545436929</v>
+        <v>0.1073074436608137</v>
       </c>
       <c r="V53" t="n">
-        <v>0.005960445177121576</v>
+        <v>0.005960520147502812</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.05989409064737705</v>
+        <v>-0.05989419877331126</v>
       </c>
       <c r="X53" t="n">
-        <v>0.06736305526842834</v>
+        <v>0.06736298732719326</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.02832355647781681</v>
+        <v>0.02832345285207127</v>
       </c>
       <c r="Z53" t="n">
-        <v>-0.006580846087347214</v>
+        <v>-0.006580751745117186</v>
       </c>
       <c r="AA53" t="n">
         <v>0.02285141369217158</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.04672900713997552</v>
+        <v>0.04672900263005486</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.02680843951062917</v>
+        <v>0.02680854321520321</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.04469499803699817</v>
+        <v>0.04469491582455931</v>
       </c>
       <c r="AE53" t="n">
         <v>-0.04508989729260926</v>
@@ -6810,28 +6810,28 @@
         <v>45351</v>
       </c>
       <c r="B54" t="n">
-        <v>0.08329574323739131</v>
+        <v>0.08329560444319095</v>
       </c>
       <c r="C54" t="n">
-        <v>0.05822550619433109</v>
+        <v>0.05822557799851014</v>
       </c>
       <c r="D54" t="n">
-        <v>0.01457955042597159</v>
+        <v>0.0145795492028955</v>
       </c>
       <c r="E54" t="n">
-        <v>0.03034536405175392</v>
+        <v>0.03034524935801386</v>
       </c>
       <c r="F54" t="n">
         <v>0.07666975983632751</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.04590763726220504</v>
+        <v>-0.04590755331322216</v>
       </c>
       <c r="H54" t="n">
         <v>-0.0527172494987469</v>
       </c>
       <c r="I54" t="n">
-        <v>0.01789096003480983</v>
+        <v>0.01789113582647461</v>
       </c>
       <c r="J54" t="n">
         <v>0.07446801963030092</v>
@@ -6840,16 +6840,16 @@
         <v>-0.02598294686346658</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.01225998550770335</v>
+        <v>-0.01225991680429672</v>
       </c>
       <c r="M54" t="n">
         <v>0.09681113506194516</v>
       </c>
       <c r="N54" t="n">
-        <v>0.06447364407409406</v>
+        <v>0.06447357688535305</v>
       </c>
       <c r="O54" t="n">
-        <v>-0.04759956208172744</v>
+        <v>-0.04759950454569206</v>
       </c>
       <c r="P54" t="n">
         <v>0.0744129603267516</v>
@@ -6861,22 +6861,22 @@
         <v>0.09357647735546126</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.01793513377114453</v>
+        <v>-0.01793507417216289</v>
       </c>
       <c r="T54" t="n">
         <v>-0.0790564469539331</v>
       </c>
       <c r="U54" t="n">
-        <v>0.2134361939429792</v>
+        <v>0.2134364893000225</v>
       </c>
       <c r="V54" t="n">
-        <v>0.06153141594882428</v>
+        <v>0.06153141136312379</v>
       </c>
       <c r="W54" t="n">
-        <v>0.03238282941973059</v>
+        <v>0.03238294815887444</v>
       </c>
       <c r="X54" t="n">
-        <v>0.03813714139929925</v>
+        <v>0.03813714382685629</v>
       </c>
       <c r="Y54" t="n">
         <v>0.09995557843434422</v>
@@ -6888,13 +6888,13 @@
         <v>0.09664892279947468</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.06860901657701857</v>
+        <v>0.06860891804737013</v>
       </c>
       <c r="AC54" t="n">
         <v>-0.02183220689695198</v>
       </c>
       <c r="AD54" t="n">
-        <v>-0.06471569393718524</v>
+        <v>-0.06471553984534539</v>
       </c>
       <c r="AE54" t="n">
         <v>0.1408563351128405</v>
@@ -6929,22 +6929,22 @@
         <v>45382</v>
       </c>
       <c r="B55" t="n">
-        <v>0.03521918275865099</v>
+        <v>0.03521937945428788</v>
       </c>
       <c r="C55" t="n">
-        <v>0.06462885319846245</v>
+        <v>0.06462878095979963</v>
       </c>
       <c r="D55" t="n">
-        <v>0.07980493772670494</v>
+        <v>0.07980493112808706</v>
       </c>
       <c r="E55" t="n">
         <v>0.03960715873092346</v>
       </c>
       <c r="F55" t="n">
-        <v>0.005841473948086762</v>
+        <v>0.005841563076465661</v>
       </c>
       <c r="G55" t="n">
-        <v>0.094162079620975</v>
+        <v>0.09416189517696427</v>
       </c>
       <c r="H55" t="n">
         <v>0.1330284612166672</v>
@@ -6959,22 +6959,22 @@
         <v>0.02507551152579546</v>
       </c>
       <c r="L55" t="n">
-        <v>0.08636448083870274</v>
+        <v>0.0863644052753616</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.008051364769335545</v>
+        <v>-0.008051273189136676</v>
       </c>
       <c r="N55" t="n">
-        <v>0.04408732013232819</v>
+        <v>0.04408738603430473</v>
       </c>
       <c r="O55" t="n">
-        <v>0.2429161356486926</v>
+        <v>0.2429160605621432</v>
       </c>
       <c r="P55" t="n">
         <v>0.04484816570936556</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.03168202351659533</v>
+        <v>0.03168214616942633</v>
       </c>
       <c r="R55" t="n">
         <v>0.01377810976435057</v>
@@ -6983,22 +6983,22 @@
         <v>-0.04660349660012253</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.09034273276057347</v>
+        <v>-0.0903426649804786</v>
       </c>
       <c r="U55" t="n">
-        <v>0.1660951365809453</v>
+        <v>0.1660950356726525</v>
       </c>
       <c r="V55" t="n">
-        <v>0.02060975558385647</v>
+        <v>0.0206096839306471</v>
       </c>
       <c r="W55" t="n">
         <v>0.1396651106828133</v>
       </c>
       <c r="X55" t="n">
-        <v>0.01738512486487709</v>
+        <v>0.01738524856079948</v>
       </c>
       <c r="Y55" t="n">
-        <v>-0.02160648581228564</v>
+        <v>-0.02160657490311368</v>
       </c>
       <c r="Z55" t="n">
         <v>0.02599775111261171</v>
@@ -7010,10 +7010,10 @@
         <v>-0.001298053609855687</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.01127478076144817</v>
+        <v>0.01127488131690635</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.1118767542727011</v>
+        <v>0.1118768423496534</v>
       </c>
       <c r="AE55" t="n">
         <v>0.07860025238167867</v>
@@ -7048,31 +7048,31 @@
         <v>45412</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1002830714790137</v>
+        <v>0.100283003391672</v>
       </c>
       <c r="C56" t="n">
         <v>-0.04511891769969889</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1438016320089071</v>
+        <v>0.1438015444241321</v>
       </c>
       <c r="E56" t="n">
         <v>-0.03070315276649072</v>
       </c>
       <c r="F56" t="n">
-        <v>0.08892967149952713</v>
+        <v>0.08892966361940191</v>
       </c>
       <c r="G56" t="n">
-        <v>0.150774465806887</v>
+        <v>0.1507746597941377</v>
       </c>
       <c r="H56" t="n">
         <v>0.2660180621955777</v>
       </c>
       <c r="I56" t="n">
-        <v>0.02834408850485648</v>
+        <v>0.0283441677063847</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1072062189648231</v>
+        <v>-0.1072061257660936</v>
       </c>
       <c r="K56" t="n">
         <v>-0.001546978628728435</v>
@@ -7081,7 +7081,7 @@
         <v>0.08025189579398107</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.07215582365282658</v>
+        <v>-0.07215590931466775</v>
       </c>
       <c r="N56" t="n">
         <v>-0.07753674044206238</v>
@@ -7093,19 +7093,19 @@
         <v>-0.009328180465592695</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01377261811351271</v>
+        <v>0.01377249758987831</v>
       </c>
       <c r="R56" t="n">
-        <v>-0.02677078720075365</v>
+        <v>-0.02677067547704903</v>
       </c>
       <c r="S56" t="n">
-        <v>0.07885919764814986</v>
+        <v>0.07885913283174939</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.01826482555250042</v>
+        <v>-0.018264898703236</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.07382154489568993</v>
+        <v>-0.07382160505756008</v>
       </c>
       <c r="V56" t="n">
         <v>-0.03979893102570631</v>
@@ -7114,13 +7114,13 @@
         <v>-0.01369447223919884</v>
       </c>
       <c r="X56" t="n">
-        <v>0.002414726705032066</v>
+        <v>0.002414606025070265</v>
       </c>
       <c r="Y56" t="n">
-        <v>-0.1115011339487294</v>
+        <v>-0.1115011441018315</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.007086569292946931</v>
+        <v>0.007086657661873108</v>
       </c>
       <c r="AA56" t="n">
         <v>0.05263160226640862</v>
@@ -7129,10 +7129,10 @@
         <v>0.0004710307452100437</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.1729238056392406</v>
+        <v>0.172923689010327</v>
       </c>
       <c r="AD56" t="n">
-        <v>-0.06131207697384744</v>
+        <v>-0.06131215133169754</v>
       </c>
       <c r="AE56" t="n">
         <v>-0.02309552647809632</v>
@@ -7167,10 +7167,10 @@
         <v>45443</v>
       </c>
       <c r="B57" t="n">
-        <v>0.05769936601111847</v>
+        <v>0.05769925352795013</v>
       </c>
       <c r="C57" t="n">
-        <v>0.06529208131107445</v>
+        <v>0.06529201456526956</v>
       </c>
       <c r="D57" t="n">
         <v>0.02449327767766696</v>
@@ -7179,7 +7179,7 @@
         <v>0.04135597189042728</v>
       </c>
       <c r="F57" t="n">
-        <v>0.02737281011904225</v>
+        <v>0.02737272651742706</v>
       </c>
       <c r="G57" t="n">
         <v>-0.01705054239674098</v>
@@ -7188,10 +7188,10 @@
         <v>-0.003531762506244984</v>
       </c>
       <c r="I57" t="n">
-        <v>0.06690235870723504</v>
+        <v>0.06690227653601277</v>
       </c>
       <c r="J57" t="n">
-        <v>0.05750771207112559</v>
+        <v>0.05750760167792279</v>
       </c>
       <c r="K57" t="n">
         <v>0.1487015639551035</v>
@@ -7209,16 +7209,16 @@
         <v>0.07034842573608979</v>
       </c>
       <c r="P57" t="n">
-        <v>0.03138135333426884</v>
+        <v>0.03138144270927823</v>
       </c>
       <c r="Q57" t="n">
         <v>0.05784528113235132</v>
       </c>
       <c r="R57" t="n">
-        <v>0.02888887154180053</v>
+        <v>0.02888875342855268</v>
       </c>
       <c r="S57" t="n">
-        <v>0.003110391689344905</v>
+        <v>0.003110331797562926</v>
       </c>
       <c r="T57" t="n">
         <v>0.04558316832487241</v>
@@ -7233,13 +7233,13 @@
         <v>-0.007405108022998208</v>
       </c>
       <c r="X57" t="n">
-        <v>0.02649680586622782</v>
+        <v>0.02649686758131531</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.02557700634641646</v>
+        <v>0.02557711145323061</v>
       </c>
       <c r="Z57" t="n">
-        <v>-0.0344018648715716</v>
+        <v>-0.03440194960000054</v>
       </c>
       <c r="AA57" t="n">
         <v>-0.003043450261293046</v>
@@ -7251,7 +7251,7 @@
         <v>0.0286292062172806</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.07878066738819012</v>
+        <v>0.07878075177690991</v>
       </c>
       <c r="AE57" t="n">
         <v>-0.00494004923837843</v>
@@ -7286,16 +7286,16 @@
         <v>45473</v>
       </c>
       <c r="B58" t="n">
-        <v>0.02154282078433267</v>
+        <v>0.0215429294223719</v>
       </c>
       <c r="C58" t="n">
-        <v>0.06209674109759544</v>
+        <v>0.0620966823333251</v>
       </c>
       <c r="D58" t="n">
         <v>-0.04348728144013403</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.02473975465744183</v>
+        <v>-0.02473965170210901</v>
       </c>
       <c r="F58" t="n">
         <v>-0.007968132539033501</v>
@@ -7325,10 +7325,10 @@
         <v>0.03862853667912747</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.09671350931433254</v>
+        <v>-0.09671341960896529</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.02852478307927342</v>
+        <v>-0.02852486726307113</v>
       </c>
       <c r="Q58" t="n">
         <v>0.02039397337710924</v>
@@ -7337,13 +7337,13 @@
         <v>0.04751621388583427</v>
       </c>
       <c r="S58" t="n">
-        <v>-0.02248065641545072</v>
+        <v>-0.02248053932356009</v>
       </c>
       <c r="T58" t="n">
         <v>-0.158111701857381</v>
       </c>
       <c r="U58" t="n">
-        <v>0.006314248392333077</v>
+        <v>0.006314187598907006</v>
       </c>
       <c r="V58" t="n">
         <v>-0.0785249098260532</v>
@@ -7355,10 +7355,10 @@
         <v>0.04927925952373591</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.02341840875655365</v>
+        <v>0.02341850868618311</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.02995956773746622</v>
+        <v>0.02995947686415468</v>
       </c>
       <c r="AA58" t="n">
         <v>-0.07195818313209945</v>
@@ -7370,7 +7370,7 @@
         <v>0.03996103404823104</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.04330287472806682</v>
+        <v>0.04330263666260903</v>
       </c>
       <c r="AE58" t="n">
         <v>-0.03865245357505753</v>
@@ -7408,19 +7408,19 @@
         <v>0.01156453166072402</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3097950001669467</v>
+        <v>0.3097951547011348</v>
       </c>
       <c r="D59" t="n">
-        <v>0.01917692904202872</v>
+        <v>0.01917686072525226</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0877838460055651</v>
+        <v>0.08778362560443709</v>
       </c>
       <c r="F59" t="n">
         <v>-0.04317263849681896</v>
       </c>
       <c r="G59" t="n">
-        <v>0.02137273114427241</v>
+        <v>0.02137265743884553</v>
       </c>
       <c r="H59" t="n">
         <v>-0.0368622448979592</v>
@@ -7429,10 +7429,10 @@
         <v>-0.05437355475245986</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1075990003050882</v>
+        <v>0.1075989000790183</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1133738320302247</v>
+        <v>0.1133739561033134</v>
       </c>
       <c r="L59" t="n">
         <v>0.1101694401961508</v>
@@ -7444,7 +7444,7 @@
         <v>-0.08900962216237784</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.008350678649674204</v>
+        <v>-0.008350777130342935</v>
       </c>
       <c r="P59" t="n">
         <v>0.01482094517086985</v>
@@ -7456,13 +7456,13 @@
         <v>0.09140900293452847</v>
       </c>
       <c r="S59" t="n">
-        <v>-0.004361670384718797</v>
+        <v>-0.004361609114976961</v>
       </c>
       <c r="T59" t="n">
         <v>0.04606139783779928</v>
       </c>
       <c r="U59" t="n">
-        <v>-0.03098046633328522</v>
+        <v>-0.0309804077929029</v>
       </c>
       <c r="V59" t="n">
         <v>0.03201500353072406</v>
@@ -7474,10 +7474,10 @@
         <v>0.05431315254253932</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.07181778334603184</v>
+        <v>0.07181767869055311</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.09591189918913123</v>
+        <v>0.09591199588142429</v>
       </c>
       <c r="AA59" t="n">
         <v>-0.06508456343108426</v>
@@ -7489,7 +7489,7 @@
         <v>0.03280235818015131</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.1121757158695964</v>
+        <v>0.1121758826497266</v>
       </c>
       <c r="AE59" t="n">
         <v>0.00811501042423135</v>
@@ -7530,28 +7530,28 @@
         <v>-0.05037944380909554</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.02769559923956988</v>
+        <v>-0.02769553406471659</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0159558238388231</v>
+        <v>0.01595592243511601</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0233474421827562</v>
+        <v>-0.02334735873794058</v>
       </c>
       <c r="G60" t="n">
-        <v>0.05176605847361904</v>
+        <v>0.05176620653543762</v>
       </c>
       <c r="H60" t="n">
         <v>-0.0385793152976307</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01100001034095222</v>
+        <v>-0.01099993140238542</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.01181901341660541</v>
+        <v>-0.01181892399660267</v>
       </c>
       <c r="K60" t="n">
-        <v>0.04449908909891898</v>
+        <v>0.04449897270116465</v>
       </c>
       <c r="L60" t="n">
         <v>0.0341852400392082</v>
@@ -7563,7 +7563,7 @@
         <v>-0.03669723611458964</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.02255644594494721</v>
+        <v>-0.02255624565239989</v>
       </c>
       <c r="P60" t="n">
         <v>0.01515569693352581</v>
@@ -7572,16 +7572,16 @@
         <v>0.005102102236734796</v>
       </c>
       <c r="R60" t="n">
-        <v>0.07997484082773476</v>
+        <v>0.07997474323591058</v>
       </c>
       <c r="S60" t="n">
-        <v>-0.03464751747098871</v>
+        <v>-0.03464763841513918</v>
       </c>
       <c r="T60" t="n">
         <v>0.07721762005925048</v>
       </c>
       <c r="U60" t="n">
-        <v>-0.01922290077468525</v>
+        <v>-0.01922296311808258</v>
       </c>
       <c r="V60" t="n">
         <v>-0.004105797412731205</v>
@@ -7596,7 +7596,7 @@
         <v>-0.02125690256042112</v>
       </c>
       <c r="Z60" t="n">
-        <v>-0.008608347597387489</v>
+        <v>-0.008608267089109667</v>
       </c>
       <c r="AA60" t="n">
         <v>-0.02362400577561308</v>
@@ -7608,7 +7608,7 @@
         <v>0.05716870687978992</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.02280767325988409</v>
+        <v>0.02280753842650252</v>
       </c>
       <c r="AE60" t="n">
         <v>-0.002561213333643453</v>
@@ -7652,19 +7652,19 @@
         <v>0.06023050314627998</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0317124180359345</v>
+        <v>0.03171251355958171</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05533180345164079</v>
+        <v>0.05533179872411331</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.1188674047648535</v>
+        <v>-0.1188674652205588</v>
       </c>
       <c r="H61" t="n">
         <v>0.09713377964280601</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1097067300516492</v>
+        <v>0.1097067212952374</v>
       </c>
       <c r="J61" t="n">
         <v>0.01371067621638233</v>
@@ -7682,25 +7682,25 @@
         <v>0.03999995044902649</v>
       </c>
       <c r="O61" t="n">
-        <v>0.06338472559719577</v>
+        <v>0.06338461015141039</v>
       </c>
       <c r="P61" t="n">
-        <v>0.01330085238673906</v>
+        <v>0.01330076580166728</v>
       </c>
       <c r="Q61" t="n">
         <v>0.02357946493519103</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.02565604243463659</v>
+        <v>-0.02565595438812918</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.01320132896820603</v>
+        <v>-0.01320126606292471</v>
       </c>
       <c r="T61" t="n">
         <v>0.09913108377746815</v>
       </c>
       <c r="U61" t="n">
-        <v>-0.1091398520657326</v>
+        <v>-0.1091397318726195</v>
       </c>
       <c r="V61" t="n">
         <v>0.03939532887006325</v>
@@ -7709,13 +7709,13 @@
         <v>0.03788143048487447</v>
       </c>
       <c r="X61" t="n">
-        <v>-0.0174051180556869</v>
+        <v>-0.01740500747679197</v>
       </c>
       <c r="Y61" t="n">
         <v>-0.01558076132980002</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.02170769613318257</v>
+        <v>0.0217076131630265</v>
       </c>
       <c r="AA61" t="n">
         <v>0.03989693310278586</v>
@@ -7727,7 +7727,7 @@
         <v>-0.01373383044295884</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.03140699120603729</v>
+        <v>0.0314069953463183</v>
       </c>
       <c r="AE61" t="n">
         <v>-0.01614083845193526</v>
@@ -7771,25 +7771,25 @@
         <v>-0.03630023300783503</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.02546831439039898</v>
+        <v>-0.02546840461981825</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1003064658017877</v>
+        <v>-0.100306538640927</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.03245296370896</v>
+        <v>-0.0324530415762011</v>
       </c>
       <c r="H62" t="n">
         <v>-0.03976781094419202</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.04661698415675908</v>
+        <v>-0.04661698080379528</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.1107913815937513</v>
+        <v>-0.110791291260502</v>
       </c>
       <c r="K62" t="n">
-        <v>0.180575809505324</v>
+        <v>0.1805759159183702</v>
       </c>
       <c r="L62" t="n">
         <v>-0.05080467153950463</v>
@@ -7801,25 +7801,25 @@
         <v>-0.08809521690848576</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.08420141665648562</v>
+        <v>-0.08420140854366187</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.01955540957148327</v>
+        <v>-0.01955524034538303</v>
       </c>
       <c r="Q62" t="n">
         <v>-0.03551428869439044</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.05146625584625653</v>
+        <v>-0.05146616310189811</v>
       </c>
       <c r="S62" t="n">
-        <v>0.04264214516736375</v>
+        <v>0.04264208056774277</v>
       </c>
       <c r="T62" t="n">
         <v>-0.07581742517205681</v>
       </c>
       <c r="U62" t="n">
-        <v>0.01840386788898662</v>
+        <v>0.01840372387036315</v>
       </c>
       <c r="V62" t="n">
         <v>-0.0788893337400276</v>
@@ -7828,7 +7828,7 @@
         <v>-0.04798912346117801</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.03091791201740912</v>
+        <v>-0.03091790853798115</v>
       </c>
       <c r="Y62" t="n">
         <v>0.06282979189928461</v>
@@ -7846,7 +7846,7 @@
         <v>0.002191003682360915</v>
       </c>
       <c r="AD62" t="n">
-        <v>-0.04248916149878068</v>
+        <v>-0.04248910302316256</v>
       </c>
       <c r="AE62" t="n">
         <v>0.03169269777183992</v>
@@ -7887,7 +7887,7 @@
         <v>0.01557211635287592</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.01191744612659718</v>
+        <v>-0.01191751360013493</v>
       </c>
       <c r="E63" t="n">
         <v>0.01411587679625259</v>
@@ -7896,19 +7896,19 @@
         <v>-0.007126542654962043</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.03255513336259552</v>
+        <v>-0.03255505550357052</v>
       </c>
       <c r="H63" t="n">
         <v>-0.01632410941907902</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.04170677075749774</v>
+        <v>-0.04170684305373684</v>
       </c>
       <c r="J63" t="n">
-        <v>0.07571065886454487</v>
+        <v>0.07571054958486934</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.003371468010037959</v>
+        <v>-0.003371647979255599</v>
       </c>
       <c r="L63" t="n">
         <v>-0.001994620411788661</v>
@@ -7920,25 +7920,25 @@
         <v>-0.06668000526475082</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.02450537586216106</v>
+        <v>-0.02450537328397628</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.02322396668321114</v>
+        <v>-0.02322405181201204</v>
       </c>
       <c r="Q63" t="n">
         <v>-0.003388452778786522</v>
       </c>
       <c r="R63" t="n">
-        <v>0.04416410386177283</v>
+        <v>0.04416400176701774</v>
       </c>
       <c r="S63" t="n">
-        <v>-0.01082597803503405</v>
+        <v>-0.0108259167481668</v>
       </c>
       <c r="T63" t="n">
         <v>-0.1014773755054518</v>
       </c>
       <c r="U63" t="n">
-        <v>0.09014147741635714</v>
+        <v>0.09014155379526967</v>
       </c>
       <c r="V63" t="n">
         <v>-0.03492825928626231</v>
@@ -7947,7 +7947,7 @@
         <v>0.006034762916363068</v>
       </c>
       <c r="X63" t="n">
-        <v>0.006979064316714689</v>
+        <v>0.006979063506249439</v>
       </c>
       <c r="Y63" t="n">
         <v>0.02436819636114418</v>
@@ -7965,7 +7965,7 @@
         <v>0.02507830591203675</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.03197679404858267</v>
+        <v>0.03197686292485669</v>
       </c>
       <c r="AE63" t="n">
         <v>-0.01843147548118951</v>
@@ -8006,13 +8006,13 @@
         <v>0.003999989319394937</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.003661431052893294</v>
+        <v>-0.003661363015569519</v>
       </c>
       <c r="E64" t="n">
         <v>-0.02418639284001534</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.03043351297207286</v>
+        <v>-0.03043342234003577</v>
       </c>
       <c r="G64" t="n">
         <v>-0.0166553240927334</v>
@@ -8024,10 +8024,10 @@
         <v>-0.03119491385117756</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.07382757592939637</v>
+        <v>-0.07382748149102325</v>
       </c>
       <c r="K64" t="n">
-        <v>0.01353167391901855</v>
+        <v>0.01353176558433522</v>
       </c>
       <c r="L64" t="n">
         <v>-0.01498998527935824</v>
@@ -8039,7 +8039,7 @@
         <v>0.1362168365435832</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.01421466606945465</v>
+        <v>-0.01421488024017326</v>
       </c>
       <c r="P64" t="n">
         <v>-0.02349651188240576</v>
@@ -8057,7 +8057,7 @@
         <v>-0.06447427965237074</v>
       </c>
       <c r="U64" t="n">
-        <v>-0.02156178459553015</v>
+        <v>-0.0215617203256171</v>
       </c>
       <c r="V64" t="n">
         <v>-0.01685676413344173</v>
@@ -8066,7 +8066,7 @@
         <v>-0.008821536204750235</v>
       </c>
       <c r="X64" t="n">
-        <v>-0.000330055040310695</v>
+        <v>-0.0003300550022476978</v>
       </c>
       <c r="Y64" t="n">
         <v>0.006167392311198894</v>
@@ -8119,7 +8119,7 @@
         <v>45688</v>
       </c>
       <c r="B65" t="n">
-        <v>0.01981845938766713</v>
+        <v>0.01981856219810352</v>
       </c>
       <c r="C65" t="n">
         <v>0.0770252321320346</v>
@@ -8128,22 +8128,22 @@
         <v>0.07155213129086468</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0422277101820836</v>
+        <v>0.04222780618884547</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1027538845714002</v>
+        <v>0.1027537814894321</v>
       </c>
       <c r="G65" t="n">
-        <v>0.08261315203133179</v>
+        <v>0.08261323662750253</v>
       </c>
       <c r="H65" t="n">
         <v>0.07375194125051299</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1015321204253172</v>
+        <v>0.101532039164256</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1911141062011619</v>
+        <v>0.1911139847476788</v>
       </c>
       <c r="K65" t="n">
         <v>-0.06697814686149306</v>
@@ -8158,10 +8158,10 @@
         <v>0.2272728063146028</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.006036317685383485</v>
+        <v>-0.006036208938691945</v>
       </c>
       <c r="P65" t="n">
-        <v>0.1248925351971499</v>
+        <v>0.1248926265690729</v>
       </c>
       <c r="Q65" t="n">
         <v>0.08062860019518636</v>
@@ -8176,7 +8176,7 @@
         <v>0.03122104704547346</v>
       </c>
       <c r="U65" t="n">
-        <v>0.02888328424820674</v>
+        <v>0.028883150978531</v>
       </c>
       <c r="V65" t="n">
         <v>0.1598587890872178</v>
@@ -8185,13 +8185,13 @@
         <v>0.08793173164711665</v>
       </c>
       <c r="X65" t="n">
-        <v>0.03664589817358843</v>
+        <v>0.03664577858479401</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.07530646217383885</v>
+        <v>0.07530654848783924</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.02277612417116304</v>
+        <v>0.02277619651444285</v>
       </c>
       <c r="AA65" t="n">
         <v>0.082851581159056</v>
@@ -8238,7 +8238,7 @@
         <v>45716</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.05401835553459555</v>
+        <v>-0.05401845090134927</v>
       </c>
       <c r="C66" t="n">
         <v>-0.002466084687395842</v>
@@ -8247,25 +8247,25 @@
         <v>-0.06294131974479789</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.03317681447679366</v>
+        <v>-0.03317681142064943</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.01852840169404657</v>
+        <v>-0.01852848646079985</v>
       </c>
       <c r="G66" t="n">
-        <v>0.03685749281593753</v>
+        <v>0.03685741179515323</v>
       </c>
       <c r="H66" t="n">
         <v>0.1277745012045113</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.01178697342394475</v>
+        <v>-0.01178682675158782</v>
       </c>
       <c r="J66" t="n">
         <v>-0.08584756908154112</v>
       </c>
       <c r="K66" t="n">
-        <v>0.05127592543196413</v>
+        <v>0.05127602107173734</v>
       </c>
       <c r="L66" t="n">
         <v>0.055535829960218</v>
@@ -8277,25 +8277,25 @@
         <v>-0.05516984423914373</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.02732811726403583</v>
+        <v>-0.0273280071925136</v>
       </c>
       <c r="P66" t="n">
-        <v>0.03310416419600459</v>
+        <v>0.03310416150704465</v>
       </c>
       <c r="Q66" t="n">
         <v>0.010907470184365</v>
       </c>
       <c r="R66" t="n">
-        <v>0.007123368401744878</v>
+        <v>0.007123283483482901</v>
       </c>
       <c r="S66" t="n">
-        <v>0.07091383200023449</v>
+        <v>0.07091371480472297</v>
       </c>
       <c r="T66" t="n">
         <v>-0.09755544801376403</v>
       </c>
       <c r="U66" t="n">
-        <v>0.3289664807750552</v>
+        <v>0.3289665656192728</v>
       </c>
       <c r="V66" t="n">
         <v>0.01173914901279738</v>
@@ -8304,13 +8304,13 @@
         <v>-0.03534040493905233</v>
       </c>
       <c r="X66" t="n">
-        <v>0.09968138502201351</v>
+        <v>0.09968149630523038</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.09812710260179003</v>
+        <v>0.09812701445600203</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.07058826192273804</v>
+        <v>0.0705881154653345</v>
       </c>
       <c r="AA66" t="n">
         <v>0.03113879041872325</v>
@@ -8363,13 +8363,13 @@
         <v>-0.09517926551480371</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.07664152339721986</v>
+        <v>-0.07664159165516582</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.08928024601514495</v>
+        <v>-0.08928033278659708</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1277702969565048</v>
+        <v>-0.1277701352576363</v>
       </c>
       <c r="G67" t="n">
         <v>-0.1004932057969844</v>
@@ -8378,13 +8378,13 @@
         <v>-0.1295212744104601</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.04055340167120858</v>
+        <v>-0.04055339864386287</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.0873087124980978</v>
+        <v>-0.08730861885308272</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.103551780256926</v>
+        <v>-0.1035518618112492</v>
       </c>
       <c r="L67" t="n">
         <v>-0.009231775532051234</v>
@@ -8396,25 +8396,25 @@
         <v>-0.1290321935641615</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.08532764283966709</v>
+        <v>-0.08532774634771445</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.09440476967360634</v>
+        <v>-0.09440476225108385</v>
       </c>
       <c r="Q67" t="n">
         <v>-0.06692732460123685</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.03482048564429008</v>
+        <v>-0.03482048858027131</v>
       </c>
       <c r="S67" t="n">
-        <v>-0.08952629943181323</v>
+        <v>-0.08952619979406506</v>
       </c>
       <c r="T67" t="n">
         <v>-0.05740558409287977</v>
       </c>
       <c r="U67" t="n">
-        <v>0.2318885917408429</v>
+        <v>0.2318884956627969</v>
       </c>
       <c r="V67" t="n">
         <v>-0.0975504690368747</v>
@@ -8423,13 +8423,13 @@
         <v>-0.1027814301244488</v>
       </c>
       <c r="X67" t="n">
-        <v>-0.0472052432414819</v>
+        <v>-0.04720533966036844</v>
       </c>
       <c r="Y67" t="n">
         <v>-0.05334514279833158</v>
       </c>
       <c r="Z67" t="n">
-        <v>-0.1330455208723276</v>
+        <v>-0.1330455296624601</v>
       </c>
       <c r="AA67" t="n">
         <v>-0.1276963371703792</v>
@@ -8441,7 +8441,7 @@
         <v>0.06230410096647909</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.03685722457782625</v>
+        <v>0.03685710826127808</v>
       </c>
       <c r="AE67" t="n">
         <v>-0.1195195562728721</v>
@@ -8482,13 +8482,13 @@
         <v>0.1086066399602423</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.04674393699287971</v>
+        <v>-0.04674386652479257</v>
       </c>
       <c r="E68" t="n">
         <v>-0.01744446314786019</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.05019700252764869</v>
+        <v>-0.05019719559446323</v>
       </c>
       <c r="G68" t="n">
         <v>-0.04180944968984102</v>
@@ -8497,10 +8497,10 @@
         <v>-0.09532540493207697</v>
       </c>
       <c r="I68" t="n">
-        <v>0.03828941928132945</v>
+        <v>0.03828933849603056</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.08678504062264525</v>
+        <v>-0.08678513432138124</v>
       </c>
       <c r="K68" t="n">
         <v>0.04763120634168039</v>
@@ -8518,13 +8518,13 @@
         <v>0.06219189630605282</v>
       </c>
       <c r="P68" t="n">
-        <v>-0.05358636949084405</v>
+        <v>-0.05358645165917031</v>
       </c>
       <c r="Q68" t="n">
         <v>-0.04374058378952361</v>
       </c>
       <c r="R68" t="n">
-        <v>0.06054776002719331</v>
+        <v>0.06054785267616358</v>
       </c>
       <c r="S68" t="n">
         <v>0.0336727139943771</v>
@@ -8533,7 +8533,7 @@
         <v>0.07513835091996257</v>
       </c>
       <c r="U68" t="n">
-        <v>0.140593377705335</v>
+        <v>0.1405933886705619</v>
       </c>
       <c r="V68" t="n">
         <v>-0.01928152745538114</v>
@@ -8548,7 +8548,7 @@
         <v>0.1166592449663768</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.05625781795718554</v>
+        <v>0.05625789845216822</v>
       </c>
       <c r="AA68" t="n">
         <v>-0.02527591003210772</v>
@@ -8560,7 +8560,7 @@
         <v>0.04942838555118167</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.01135504552955946</v>
+        <v>0.01135515898523898</v>
       </c>
       <c r="AE68" t="n">
         <v>-0.04380556399423685</v>
@@ -8607,7 +8607,7 @@
         <v>0.04218096622177248</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02702695658664722</v>
+        <v>0.02702706365602836</v>
       </c>
       <c r="G69" t="n">
         <v>-0.01609442923211279</v>
@@ -8652,7 +8652,7 @@
         <v>-0.03041713747753316</v>
       </c>
       <c r="U69" t="n">
-        <v>0.08182625176742264</v>
+        <v>0.08182632574147819</v>
       </c>
       <c r="V69" t="n">
         <v>0.04647667637185338</v>
@@ -8726,7 +8726,7 @@
         <v>-0.02862778051639892</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.006822575974142153</v>
+        <v>-0.0068224744658405</v>
       </c>
       <c r="G70" t="n">
         <v>-0.03416937405010523</v>
@@ -8735,7 +8735,7 @@
         <v>-0.01600524281690696</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.04242425644617687</v>
+        <v>-0.04242432874677615</v>
       </c>
       <c r="J70" t="n">
         <v>0.125801796881545</v>
@@ -8771,7 +8771,7 @@
         <v>0.02724721033559074</v>
       </c>
       <c r="U70" t="n">
-        <v>0.08884523681153644</v>
+        <v>0.08884536322530057</v>
       </c>
       <c r="V70" t="n">
         <v>0.03581662060803326</v>
@@ -8798,7 +8798,7 @@
         <v>-0.0362495109956753</v>
       </c>
       <c r="AD70" t="n">
-        <v>-0.08288333580700713</v>
+        <v>-0.08288322754994903</v>
       </c>
       <c r="AE70" t="n">
         <v>-0.001880392422556665</v>
@@ -8845,7 +8845,7 @@
         <v>0.09688342173298947</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.02257129071066521</v>
+        <v>-0.022571288403753</v>
       </c>
       <c r="G71" t="n">
         <v>0.1031238392027138</v>
@@ -8854,10 +8854,10 @@
         <v>0.01965432740052675</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.02848101170248363</v>
+        <v>-0.02848093834911103</v>
       </c>
       <c r="J71" t="n">
-        <v>0.040519152468242</v>
+        <v>0.04051925051181193</v>
       </c>
       <c r="K71" t="n">
         <v>-0.1186064298916358</v>
@@ -8872,7 +8872,7 @@
         <v>0.1344051891994655</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.00413839520348569</v>
+        <v>-0.004138335355979517</v>
       </c>
       <c r="P71" t="n">
         <v>0.06116474988340359</v>
@@ -8890,7 +8890,7 @@
         <v>0.1184928477610665</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01156194388613763</v>
+        <v>0.01156182644489445</v>
       </c>
       <c r="V71" t="n">
         <v>0.1028123930246536</v>
@@ -8917,7 +8917,7 @@
         <v>0.09439430324977494</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.03345756326064664</v>
+        <v>0.03345744127064609</v>
       </c>
       <c r="AE71" t="n">
         <v>0.05953287124563711</v>
@@ -8964,7 +8964,7 @@
         <v>0.03180983788145886</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0107096284285948</v>
+        <v>0.01070952274295278</v>
       </c>
       <c r="G72" t="n">
         <v>0.03296811547686151</v>
@@ -8973,10 +8973,10 @@
         <v>0.08275170278483657</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.009771934821644734</v>
+        <v>-0.009772012538902364</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03437784325830706</v>
+        <v>0.03437774579341513</v>
       </c>
       <c r="K72" t="n">
         <v>0.05550891115542012</v>
@@ -8991,7 +8991,7 @@
         <v>-0.02408521546260645</v>
       </c>
       <c r="O72" t="n">
-        <v>0.04911224379108514</v>
+        <v>0.04911218074342139</v>
       </c>
       <c r="P72" t="n">
         <v>0.03805841998015413</v>
@@ -9092,7 +9092,7 @@
         <v>0.1746470562880447</v>
       </c>
       <c r="I73" t="n">
-        <v>0.004048450494285705</v>
+        <v>0.00404852929623134</v>
       </c>
       <c r="J73" t="n">
         <v>-0.04235288544836924</v>
@@ -9155,7 +9155,7 @@
         <v>-0.03631450111396772</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.01671388019499997</v>
+        <v>0.01671399218154712</v>
       </c>
       <c r="AE73" t="n">
         <v>-0.07356472173836626</v>
@@ -9274,7 +9274,7 @@
         <v>-0.04405320620196362</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.05283111057702738</v>
+        <v>0.05283099461233931</v>
       </c>
       <c r="AE74" t="n">
         <v>-0.02782934426169625</v>
